--- a/dist/週間PDCA_改善版テンプレート.xlsx
+++ b/dist/週間PDCA_改善版テンプレート.xlsx
@@ -17,6 +17,11 @@
     <sheet name="07_改善提案一覧" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="08_運用ルール" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="09_リスト" sheetId="10" state="hidden" r:id="rId10"/>
+    <sheet name="10_月次_GH稼働" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="11_月次_SS稼働" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="12_月次_営業行動" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="13_月次_加算要件" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="14_案件管理台帳" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames>
     <definedName name="施設名リスト">'01_施設マスタ'!$B$2:$B$41</definedName>
@@ -29,8 +34,9 @@
     <definedName name="設定対象月">'03_設定'!$B$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'01_施設マスタ'!$A$1:$I$41</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'04_課題管理表'!$A$1:$U$61</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'05_週次KPIログ'!$A$1:$O$46</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'07_改善提案一覧'!$A$1:$G$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'05_週次KPIログ'!$A$1:$P$46</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'07_改善提案一覧'!$A$1:$G$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'14_案件管理台帳'!$A$1:$Q$61</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -38,11 +44,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="yyyy/mm/dd"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
+    <numFmt numFmtId="166" formatCode="d"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -82,6 +89,14 @@
       <b val="1"/>
       <color rgb="001F3864"/>
       <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <color rgb="00808080"/>
+      <sz val="8"/>
     </font>
     <font>
       <b val="1"/>
@@ -147,7 +162,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -184,10 +199,29 @@
     <xf numFmtId="165" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -822,6 +856,8277 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AS40"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="4.2" customWidth="1" min="5" max="5"/>
+    <col width="4.2" customWidth="1" min="6" max="6"/>
+    <col width="4.2" customWidth="1" min="7" max="7"/>
+    <col width="4.2" customWidth="1" min="8" max="8"/>
+    <col width="4.2" customWidth="1" min="9" max="9"/>
+    <col width="4.2" customWidth="1" min="10" max="10"/>
+    <col width="4.2" customWidth="1" min="11" max="11"/>
+    <col width="4.2" customWidth="1" min="12" max="12"/>
+    <col width="4.2" customWidth="1" min="13" max="13"/>
+    <col width="4.2" customWidth="1" min="14" max="14"/>
+    <col width="4.2" customWidth="1" min="15" max="15"/>
+    <col width="4.2" customWidth="1" min="16" max="16"/>
+    <col width="4.2" customWidth="1" min="17" max="17"/>
+    <col width="4.2" customWidth="1" min="18" max="18"/>
+    <col width="4.2" customWidth="1" min="19" max="19"/>
+    <col width="4.2" customWidth="1" min="20" max="20"/>
+    <col width="4.2" customWidth="1" min="21" max="21"/>
+    <col width="4.2" customWidth="1" min="22" max="22"/>
+    <col width="4.2" customWidth="1" min="23" max="23"/>
+    <col width="4.2" customWidth="1" min="24" max="24"/>
+    <col width="4.2" customWidth="1" min="25" max="25"/>
+    <col width="4.2" customWidth="1" min="26" max="26"/>
+    <col width="4.2" customWidth="1" min="27" max="27"/>
+    <col width="4.2" customWidth="1" min="28" max="28"/>
+    <col width="4.2" customWidth="1" min="29" max="29"/>
+    <col width="4.2" customWidth="1" min="30" max="30"/>
+    <col width="4.2" customWidth="1" min="31" max="31"/>
+    <col width="4.2" customWidth="1" min="32" max="32"/>
+    <col width="4.2" customWidth="1" min="33" max="33"/>
+    <col width="4.2" customWidth="1" min="34" max="34"/>
+    <col width="4.2" customWidth="1" min="35" max="35"/>
+    <col width="9" customWidth="1" min="37" max="37"/>
+    <col width="9" customWidth="1" min="38" max="38"/>
+    <col width="9" customWidth="1" min="39" max="39"/>
+    <col width="13" customWidth="1" min="40" max="40"/>
+    <col width="13" customWidth="1" min="41" max="41"/>
+    <col width="13" customWidth="1" min="42" max="42"/>
+    <col width="13" customWidth="1" min="43" max="43"/>
+    <col width="13" customWidth="1" min="44" max="44"/>
+    <col width="13" customWidth="1" min="45" max="45"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>共同生活援助 稼働実績（●=稼働 / 入=入院 / 外=外泊。入院・外泊は未算定日）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>利用者ID</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>利用者名（任意）</t>
+        </is>
+      </c>
+      <c r="D3" s="22" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="E3" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;1,"",DATE(設定対象年,設定対象月,1))</f>
+        <v/>
+      </c>
+      <c r="F3" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;2,"",DATE(設定対象年,設定対象月,2))</f>
+        <v/>
+      </c>
+      <c r="G3" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;3,"",DATE(設定対象年,設定対象月,3))</f>
+        <v/>
+      </c>
+      <c r="H3" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;4,"",DATE(設定対象年,設定対象月,4))</f>
+        <v/>
+      </c>
+      <c r="I3" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;5,"",DATE(設定対象年,設定対象月,5))</f>
+        <v/>
+      </c>
+      <c r="J3" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;6,"",DATE(設定対象年,設定対象月,6))</f>
+        <v/>
+      </c>
+      <c r="K3" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;7,"",DATE(設定対象年,設定対象月,7))</f>
+        <v/>
+      </c>
+      <c r="L3" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;8,"",DATE(設定対象年,設定対象月,8))</f>
+        <v/>
+      </c>
+      <c r="M3" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;9,"",DATE(設定対象年,設定対象月,9))</f>
+        <v/>
+      </c>
+      <c r="N3" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;10,"",DATE(設定対象年,設定対象月,10))</f>
+        <v/>
+      </c>
+      <c r="O3" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;11,"",DATE(設定対象年,設定対象月,11))</f>
+        <v/>
+      </c>
+      <c r="P3" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;12,"",DATE(設定対象年,設定対象月,12))</f>
+        <v/>
+      </c>
+      <c r="Q3" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;13,"",DATE(設定対象年,設定対象月,13))</f>
+        <v/>
+      </c>
+      <c r="R3" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;14,"",DATE(設定対象年,設定対象月,14))</f>
+        <v/>
+      </c>
+      <c r="S3" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;15,"",DATE(設定対象年,設定対象月,15))</f>
+        <v/>
+      </c>
+      <c r="T3" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;16,"",DATE(設定対象年,設定対象月,16))</f>
+        <v/>
+      </c>
+      <c r="U3" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;17,"",DATE(設定対象年,設定対象月,17))</f>
+        <v/>
+      </c>
+      <c r="V3" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;18,"",DATE(設定対象年,設定対象月,18))</f>
+        <v/>
+      </c>
+      <c r="W3" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;19,"",DATE(設定対象年,設定対象月,19))</f>
+        <v/>
+      </c>
+      <c r="X3" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;20,"",DATE(設定対象年,設定対象月,20))</f>
+        <v/>
+      </c>
+      <c r="Y3" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;21,"",DATE(設定対象年,設定対象月,21))</f>
+        <v/>
+      </c>
+      <c r="Z3" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;22,"",DATE(設定対象年,設定対象月,22))</f>
+        <v/>
+      </c>
+      <c r="AA3" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;23,"",DATE(設定対象年,設定対象月,23))</f>
+        <v/>
+      </c>
+      <c r="AB3" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;24,"",DATE(設定対象年,設定対象月,24))</f>
+        <v/>
+      </c>
+      <c r="AC3" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;25,"",DATE(設定対象年,設定対象月,25))</f>
+        <v/>
+      </c>
+      <c r="AD3" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;26,"",DATE(設定対象年,設定対象月,26))</f>
+        <v/>
+      </c>
+      <c r="AE3" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;27,"",DATE(設定対象年,設定対象月,27))</f>
+        <v/>
+      </c>
+      <c r="AF3" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;28,"",DATE(設定対象年,設定対象月,28))</f>
+        <v/>
+      </c>
+      <c r="AG3" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;29,"",DATE(設定対象年,設定対象月,29))</f>
+        <v/>
+      </c>
+      <c r="AH3" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;30,"",DATE(設定対象年,設定対象月,30))</f>
+        <v/>
+      </c>
+      <c r="AI3" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;31,"",DATE(設定対象年,設定対象月,31))</f>
+        <v/>
+      </c>
+      <c r="AJ3" s="4" t="n"/>
+      <c r="AK3" s="4" t="n"/>
+      <c r="AL3" s="4" t="n"/>
+      <c r="AM3" s="4" t="n"/>
+      <c r="AN3" s="5" t="inlineStr">
+        <is>
+          <t>週</t>
+        </is>
+      </c>
+      <c r="AO3" s="5" t="inlineStr">
+        <is>
+          <t>日数</t>
+        </is>
+      </c>
+      <c r="AP3" s="5" t="inlineStr">
+        <is>
+          <t>稼働回数</t>
+        </is>
+      </c>
+      <c r="AQ3" s="5" t="inlineStr">
+        <is>
+          <t>稼働率</t>
+        </is>
+      </c>
+      <c r="AR3" s="5" t="inlineStr">
+        <is>
+          <t>入院</t>
+        </is>
+      </c>
+      <c r="AS3" s="5" t="inlineStr">
+        <is>
+          <t>外泊</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="n"/>
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="24" t="inlineStr">
+        <is>
+          <t>週</t>
+        </is>
+      </c>
+      <c r="E4" s="24">
+        <f>IF(E3="","","第"&amp;ROUNDUP(1/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="F4" s="24">
+        <f>IF(F3="","","第"&amp;ROUNDUP(2/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="G4" s="24">
+        <f>IF(G3="","","第"&amp;ROUNDUP(3/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="H4" s="24">
+        <f>IF(H3="","","第"&amp;ROUNDUP(4/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="I4" s="24">
+        <f>IF(I3="","","第"&amp;ROUNDUP(5/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="J4" s="24">
+        <f>IF(J3="","","第"&amp;ROUNDUP(6/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="K4" s="24">
+        <f>IF(K3="","","第"&amp;ROUNDUP(7/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="L4" s="24">
+        <f>IF(L3="","","第"&amp;ROUNDUP(8/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="M4" s="24">
+        <f>IF(M3="","","第"&amp;ROUNDUP(9/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="N4" s="24">
+        <f>IF(N3="","","第"&amp;ROUNDUP(10/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="O4" s="24">
+        <f>IF(O3="","","第"&amp;ROUNDUP(11/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="P4" s="24">
+        <f>IF(P3="","","第"&amp;ROUNDUP(12/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="Q4" s="24">
+        <f>IF(Q3="","","第"&amp;ROUNDUP(13/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="R4" s="24">
+        <f>IF(R3="","","第"&amp;ROUNDUP(14/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="S4" s="24">
+        <f>IF(S3="","","第"&amp;ROUNDUP(15/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="T4" s="24">
+        <f>IF(T3="","","第"&amp;ROUNDUP(16/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="U4" s="24">
+        <f>IF(U3="","","第"&amp;ROUNDUP(17/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="V4" s="24">
+        <f>IF(V3="","","第"&amp;ROUNDUP(18/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="W4" s="24">
+        <f>IF(W3="","","第"&amp;ROUNDUP(19/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="X4" s="24">
+        <f>IF(X3="","","第"&amp;ROUNDUP(20/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="Y4" s="24">
+        <f>IF(Y3="","","第"&amp;ROUNDUP(21/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="Z4" s="24">
+        <f>IF(Z3="","","第"&amp;ROUNDUP(22/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="AA4" s="24">
+        <f>IF(AA3="","","第"&amp;ROUNDUP(23/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="AB4" s="24">
+        <f>IF(AB3="","","第"&amp;ROUNDUP(24/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="AC4" s="24">
+        <f>IF(AC3="","","第"&amp;ROUNDUP(25/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="AD4" s="24">
+        <f>IF(AD3="","","第"&amp;ROUNDUP(26/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="AE4" s="24">
+        <f>IF(AE3="","","第"&amp;ROUNDUP(27/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="AF4" s="24">
+        <f>IF(AF3="","","第"&amp;ROUNDUP(28/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="AG4" s="24">
+        <f>IF(AG3="","","第"&amp;ROUNDUP(29/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="AH4" s="24">
+        <f>IF(AH3="","","第"&amp;ROUNDUP(30/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="AI4" s="24">
+        <f>IF(AI3="","","第"&amp;ROUNDUP(31/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="AJ4" s="4" t="n"/>
+      <c r="AK4" s="5" t="inlineStr">
+        <is>
+          <t>稼働日数</t>
+        </is>
+      </c>
+      <c r="AL4" s="5" t="inlineStr">
+        <is>
+          <t>入院</t>
+        </is>
+      </c>
+      <c r="AM4" s="5" t="inlineStr">
+        <is>
+          <t>外泊</t>
+        </is>
+      </c>
+      <c r="AN4" s="4" t="inlineStr">
+        <is>
+          <t>第1週</t>
+        </is>
+      </c>
+      <c r="AO4" s="4">
+        <f>COUNTIF($E$4:$AI$4,$AN4)</f>
+        <v/>
+      </c>
+      <c r="AP4" s="4">
+        <f>SUMPRODUCT(($E$4:$AI$4=$AN4)*$E$35:$AI$35)</f>
+        <v/>
+      </c>
+      <c r="AQ4" s="17">
+        <f>IFERROR($AP4/($AO4*$D$39),"")</f>
+        <v/>
+      </c>
+      <c r="AR4" s="4">
+        <f>SUMPRODUCT(($E$4:$AI$4=$AN4)*$E$36:$AI$36)</f>
+        <v/>
+      </c>
+      <c r="AS4" s="4">
+        <f>SUMPRODUCT(($E$4:$AI$4=$AN4)*$E$37:$AI$37)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="16" t="n"/>
+      <c r="C5" s="16" t="n"/>
+      <c r="D5" s="16" t="n"/>
+      <c r="E5" s="16" t="n"/>
+      <c r="F5" s="16" t="n"/>
+      <c r="G5" s="16" t="n"/>
+      <c r="H5" s="16" t="n"/>
+      <c r="I5" s="16" t="n"/>
+      <c r="J5" s="16" t="n"/>
+      <c r="K5" s="16" t="n"/>
+      <c r="L5" s="16" t="n"/>
+      <c r="M5" s="16" t="n"/>
+      <c r="N5" s="16" t="n"/>
+      <c r="O5" s="16" t="n"/>
+      <c r="P5" s="16" t="n"/>
+      <c r="Q5" s="16" t="n"/>
+      <c r="R5" s="16" t="n"/>
+      <c r="S5" s="16" t="n"/>
+      <c r="T5" s="16" t="n"/>
+      <c r="U5" s="16" t="n"/>
+      <c r="V5" s="16" t="n"/>
+      <c r="W5" s="16" t="n"/>
+      <c r="X5" s="16" t="n"/>
+      <c r="Y5" s="16" t="n"/>
+      <c r="Z5" s="16" t="n"/>
+      <c r="AA5" s="16" t="n"/>
+      <c r="AB5" s="16" t="n"/>
+      <c r="AC5" s="16" t="n"/>
+      <c r="AD5" s="16" t="n"/>
+      <c r="AE5" s="16" t="n"/>
+      <c r="AF5" s="16" t="n"/>
+      <c r="AG5" s="16" t="n"/>
+      <c r="AH5" s="16" t="n"/>
+      <c r="AI5" s="16" t="n"/>
+      <c r="AJ5" s="4" t="n"/>
+      <c r="AK5" s="4">
+        <f>COUNTIF($E5:$AI5,"●")</f>
+        <v/>
+      </c>
+      <c r="AL5" s="4">
+        <f>COUNTIF($E5:$AI5,"入")</f>
+        <v/>
+      </c>
+      <c r="AM5" s="4">
+        <f>COUNTIF($E5:$AI5,"外")</f>
+        <v/>
+      </c>
+      <c r="AN5" s="4" t="inlineStr">
+        <is>
+          <t>第2週</t>
+        </is>
+      </c>
+      <c r="AO5" s="4">
+        <f>COUNTIF($E$4:$AI$4,$AN5)</f>
+        <v/>
+      </c>
+      <c r="AP5" s="4">
+        <f>SUMPRODUCT(($E$4:$AI$4=$AN5)*$E$35:$AI$35)</f>
+        <v/>
+      </c>
+      <c r="AQ5" s="17">
+        <f>IFERROR($AP5/($AO5*$D$39),"")</f>
+        <v/>
+      </c>
+      <c r="AR5" s="4">
+        <f>SUMPRODUCT(($E$4:$AI$4=$AN5)*$E$36:$AI$36)</f>
+        <v/>
+      </c>
+      <c r="AS5" s="4">
+        <f>SUMPRODUCT(($E$4:$AI$4=$AN5)*$E$37:$AI$37)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="16" t="n"/>
+      <c r="C6" s="16" t="n"/>
+      <c r="D6" s="16" t="n"/>
+      <c r="E6" s="16" t="n"/>
+      <c r="F6" s="16" t="n"/>
+      <c r="G6" s="16" t="n"/>
+      <c r="H6" s="16" t="n"/>
+      <c r="I6" s="16" t="n"/>
+      <c r="J6" s="16" t="n"/>
+      <c r="K6" s="16" t="n"/>
+      <c r="L6" s="16" t="n"/>
+      <c r="M6" s="16" t="n"/>
+      <c r="N6" s="16" t="n"/>
+      <c r="O6" s="16" t="n"/>
+      <c r="P6" s="16" t="n"/>
+      <c r="Q6" s="16" t="n"/>
+      <c r="R6" s="16" t="n"/>
+      <c r="S6" s="16" t="n"/>
+      <c r="T6" s="16" t="n"/>
+      <c r="U6" s="16" t="n"/>
+      <c r="V6" s="16" t="n"/>
+      <c r="W6" s="16" t="n"/>
+      <c r="X6" s="16" t="n"/>
+      <c r="Y6" s="16" t="n"/>
+      <c r="Z6" s="16" t="n"/>
+      <c r="AA6" s="16" t="n"/>
+      <c r="AB6" s="16" t="n"/>
+      <c r="AC6" s="16" t="n"/>
+      <c r="AD6" s="16" t="n"/>
+      <c r="AE6" s="16" t="n"/>
+      <c r="AF6" s="16" t="n"/>
+      <c r="AG6" s="16" t="n"/>
+      <c r="AH6" s="16" t="n"/>
+      <c r="AI6" s="16" t="n"/>
+      <c r="AJ6" s="4" t="n"/>
+      <c r="AK6" s="4">
+        <f>COUNTIF($E6:$AI6,"●")</f>
+        <v/>
+      </c>
+      <c r="AL6" s="4">
+        <f>COUNTIF($E6:$AI6,"入")</f>
+        <v/>
+      </c>
+      <c r="AM6" s="4">
+        <f>COUNTIF($E6:$AI6,"外")</f>
+        <v/>
+      </c>
+      <c r="AN6" s="4" t="inlineStr">
+        <is>
+          <t>第3週</t>
+        </is>
+      </c>
+      <c r="AO6" s="4">
+        <f>COUNTIF($E$4:$AI$4,$AN6)</f>
+        <v/>
+      </c>
+      <c r="AP6" s="4">
+        <f>SUMPRODUCT(($E$4:$AI$4=$AN6)*$E$35:$AI$35)</f>
+        <v/>
+      </c>
+      <c r="AQ6" s="17">
+        <f>IFERROR($AP6/($AO6*$D$39),"")</f>
+        <v/>
+      </c>
+      <c r="AR6" s="4">
+        <f>SUMPRODUCT(($E$4:$AI$4=$AN6)*$E$36:$AI$36)</f>
+        <v/>
+      </c>
+      <c r="AS6" s="4">
+        <f>SUMPRODUCT(($E$4:$AI$4=$AN6)*$E$37:$AI$37)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="16" t="n"/>
+      <c r="C7" s="16" t="n"/>
+      <c r="D7" s="16" t="n"/>
+      <c r="E7" s="16" t="n"/>
+      <c r="F7" s="16" t="n"/>
+      <c r="G7" s="16" t="n"/>
+      <c r="H7" s="16" t="n"/>
+      <c r="I7" s="16" t="n"/>
+      <c r="J7" s="16" t="n"/>
+      <c r="K7" s="16" t="n"/>
+      <c r="L7" s="16" t="n"/>
+      <c r="M7" s="16" t="n"/>
+      <c r="N7" s="16" t="n"/>
+      <c r="O7" s="16" t="n"/>
+      <c r="P7" s="16" t="n"/>
+      <c r="Q7" s="16" t="n"/>
+      <c r="R7" s="16" t="n"/>
+      <c r="S7" s="16" t="n"/>
+      <c r="T7" s="16" t="n"/>
+      <c r="U7" s="16" t="n"/>
+      <c r="V7" s="16" t="n"/>
+      <c r="W7" s="16" t="n"/>
+      <c r="X7" s="16" t="n"/>
+      <c r="Y7" s="16" t="n"/>
+      <c r="Z7" s="16" t="n"/>
+      <c r="AA7" s="16" t="n"/>
+      <c r="AB7" s="16" t="n"/>
+      <c r="AC7" s="16" t="n"/>
+      <c r="AD7" s="16" t="n"/>
+      <c r="AE7" s="16" t="n"/>
+      <c r="AF7" s="16" t="n"/>
+      <c r="AG7" s="16" t="n"/>
+      <c r="AH7" s="16" t="n"/>
+      <c r="AI7" s="16" t="n"/>
+      <c r="AJ7" s="4" t="n"/>
+      <c r="AK7" s="4">
+        <f>COUNTIF($E7:$AI7,"●")</f>
+        <v/>
+      </c>
+      <c r="AL7" s="4">
+        <f>COUNTIF($E7:$AI7,"入")</f>
+        <v/>
+      </c>
+      <c r="AM7" s="4">
+        <f>COUNTIF($E7:$AI7,"外")</f>
+        <v/>
+      </c>
+      <c r="AN7" s="4" t="inlineStr">
+        <is>
+          <t>第4週</t>
+        </is>
+      </c>
+      <c r="AO7" s="4">
+        <f>COUNTIF($E$4:$AI$4,$AN7)</f>
+        <v/>
+      </c>
+      <c r="AP7" s="4">
+        <f>SUMPRODUCT(($E$4:$AI$4=$AN7)*$E$35:$AI$35)</f>
+        <v/>
+      </c>
+      <c r="AQ7" s="17">
+        <f>IFERROR($AP7/($AO7*$D$39),"")</f>
+        <v/>
+      </c>
+      <c r="AR7" s="4">
+        <f>SUMPRODUCT(($E$4:$AI$4=$AN7)*$E$36:$AI$36)</f>
+        <v/>
+      </c>
+      <c r="AS7" s="4">
+        <f>SUMPRODUCT(($E$4:$AI$4=$AN7)*$E$37:$AI$37)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="16" t="n"/>
+      <c r="C8" s="16" t="n"/>
+      <c r="D8" s="16" t="n"/>
+      <c r="E8" s="16" t="n"/>
+      <c r="F8" s="16" t="n"/>
+      <c r="G8" s="16" t="n"/>
+      <c r="H8" s="16" t="n"/>
+      <c r="I8" s="16" t="n"/>
+      <c r="J8" s="16" t="n"/>
+      <c r="K8" s="16" t="n"/>
+      <c r="L8" s="16" t="n"/>
+      <c r="M8" s="16" t="n"/>
+      <c r="N8" s="16" t="n"/>
+      <c r="O8" s="16" t="n"/>
+      <c r="P8" s="16" t="n"/>
+      <c r="Q8" s="16" t="n"/>
+      <c r="R8" s="16" t="n"/>
+      <c r="S8" s="16" t="n"/>
+      <c r="T8" s="16" t="n"/>
+      <c r="U8" s="16" t="n"/>
+      <c r="V8" s="16" t="n"/>
+      <c r="W8" s="16" t="n"/>
+      <c r="X8" s="16" t="n"/>
+      <c r="Y8" s="16" t="n"/>
+      <c r="Z8" s="16" t="n"/>
+      <c r="AA8" s="16" t="n"/>
+      <c r="AB8" s="16" t="n"/>
+      <c r="AC8" s="16" t="n"/>
+      <c r="AD8" s="16" t="n"/>
+      <c r="AE8" s="16" t="n"/>
+      <c r="AF8" s="16" t="n"/>
+      <c r="AG8" s="16" t="n"/>
+      <c r="AH8" s="16" t="n"/>
+      <c r="AI8" s="16" t="n"/>
+      <c r="AJ8" s="4" t="n"/>
+      <c r="AK8" s="4">
+        <f>COUNTIF($E8:$AI8,"●")</f>
+        <v/>
+      </c>
+      <c r="AL8" s="4">
+        <f>COUNTIF($E8:$AI8,"入")</f>
+        <v/>
+      </c>
+      <c r="AM8" s="4">
+        <f>COUNTIF($E8:$AI8,"外")</f>
+        <v/>
+      </c>
+      <c r="AN8" s="4" t="inlineStr">
+        <is>
+          <t>第5週</t>
+        </is>
+      </c>
+      <c r="AO8" s="4">
+        <f>COUNTIF($E$4:$AI$4,$AN8)</f>
+        <v/>
+      </c>
+      <c r="AP8" s="4">
+        <f>SUMPRODUCT(($E$4:$AI$4=$AN8)*$E$35:$AI$35)</f>
+        <v/>
+      </c>
+      <c r="AQ8" s="17">
+        <f>IFERROR($AP8/($AO8*$D$39),"")</f>
+        <v/>
+      </c>
+      <c r="AR8" s="4">
+        <f>SUMPRODUCT(($E$4:$AI$4=$AN8)*$E$36:$AI$36)</f>
+        <v/>
+      </c>
+      <c r="AS8" s="4">
+        <f>SUMPRODUCT(($E$4:$AI$4=$AN8)*$E$37:$AI$37)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="16" t="n"/>
+      <c r="C9" s="16" t="n"/>
+      <c r="D9" s="16" t="n"/>
+      <c r="E9" s="16" t="n"/>
+      <c r="F9" s="16" t="n"/>
+      <c r="G9" s="16" t="n"/>
+      <c r="H9" s="16" t="n"/>
+      <c r="I9" s="16" t="n"/>
+      <c r="J9" s="16" t="n"/>
+      <c r="K9" s="16" t="n"/>
+      <c r="L9" s="16" t="n"/>
+      <c r="M9" s="16" t="n"/>
+      <c r="N9" s="16" t="n"/>
+      <c r="O9" s="16" t="n"/>
+      <c r="P9" s="16" t="n"/>
+      <c r="Q9" s="16" t="n"/>
+      <c r="R9" s="16" t="n"/>
+      <c r="S9" s="16" t="n"/>
+      <c r="T9" s="16" t="n"/>
+      <c r="U9" s="16" t="n"/>
+      <c r="V9" s="16" t="n"/>
+      <c r="W9" s="16" t="n"/>
+      <c r="X9" s="16" t="n"/>
+      <c r="Y9" s="16" t="n"/>
+      <c r="Z9" s="16" t="n"/>
+      <c r="AA9" s="16" t="n"/>
+      <c r="AB9" s="16" t="n"/>
+      <c r="AC9" s="16" t="n"/>
+      <c r="AD9" s="16" t="n"/>
+      <c r="AE9" s="16" t="n"/>
+      <c r="AF9" s="16" t="n"/>
+      <c r="AG9" s="16" t="n"/>
+      <c r="AH9" s="16" t="n"/>
+      <c r="AI9" s="16" t="n"/>
+      <c r="AJ9" s="4" t="n"/>
+      <c r="AK9" s="4">
+        <f>COUNTIF($E9:$AI9,"●")</f>
+        <v/>
+      </c>
+      <c r="AL9" s="4">
+        <f>COUNTIF($E9:$AI9,"入")</f>
+        <v/>
+      </c>
+      <c r="AM9" s="4">
+        <f>COUNTIF($E9:$AI9,"外")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="16" t="n"/>
+      <c r="C10" s="16" t="n"/>
+      <c r="D10" s="16" t="n"/>
+      <c r="E10" s="16" t="n"/>
+      <c r="F10" s="16" t="n"/>
+      <c r="G10" s="16" t="n"/>
+      <c r="H10" s="16" t="n"/>
+      <c r="I10" s="16" t="n"/>
+      <c r="J10" s="16" t="n"/>
+      <c r="K10" s="16" t="n"/>
+      <c r="L10" s="16" t="n"/>
+      <c r="M10" s="16" t="n"/>
+      <c r="N10" s="16" t="n"/>
+      <c r="O10" s="16" t="n"/>
+      <c r="P10" s="16" t="n"/>
+      <c r="Q10" s="16" t="n"/>
+      <c r="R10" s="16" t="n"/>
+      <c r="S10" s="16" t="n"/>
+      <c r="T10" s="16" t="n"/>
+      <c r="U10" s="16" t="n"/>
+      <c r="V10" s="16" t="n"/>
+      <c r="W10" s="16" t="n"/>
+      <c r="X10" s="16" t="n"/>
+      <c r="Y10" s="16" t="n"/>
+      <c r="Z10" s="16" t="n"/>
+      <c r="AA10" s="16" t="n"/>
+      <c r="AB10" s="16" t="n"/>
+      <c r="AC10" s="16" t="n"/>
+      <c r="AD10" s="16" t="n"/>
+      <c r="AE10" s="16" t="n"/>
+      <c r="AF10" s="16" t="n"/>
+      <c r="AG10" s="16" t="n"/>
+      <c r="AH10" s="16" t="n"/>
+      <c r="AI10" s="16" t="n"/>
+      <c r="AJ10" s="4" t="n"/>
+      <c r="AK10" s="4">
+        <f>COUNTIF($E10:$AI10,"●")</f>
+        <v/>
+      </c>
+      <c r="AL10" s="4">
+        <f>COUNTIF($E10:$AI10,"入")</f>
+        <v/>
+      </c>
+      <c r="AM10" s="4">
+        <f>COUNTIF($E10:$AI10,"外")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="16" t="n"/>
+      <c r="C11" s="16" t="n"/>
+      <c r="D11" s="16" t="n"/>
+      <c r="E11" s="16" t="n"/>
+      <c r="F11" s="16" t="n"/>
+      <c r="G11" s="16" t="n"/>
+      <c r="H11" s="16" t="n"/>
+      <c r="I11" s="16" t="n"/>
+      <c r="J11" s="16" t="n"/>
+      <c r="K11" s="16" t="n"/>
+      <c r="L11" s="16" t="n"/>
+      <c r="M11" s="16" t="n"/>
+      <c r="N11" s="16" t="n"/>
+      <c r="O11" s="16" t="n"/>
+      <c r="P11" s="16" t="n"/>
+      <c r="Q11" s="16" t="n"/>
+      <c r="R11" s="16" t="n"/>
+      <c r="S11" s="16" t="n"/>
+      <c r="T11" s="16" t="n"/>
+      <c r="U11" s="16" t="n"/>
+      <c r="V11" s="16" t="n"/>
+      <c r="W11" s="16" t="n"/>
+      <c r="X11" s="16" t="n"/>
+      <c r="Y11" s="16" t="n"/>
+      <c r="Z11" s="16" t="n"/>
+      <c r="AA11" s="16" t="n"/>
+      <c r="AB11" s="16" t="n"/>
+      <c r="AC11" s="16" t="n"/>
+      <c r="AD11" s="16" t="n"/>
+      <c r="AE11" s="16" t="n"/>
+      <c r="AF11" s="16" t="n"/>
+      <c r="AG11" s="16" t="n"/>
+      <c r="AH11" s="16" t="n"/>
+      <c r="AI11" s="16" t="n"/>
+      <c r="AJ11" s="4" t="n"/>
+      <c r="AK11" s="4">
+        <f>COUNTIF($E11:$AI11,"●")</f>
+        <v/>
+      </c>
+      <c r="AL11" s="4">
+        <f>COUNTIF($E11:$AI11,"入")</f>
+        <v/>
+      </c>
+      <c r="AM11" s="4">
+        <f>COUNTIF($E11:$AI11,"外")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="16" t="n"/>
+      <c r="C12" s="16" t="n"/>
+      <c r="D12" s="16" t="n"/>
+      <c r="E12" s="16" t="n"/>
+      <c r="F12" s="16" t="n"/>
+      <c r="G12" s="16" t="n"/>
+      <c r="H12" s="16" t="n"/>
+      <c r="I12" s="16" t="n"/>
+      <c r="J12" s="16" t="n"/>
+      <c r="K12" s="16" t="n"/>
+      <c r="L12" s="16" t="n"/>
+      <c r="M12" s="16" t="n"/>
+      <c r="N12" s="16" t="n"/>
+      <c r="O12" s="16" t="n"/>
+      <c r="P12" s="16" t="n"/>
+      <c r="Q12" s="16" t="n"/>
+      <c r="R12" s="16" t="n"/>
+      <c r="S12" s="16" t="n"/>
+      <c r="T12" s="16" t="n"/>
+      <c r="U12" s="16" t="n"/>
+      <c r="V12" s="16" t="n"/>
+      <c r="W12" s="16" t="n"/>
+      <c r="X12" s="16" t="n"/>
+      <c r="Y12" s="16" t="n"/>
+      <c r="Z12" s="16" t="n"/>
+      <c r="AA12" s="16" t="n"/>
+      <c r="AB12" s="16" t="n"/>
+      <c r="AC12" s="16" t="n"/>
+      <c r="AD12" s="16" t="n"/>
+      <c r="AE12" s="16" t="n"/>
+      <c r="AF12" s="16" t="n"/>
+      <c r="AG12" s="16" t="n"/>
+      <c r="AH12" s="16" t="n"/>
+      <c r="AI12" s="16" t="n"/>
+      <c r="AJ12" s="4" t="n"/>
+      <c r="AK12" s="4">
+        <f>COUNTIF($E12:$AI12,"●")</f>
+        <v/>
+      </c>
+      <c r="AL12" s="4">
+        <f>COUNTIF($E12:$AI12,"入")</f>
+        <v/>
+      </c>
+      <c r="AM12" s="4">
+        <f>COUNTIF($E12:$AI12,"外")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="16" t="n"/>
+      <c r="C13" s="16" t="n"/>
+      <c r="D13" s="16" t="n"/>
+      <c r="E13" s="16" t="n"/>
+      <c r="F13" s="16" t="n"/>
+      <c r="G13" s="16" t="n"/>
+      <c r="H13" s="16" t="n"/>
+      <c r="I13" s="16" t="n"/>
+      <c r="J13" s="16" t="n"/>
+      <c r="K13" s="16" t="n"/>
+      <c r="L13" s="16" t="n"/>
+      <c r="M13" s="16" t="n"/>
+      <c r="N13" s="16" t="n"/>
+      <c r="O13" s="16" t="n"/>
+      <c r="P13" s="16" t="n"/>
+      <c r="Q13" s="16" t="n"/>
+      <c r="R13" s="16" t="n"/>
+      <c r="S13" s="16" t="n"/>
+      <c r="T13" s="16" t="n"/>
+      <c r="U13" s="16" t="n"/>
+      <c r="V13" s="16" t="n"/>
+      <c r="W13" s="16" t="n"/>
+      <c r="X13" s="16" t="n"/>
+      <c r="Y13" s="16" t="n"/>
+      <c r="Z13" s="16" t="n"/>
+      <c r="AA13" s="16" t="n"/>
+      <c r="AB13" s="16" t="n"/>
+      <c r="AC13" s="16" t="n"/>
+      <c r="AD13" s="16" t="n"/>
+      <c r="AE13" s="16" t="n"/>
+      <c r="AF13" s="16" t="n"/>
+      <c r="AG13" s="16" t="n"/>
+      <c r="AH13" s="16" t="n"/>
+      <c r="AI13" s="16" t="n"/>
+      <c r="AJ13" s="4" t="n"/>
+      <c r="AK13" s="4">
+        <f>COUNTIF($E13:$AI13,"●")</f>
+        <v/>
+      </c>
+      <c r="AL13" s="4">
+        <f>COUNTIF($E13:$AI13,"入")</f>
+        <v/>
+      </c>
+      <c r="AM13" s="4">
+        <f>COUNTIF($E13:$AI13,"外")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="16" t="n"/>
+      <c r="C14" s="16" t="n"/>
+      <c r="D14" s="16" t="n"/>
+      <c r="E14" s="16" t="n"/>
+      <c r="F14" s="16" t="n"/>
+      <c r="G14" s="16" t="n"/>
+      <c r="H14" s="16" t="n"/>
+      <c r="I14" s="16" t="n"/>
+      <c r="J14" s="16" t="n"/>
+      <c r="K14" s="16" t="n"/>
+      <c r="L14" s="16" t="n"/>
+      <c r="M14" s="16" t="n"/>
+      <c r="N14" s="16" t="n"/>
+      <c r="O14" s="16" t="n"/>
+      <c r="P14" s="16" t="n"/>
+      <c r="Q14" s="16" t="n"/>
+      <c r="R14" s="16" t="n"/>
+      <c r="S14" s="16" t="n"/>
+      <c r="T14" s="16" t="n"/>
+      <c r="U14" s="16" t="n"/>
+      <c r="V14" s="16" t="n"/>
+      <c r="W14" s="16" t="n"/>
+      <c r="X14" s="16" t="n"/>
+      <c r="Y14" s="16" t="n"/>
+      <c r="Z14" s="16" t="n"/>
+      <c r="AA14" s="16" t="n"/>
+      <c r="AB14" s="16" t="n"/>
+      <c r="AC14" s="16" t="n"/>
+      <c r="AD14" s="16" t="n"/>
+      <c r="AE14" s="16" t="n"/>
+      <c r="AF14" s="16" t="n"/>
+      <c r="AG14" s="16" t="n"/>
+      <c r="AH14" s="16" t="n"/>
+      <c r="AI14" s="16" t="n"/>
+      <c r="AJ14" s="4" t="n"/>
+      <c r="AK14" s="4">
+        <f>COUNTIF($E14:$AI14,"●")</f>
+        <v/>
+      </c>
+      <c r="AL14" s="4">
+        <f>COUNTIF($E14:$AI14,"入")</f>
+        <v/>
+      </c>
+      <c r="AM14" s="4">
+        <f>COUNTIF($E14:$AI14,"外")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="16" t="n"/>
+      <c r="C15" s="16" t="n"/>
+      <c r="D15" s="16" t="n"/>
+      <c r="E15" s="16" t="n"/>
+      <c r="F15" s="16" t="n"/>
+      <c r="G15" s="16" t="n"/>
+      <c r="H15" s="16" t="n"/>
+      <c r="I15" s="16" t="n"/>
+      <c r="J15" s="16" t="n"/>
+      <c r="K15" s="16" t="n"/>
+      <c r="L15" s="16" t="n"/>
+      <c r="M15" s="16" t="n"/>
+      <c r="N15" s="16" t="n"/>
+      <c r="O15" s="16" t="n"/>
+      <c r="P15" s="16" t="n"/>
+      <c r="Q15" s="16" t="n"/>
+      <c r="R15" s="16" t="n"/>
+      <c r="S15" s="16" t="n"/>
+      <c r="T15" s="16" t="n"/>
+      <c r="U15" s="16" t="n"/>
+      <c r="V15" s="16" t="n"/>
+      <c r="W15" s="16" t="n"/>
+      <c r="X15" s="16" t="n"/>
+      <c r="Y15" s="16" t="n"/>
+      <c r="Z15" s="16" t="n"/>
+      <c r="AA15" s="16" t="n"/>
+      <c r="AB15" s="16" t="n"/>
+      <c r="AC15" s="16" t="n"/>
+      <c r="AD15" s="16" t="n"/>
+      <c r="AE15" s="16" t="n"/>
+      <c r="AF15" s="16" t="n"/>
+      <c r="AG15" s="16" t="n"/>
+      <c r="AH15" s="16" t="n"/>
+      <c r="AI15" s="16" t="n"/>
+      <c r="AJ15" s="4" t="n"/>
+      <c r="AK15" s="4">
+        <f>COUNTIF($E15:$AI15,"●")</f>
+        <v/>
+      </c>
+      <c r="AL15" s="4">
+        <f>COUNTIF($E15:$AI15,"入")</f>
+        <v/>
+      </c>
+      <c r="AM15" s="4">
+        <f>COUNTIF($E15:$AI15,"外")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="16" t="n"/>
+      <c r="C16" s="16" t="n"/>
+      <c r="D16" s="16" t="n"/>
+      <c r="E16" s="16" t="n"/>
+      <c r="F16" s="16" t="n"/>
+      <c r="G16" s="16" t="n"/>
+      <c r="H16" s="16" t="n"/>
+      <c r="I16" s="16" t="n"/>
+      <c r="J16" s="16" t="n"/>
+      <c r="K16" s="16" t="n"/>
+      <c r="L16" s="16" t="n"/>
+      <c r="M16" s="16" t="n"/>
+      <c r="N16" s="16" t="n"/>
+      <c r="O16" s="16" t="n"/>
+      <c r="P16" s="16" t="n"/>
+      <c r="Q16" s="16" t="n"/>
+      <c r="R16" s="16" t="n"/>
+      <c r="S16" s="16" t="n"/>
+      <c r="T16" s="16" t="n"/>
+      <c r="U16" s="16" t="n"/>
+      <c r="V16" s="16" t="n"/>
+      <c r="W16" s="16" t="n"/>
+      <c r="X16" s="16" t="n"/>
+      <c r="Y16" s="16" t="n"/>
+      <c r="Z16" s="16" t="n"/>
+      <c r="AA16" s="16" t="n"/>
+      <c r="AB16" s="16" t="n"/>
+      <c r="AC16" s="16" t="n"/>
+      <c r="AD16" s="16" t="n"/>
+      <c r="AE16" s="16" t="n"/>
+      <c r="AF16" s="16" t="n"/>
+      <c r="AG16" s="16" t="n"/>
+      <c r="AH16" s="16" t="n"/>
+      <c r="AI16" s="16" t="n"/>
+      <c r="AJ16" s="4" t="n"/>
+      <c r="AK16" s="4">
+        <f>COUNTIF($E16:$AI16,"●")</f>
+        <v/>
+      </c>
+      <c r="AL16" s="4">
+        <f>COUNTIF($E16:$AI16,"入")</f>
+        <v/>
+      </c>
+      <c r="AM16" s="4">
+        <f>COUNTIF($E16:$AI16,"外")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="16" t="n"/>
+      <c r="C17" s="16" t="n"/>
+      <c r="D17" s="16" t="n"/>
+      <c r="E17" s="16" t="n"/>
+      <c r="F17" s="16" t="n"/>
+      <c r="G17" s="16" t="n"/>
+      <c r="H17" s="16" t="n"/>
+      <c r="I17" s="16" t="n"/>
+      <c r="J17" s="16" t="n"/>
+      <c r="K17" s="16" t="n"/>
+      <c r="L17" s="16" t="n"/>
+      <c r="M17" s="16" t="n"/>
+      <c r="N17" s="16" t="n"/>
+      <c r="O17" s="16" t="n"/>
+      <c r="P17" s="16" t="n"/>
+      <c r="Q17" s="16" t="n"/>
+      <c r="R17" s="16" t="n"/>
+      <c r="S17" s="16" t="n"/>
+      <c r="T17" s="16" t="n"/>
+      <c r="U17" s="16" t="n"/>
+      <c r="V17" s="16" t="n"/>
+      <c r="W17" s="16" t="n"/>
+      <c r="X17" s="16" t="n"/>
+      <c r="Y17" s="16" t="n"/>
+      <c r="Z17" s="16" t="n"/>
+      <c r="AA17" s="16" t="n"/>
+      <c r="AB17" s="16" t="n"/>
+      <c r="AC17" s="16" t="n"/>
+      <c r="AD17" s="16" t="n"/>
+      <c r="AE17" s="16" t="n"/>
+      <c r="AF17" s="16" t="n"/>
+      <c r="AG17" s="16" t="n"/>
+      <c r="AH17" s="16" t="n"/>
+      <c r="AI17" s="16" t="n"/>
+      <c r="AJ17" s="4" t="n"/>
+      <c r="AK17" s="4">
+        <f>COUNTIF($E17:$AI17,"●")</f>
+        <v/>
+      </c>
+      <c r="AL17" s="4">
+        <f>COUNTIF($E17:$AI17,"入")</f>
+        <v/>
+      </c>
+      <c r="AM17" s="4">
+        <f>COUNTIF($E17:$AI17,"外")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="16" t="n"/>
+      <c r="C18" s="16" t="n"/>
+      <c r="D18" s="16" t="n"/>
+      <c r="E18" s="16" t="n"/>
+      <c r="F18" s="16" t="n"/>
+      <c r="G18" s="16" t="n"/>
+      <c r="H18" s="16" t="n"/>
+      <c r="I18" s="16" t="n"/>
+      <c r="J18" s="16" t="n"/>
+      <c r="K18" s="16" t="n"/>
+      <c r="L18" s="16" t="n"/>
+      <c r="M18" s="16" t="n"/>
+      <c r="N18" s="16" t="n"/>
+      <c r="O18" s="16" t="n"/>
+      <c r="P18" s="16" t="n"/>
+      <c r="Q18" s="16" t="n"/>
+      <c r="R18" s="16" t="n"/>
+      <c r="S18" s="16" t="n"/>
+      <c r="T18" s="16" t="n"/>
+      <c r="U18" s="16" t="n"/>
+      <c r="V18" s="16" t="n"/>
+      <c r="W18" s="16" t="n"/>
+      <c r="X18" s="16" t="n"/>
+      <c r="Y18" s="16" t="n"/>
+      <c r="Z18" s="16" t="n"/>
+      <c r="AA18" s="16" t="n"/>
+      <c r="AB18" s="16" t="n"/>
+      <c r="AC18" s="16" t="n"/>
+      <c r="AD18" s="16" t="n"/>
+      <c r="AE18" s="16" t="n"/>
+      <c r="AF18" s="16" t="n"/>
+      <c r="AG18" s="16" t="n"/>
+      <c r="AH18" s="16" t="n"/>
+      <c r="AI18" s="16" t="n"/>
+      <c r="AJ18" s="4" t="n"/>
+      <c r="AK18" s="4">
+        <f>COUNTIF($E18:$AI18,"●")</f>
+        <v/>
+      </c>
+      <c r="AL18" s="4">
+        <f>COUNTIF($E18:$AI18,"入")</f>
+        <v/>
+      </c>
+      <c r="AM18" s="4">
+        <f>COUNTIF($E18:$AI18,"外")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="16" t="n"/>
+      <c r="C19" s="16" t="n"/>
+      <c r="D19" s="16" t="n"/>
+      <c r="E19" s="16" t="n"/>
+      <c r="F19" s="16" t="n"/>
+      <c r="G19" s="16" t="n"/>
+      <c r="H19" s="16" t="n"/>
+      <c r="I19" s="16" t="n"/>
+      <c r="J19" s="16" t="n"/>
+      <c r="K19" s="16" t="n"/>
+      <c r="L19" s="16" t="n"/>
+      <c r="M19" s="16" t="n"/>
+      <c r="N19" s="16" t="n"/>
+      <c r="O19" s="16" t="n"/>
+      <c r="P19" s="16" t="n"/>
+      <c r="Q19" s="16" t="n"/>
+      <c r="R19" s="16" t="n"/>
+      <c r="S19" s="16" t="n"/>
+      <c r="T19" s="16" t="n"/>
+      <c r="U19" s="16" t="n"/>
+      <c r="V19" s="16" t="n"/>
+      <c r="W19" s="16" t="n"/>
+      <c r="X19" s="16" t="n"/>
+      <c r="Y19" s="16" t="n"/>
+      <c r="Z19" s="16" t="n"/>
+      <c r="AA19" s="16" t="n"/>
+      <c r="AB19" s="16" t="n"/>
+      <c r="AC19" s="16" t="n"/>
+      <c r="AD19" s="16" t="n"/>
+      <c r="AE19" s="16" t="n"/>
+      <c r="AF19" s="16" t="n"/>
+      <c r="AG19" s="16" t="n"/>
+      <c r="AH19" s="16" t="n"/>
+      <c r="AI19" s="16" t="n"/>
+      <c r="AJ19" s="4" t="n"/>
+      <c r="AK19" s="4">
+        <f>COUNTIF($E19:$AI19,"●")</f>
+        <v/>
+      </c>
+      <c r="AL19" s="4">
+        <f>COUNTIF($E19:$AI19,"入")</f>
+        <v/>
+      </c>
+      <c r="AM19" s="4">
+        <f>COUNTIF($E19:$AI19,"外")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="16" t="n"/>
+      <c r="C20" s="16" t="n"/>
+      <c r="D20" s="16" t="n"/>
+      <c r="E20" s="16" t="n"/>
+      <c r="F20" s="16" t="n"/>
+      <c r="G20" s="16" t="n"/>
+      <c r="H20" s="16" t="n"/>
+      <c r="I20" s="16" t="n"/>
+      <c r="J20" s="16" t="n"/>
+      <c r="K20" s="16" t="n"/>
+      <c r="L20" s="16" t="n"/>
+      <c r="M20" s="16" t="n"/>
+      <c r="N20" s="16" t="n"/>
+      <c r="O20" s="16" t="n"/>
+      <c r="P20" s="16" t="n"/>
+      <c r="Q20" s="16" t="n"/>
+      <c r="R20" s="16" t="n"/>
+      <c r="S20" s="16" t="n"/>
+      <c r="T20" s="16" t="n"/>
+      <c r="U20" s="16" t="n"/>
+      <c r="V20" s="16" t="n"/>
+      <c r="W20" s="16" t="n"/>
+      <c r="X20" s="16" t="n"/>
+      <c r="Y20" s="16" t="n"/>
+      <c r="Z20" s="16" t="n"/>
+      <c r="AA20" s="16" t="n"/>
+      <c r="AB20" s="16" t="n"/>
+      <c r="AC20" s="16" t="n"/>
+      <c r="AD20" s="16" t="n"/>
+      <c r="AE20" s="16" t="n"/>
+      <c r="AF20" s="16" t="n"/>
+      <c r="AG20" s="16" t="n"/>
+      <c r="AH20" s="16" t="n"/>
+      <c r="AI20" s="16" t="n"/>
+      <c r="AJ20" s="4" t="n"/>
+      <c r="AK20" s="4">
+        <f>COUNTIF($E20:$AI20,"●")</f>
+        <v/>
+      </c>
+      <c r="AL20" s="4">
+        <f>COUNTIF($E20:$AI20,"入")</f>
+        <v/>
+      </c>
+      <c r="AM20" s="4">
+        <f>COUNTIF($E20:$AI20,"外")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="16" t="n"/>
+      <c r="C21" s="16" t="n"/>
+      <c r="D21" s="16" t="n"/>
+      <c r="E21" s="16" t="n"/>
+      <c r="F21" s="16" t="n"/>
+      <c r="G21" s="16" t="n"/>
+      <c r="H21" s="16" t="n"/>
+      <c r="I21" s="16" t="n"/>
+      <c r="J21" s="16" t="n"/>
+      <c r="K21" s="16" t="n"/>
+      <c r="L21" s="16" t="n"/>
+      <c r="M21" s="16" t="n"/>
+      <c r="N21" s="16" t="n"/>
+      <c r="O21" s="16" t="n"/>
+      <c r="P21" s="16" t="n"/>
+      <c r="Q21" s="16" t="n"/>
+      <c r="R21" s="16" t="n"/>
+      <c r="S21" s="16" t="n"/>
+      <c r="T21" s="16" t="n"/>
+      <c r="U21" s="16" t="n"/>
+      <c r="V21" s="16" t="n"/>
+      <c r="W21" s="16" t="n"/>
+      <c r="X21" s="16" t="n"/>
+      <c r="Y21" s="16" t="n"/>
+      <c r="Z21" s="16" t="n"/>
+      <c r="AA21" s="16" t="n"/>
+      <c r="AB21" s="16" t="n"/>
+      <c r="AC21" s="16" t="n"/>
+      <c r="AD21" s="16" t="n"/>
+      <c r="AE21" s="16" t="n"/>
+      <c r="AF21" s="16" t="n"/>
+      <c r="AG21" s="16" t="n"/>
+      <c r="AH21" s="16" t="n"/>
+      <c r="AI21" s="16" t="n"/>
+      <c r="AJ21" s="4" t="n"/>
+      <c r="AK21" s="4">
+        <f>COUNTIF($E21:$AI21,"●")</f>
+        <v/>
+      </c>
+      <c r="AL21" s="4">
+        <f>COUNTIF($E21:$AI21,"入")</f>
+        <v/>
+      </c>
+      <c r="AM21" s="4">
+        <f>COUNTIF($E21:$AI21,"外")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="16" t="n"/>
+      <c r="C22" s="16" t="n"/>
+      <c r="D22" s="16" t="n"/>
+      <c r="E22" s="16" t="n"/>
+      <c r="F22" s="16" t="n"/>
+      <c r="G22" s="16" t="n"/>
+      <c r="H22" s="16" t="n"/>
+      <c r="I22" s="16" t="n"/>
+      <c r="J22" s="16" t="n"/>
+      <c r="K22" s="16" t="n"/>
+      <c r="L22" s="16" t="n"/>
+      <c r="M22" s="16" t="n"/>
+      <c r="N22" s="16" t="n"/>
+      <c r="O22" s="16" t="n"/>
+      <c r="P22" s="16" t="n"/>
+      <c r="Q22" s="16" t="n"/>
+      <c r="R22" s="16" t="n"/>
+      <c r="S22" s="16" t="n"/>
+      <c r="T22" s="16" t="n"/>
+      <c r="U22" s="16" t="n"/>
+      <c r="V22" s="16" t="n"/>
+      <c r="W22" s="16" t="n"/>
+      <c r="X22" s="16" t="n"/>
+      <c r="Y22" s="16" t="n"/>
+      <c r="Z22" s="16" t="n"/>
+      <c r="AA22" s="16" t="n"/>
+      <c r="AB22" s="16" t="n"/>
+      <c r="AC22" s="16" t="n"/>
+      <c r="AD22" s="16" t="n"/>
+      <c r="AE22" s="16" t="n"/>
+      <c r="AF22" s="16" t="n"/>
+      <c r="AG22" s="16" t="n"/>
+      <c r="AH22" s="16" t="n"/>
+      <c r="AI22" s="16" t="n"/>
+      <c r="AJ22" s="4" t="n"/>
+      <c r="AK22" s="4">
+        <f>COUNTIF($E22:$AI22,"●")</f>
+        <v/>
+      </c>
+      <c r="AL22" s="4">
+        <f>COUNTIF($E22:$AI22,"入")</f>
+        <v/>
+      </c>
+      <c r="AM22" s="4">
+        <f>COUNTIF($E22:$AI22,"外")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="16" t="n"/>
+      <c r="C23" s="16" t="n"/>
+      <c r="D23" s="16" t="n"/>
+      <c r="E23" s="16" t="n"/>
+      <c r="F23" s="16" t="n"/>
+      <c r="G23" s="16" t="n"/>
+      <c r="H23" s="16" t="n"/>
+      <c r="I23" s="16" t="n"/>
+      <c r="J23" s="16" t="n"/>
+      <c r="K23" s="16" t="n"/>
+      <c r="L23" s="16" t="n"/>
+      <c r="M23" s="16" t="n"/>
+      <c r="N23" s="16" t="n"/>
+      <c r="O23" s="16" t="n"/>
+      <c r="P23" s="16" t="n"/>
+      <c r="Q23" s="16" t="n"/>
+      <c r="R23" s="16" t="n"/>
+      <c r="S23" s="16" t="n"/>
+      <c r="T23" s="16" t="n"/>
+      <c r="U23" s="16" t="n"/>
+      <c r="V23" s="16" t="n"/>
+      <c r="W23" s="16" t="n"/>
+      <c r="X23" s="16" t="n"/>
+      <c r="Y23" s="16" t="n"/>
+      <c r="Z23" s="16" t="n"/>
+      <c r="AA23" s="16" t="n"/>
+      <c r="AB23" s="16" t="n"/>
+      <c r="AC23" s="16" t="n"/>
+      <c r="AD23" s="16" t="n"/>
+      <c r="AE23" s="16" t="n"/>
+      <c r="AF23" s="16" t="n"/>
+      <c r="AG23" s="16" t="n"/>
+      <c r="AH23" s="16" t="n"/>
+      <c r="AI23" s="16" t="n"/>
+      <c r="AJ23" s="4" t="n"/>
+      <c r="AK23" s="4">
+        <f>COUNTIF($E23:$AI23,"●")</f>
+        <v/>
+      </c>
+      <c r="AL23" s="4">
+        <f>COUNTIF($E23:$AI23,"入")</f>
+        <v/>
+      </c>
+      <c r="AM23" s="4">
+        <f>COUNTIF($E23:$AI23,"外")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="16" t="n"/>
+      <c r="C24" s="16" t="n"/>
+      <c r="D24" s="16" t="n"/>
+      <c r="E24" s="16" t="n"/>
+      <c r="F24" s="16" t="n"/>
+      <c r="G24" s="16" t="n"/>
+      <c r="H24" s="16" t="n"/>
+      <c r="I24" s="16" t="n"/>
+      <c r="J24" s="16" t="n"/>
+      <c r="K24" s="16" t="n"/>
+      <c r="L24" s="16" t="n"/>
+      <c r="M24" s="16" t="n"/>
+      <c r="N24" s="16" t="n"/>
+      <c r="O24" s="16" t="n"/>
+      <c r="P24" s="16" t="n"/>
+      <c r="Q24" s="16" t="n"/>
+      <c r="R24" s="16" t="n"/>
+      <c r="S24" s="16" t="n"/>
+      <c r="T24" s="16" t="n"/>
+      <c r="U24" s="16" t="n"/>
+      <c r="V24" s="16" t="n"/>
+      <c r="W24" s="16" t="n"/>
+      <c r="X24" s="16" t="n"/>
+      <c r="Y24" s="16" t="n"/>
+      <c r="Z24" s="16" t="n"/>
+      <c r="AA24" s="16" t="n"/>
+      <c r="AB24" s="16" t="n"/>
+      <c r="AC24" s="16" t="n"/>
+      <c r="AD24" s="16" t="n"/>
+      <c r="AE24" s="16" t="n"/>
+      <c r="AF24" s="16" t="n"/>
+      <c r="AG24" s="16" t="n"/>
+      <c r="AH24" s="16" t="n"/>
+      <c r="AI24" s="16" t="n"/>
+      <c r="AJ24" s="4" t="n"/>
+      <c r="AK24" s="4">
+        <f>COUNTIF($E24:$AI24,"●")</f>
+        <v/>
+      </c>
+      <c r="AL24" s="4">
+        <f>COUNTIF($E24:$AI24,"入")</f>
+        <v/>
+      </c>
+      <c r="AM24" s="4">
+        <f>COUNTIF($E24:$AI24,"外")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="16" t="n"/>
+      <c r="C25" s="16" t="n"/>
+      <c r="D25" s="16" t="n"/>
+      <c r="E25" s="16" t="n"/>
+      <c r="F25" s="16" t="n"/>
+      <c r="G25" s="16" t="n"/>
+      <c r="H25" s="16" t="n"/>
+      <c r="I25" s="16" t="n"/>
+      <c r="J25" s="16" t="n"/>
+      <c r="K25" s="16" t="n"/>
+      <c r="L25" s="16" t="n"/>
+      <c r="M25" s="16" t="n"/>
+      <c r="N25" s="16" t="n"/>
+      <c r="O25" s="16" t="n"/>
+      <c r="P25" s="16" t="n"/>
+      <c r="Q25" s="16" t="n"/>
+      <c r="R25" s="16" t="n"/>
+      <c r="S25" s="16" t="n"/>
+      <c r="T25" s="16" t="n"/>
+      <c r="U25" s="16" t="n"/>
+      <c r="V25" s="16" t="n"/>
+      <c r="W25" s="16" t="n"/>
+      <c r="X25" s="16" t="n"/>
+      <c r="Y25" s="16" t="n"/>
+      <c r="Z25" s="16" t="n"/>
+      <c r="AA25" s="16" t="n"/>
+      <c r="AB25" s="16" t="n"/>
+      <c r="AC25" s="16" t="n"/>
+      <c r="AD25" s="16" t="n"/>
+      <c r="AE25" s="16" t="n"/>
+      <c r="AF25" s="16" t="n"/>
+      <c r="AG25" s="16" t="n"/>
+      <c r="AH25" s="16" t="n"/>
+      <c r="AI25" s="16" t="n"/>
+      <c r="AJ25" s="4" t="n"/>
+      <c r="AK25" s="4">
+        <f>COUNTIF($E25:$AI25,"●")</f>
+        <v/>
+      </c>
+      <c r="AL25" s="4">
+        <f>COUNTIF($E25:$AI25,"入")</f>
+        <v/>
+      </c>
+      <c r="AM25" s="4">
+        <f>COUNTIF($E25:$AI25,"外")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="B26" s="16" t="n"/>
+      <c r="C26" s="16" t="n"/>
+      <c r="D26" s="16" t="n"/>
+      <c r="E26" s="16" t="n"/>
+      <c r="F26" s="16" t="n"/>
+      <c r="G26" s="16" t="n"/>
+      <c r="H26" s="16" t="n"/>
+      <c r="I26" s="16" t="n"/>
+      <c r="J26" s="16" t="n"/>
+      <c r="K26" s="16" t="n"/>
+      <c r="L26" s="16" t="n"/>
+      <c r="M26" s="16" t="n"/>
+      <c r="N26" s="16" t="n"/>
+      <c r="O26" s="16" t="n"/>
+      <c r="P26" s="16" t="n"/>
+      <c r="Q26" s="16" t="n"/>
+      <c r="R26" s="16" t="n"/>
+      <c r="S26" s="16" t="n"/>
+      <c r="T26" s="16" t="n"/>
+      <c r="U26" s="16" t="n"/>
+      <c r="V26" s="16" t="n"/>
+      <c r="W26" s="16" t="n"/>
+      <c r="X26" s="16" t="n"/>
+      <c r="Y26" s="16" t="n"/>
+      <c r="Z26" s="16" t="n"/>
+      <c r="AA26" s="16" t="n"/>
+      <c r="AB26" s="16" t="n"/>
+      <c r="AC26" s="16" t="n"/>
+      <c r="AD26" s="16" t="n"/>
+      <c r="AE26" s="16" t="n"/>
+      <c r="AF26" s="16" t="n"/>
+      <c r="AG26" s="16" t="n"/>
+      <c r="AH26" s="16" t="n"/>
+      <c r="AI26" s="16" t="n"/>
+      <c r="AJ26" s="4" t="n"/>
+      <c r="AK26" s="4">
+        <f>COUNTIF($E26:$AI26,"●")</f>
+        <v/>
+      </c>
+      <c r="AL26" s="4">
+        <f>COUNTIF($E26:$AI26,"入")</f>
+        <v/>
+      </c>
+      <c r="AM26" s="4">
+        <f>COUNTIF($E26:$AI26,"外")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" s="16" t="n"/>
+      <c r="C27" s="16" t="n"/>
+      <c r="D27" s="16" t="n"/>
+      <c r="E27" s="16" t="n"/>
+      <c r="F27" s="16" t="n"/>
+      <c r="G27" s="16" t="n"/>
+      <c r="H27" s="16" t="n"/>
+      <c r="I27" s="16" t="n"/>
+      <c r="J27" s="16" t="n"/>
+      <c r="K27" s="16" t="n"/>
+      <c r="L27" s="16" t="n"/>
+      <c r="M27" s="16" t="n"/>
+      <c r="N27" s="16" t="n"/>
+      <c r="O27" s="16" t="n"/>
+      <c r="P27" s="16" t="n"/>
+      <c r="Q27" s="16" t="n"/>
+      <c r="R27" s="16" t="n"/>
+      <c r="S27" s="16" t="n"/>
+      <c r="T27" s="16" t="n"/>
+      <c r="U27" s="16" t="n"/>
+      <c r="V27" s="16" t="n"/>
+      <c r="W27" s="16" t="n"/>
+      <c r="X27" s="16" t="n"/>
+      <c r="Y27" s="16" t="n"/>
+      <c r="Z27" s="16" t="n"/>
+      <c r="AA27" s="16" t="n"/>
+      <c r="AB27" s="16" t="n"/>
+      <c r="AC27" s="16" t="n"/>
+      <c r="AD27" s="16" t="n"/>
+      <c r="AE27" s="16" t="n"/>
+      <c r="AF27" s="16" t="n"/>
+      <c r="AG27" s="16" t="n"/>
+      <c r="AH27" s="16" t="n"/>
+      <c r="AI27" s="16" t="n"/>
+      <c r="AJ27" s="4" t="n"/>
+      <c r="AK27" s="4">
+        <f>COUNTIF($E27:$AI27,"●")</f>
+        <v/>
+      </c>
+      <c r="AL27" s="4">
+        <f>COUNTIF($E27:$AI27,"入")</f>
+        <v/>
+      </c>
+      <c r="AM27" s="4">
+        <f>COUNTIF($E27:$AI27,"外")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="B28" s="16" t="n"/>
+      <c r="C28" s="16" t="n"/>
+      <c r="D28" s="16" t="n"/>
+      <c r="E28" s="16" t="n"/>
+      <c r="F28" s="16" t="n"/>
+      <c r="G28" s="16" t="n"/>
+      <c r="H28" s="16" t="n"/>
+      <c r="I28" s="16" t="n"/>
+      <c r="J28" s="16" t="n"/>
+      <c r="K28" s="16" t="n"/>
+      <c r="L28" s="16" t="n"/>
+      <c r="M28" s="16" t="n"/>
+      <c r="N28" s="16" t="n"/>
+      <c r="O28" s="16" t="n"/>
+      <c r="P28" s="16" t="n"/>
+      <c r="Q28" s="16" t="n"/>
+      <c r="R28" s="16" t="n"/>
+      <c r="S28" s="16" t="n"/>
+      <c r="T28" s="16" t="n"/>
+      <c r="U28" s="16" t="n"/>
+      <c r="V28" s="16" t="n"/>
+      <c r="W28" s="16" t="n"/>
+      <c r="X28" s="16" t="n"/>
+      <c r="Y28" s="16" t="n"/>
+      <c r="Z28" s="16" t="n"/>
+      <c r="AA28" s="16" t="n"/>
+      <c r="AB28" s="16" t="n"/>
+      <c r="AC28" s="16" t="n"/>
+      <c r="AD28" s="16" t="n"/>
+      <c r="AE28" s="16" t="n"/>
+      <c r="AF28" s="16" t="n"/>
+      <c r="AG28" s="16" t="n"/>
+      <c r="AH28" s="16" t="n"/>
+      <c r="AI28" s="16" t="n"/>
+      <c r="AJ28" s="4" t="n"/>
+      <c r="AK28" s="4">
+        <f>COUNTIF($E28:$AI28,"●")</f>
+        <v/>
+      </c>
+      <c r="AL28" s="4">
+        <f>COUNTIF($E28:$AI28,"入")</f>
+        <v/>
+      </c>
+      <c r="AM28" s="4">
+        <f>COUNTIF($E28:$AI28,"外")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="16" t="n"/>
+      <c r="C29" s="16" t="n"/>
+      <c r="D29" s="16" t="n"/>
+      <c r="E29" s="16" t="n"/>
+      <c r="F29" s="16" t="n"/>
+      <c r="G29" s="16" t="n"/>
+      <c r="H29" s="16" t="n"/>
+      <c r="I29" s="16" t="n"/>
+      <c r="J29" s="16" t="n"/>
+      <c r="K29" s="16" t="n"/>
+      <c r="L29" s="16" t="n"/>
+      <c r="M29" s="16" t="n"/>
+      <c r="N29" s="16" t="n"/>
+      <c r="O29" s="16" t="n"/>
+      <c r="P29" s="16" t="n"/>
+      <c r="Q29" s="16" t="n"/>
+      <c r="R29" s="16" t="n"/>
+      <c r="S29" s="16" t="n"/>
+      <c r="T29" s="16" t="n"/>
+      <c r="U29" s="16" t="n"/>
+      <c r="V29" s="16" t="n"/>
+      <c r="W29" s="16" t="n"/>
+      <c r="X29" s="16" t="n"/>
+      <c r="Y29" s="16" t="n"/>
+      <c r="Z29" s="16" t="n"/>
+      <c r="AA29" s="16" t="n"/>
+      <c r="AB29" s="16" t="n"/>
+      <c r="AC29" s="16" t="n"/>
+      <c r="AD29" s="16" t="n"/>
+      <c r="AE29" s="16" t="n"/>
+      <c r="AF29" s="16" t="n"/>
+      <c r="AG29" s="16" t="n"/>
+      <c r="AH29" s="16" t="n"/>
+      <c r="AI29" s="16" t="n"/>
+      <c r="AJ29" s="4" t="n"/>
+      <c r="AK29" s="4">
+        <f>COUNTIF($E29:$AI29,"●")</f>
+        <v/>
+      </c>
+      <c r="AL29" s="4">
+        <f>COUNTIF($E29:$AI29,"入")</f>
+        <v/>
+      </c>
+      <c r="AM29" s="4">
+        <f>COUNTIF($E29:$AI29,"外")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="B30" s="16" t="n"/>
+      <c r="C30" s="16" t="n"/>
+      <c r="D30" s="16" t="n"/>
+      <c r="E30" s="16" t="n"/>
+      <c r="F30" s="16" t="n"/>
+      <c r="G30" s="16" t="n"/>
+      <c r="H30" s="16" t="n"/>
+      <c r="I30" s="16" t="n"/>
+      <c r="J30" s="16" t="n"/>
+      <c r="K30" s="16" t="n"/>
+      <c r="L30" s="16" t="n"/>
+      <c r="M30" s="16" t="n"/>
+      <c r="N30" s="16" t="n"/>
+      <c r="O30" s="16" t="n"/>
+      <c r="P30" s="16" t="n"/>
+      <c r="Q30" s="16" t="n"/>
+      <c r="R30" s="16" t="n"/>
+      <c r="S30" s="16" t="n"/>
+      <c r="T30" s="16" t="n"/>
+      <c r="U30" s="16" t="n"/>
+      <c r="V30" s="16" t="n"/>
+      <c r="W30" s="16" t="n"/>
+      <c r="X30" s="16" t="n"/>
+      <c r="Y30" s="16" t="n"/>
+      <c r="Z30" s="16" t="n"/>
+      <c r="AA30" s="16" t="n"/>
+      <c r="AB30" s="16" t="n"/>
+      <c r="AC30" s="16" t="n"/>
+      <c r="AD30" s="16" t="n"/>
+      <c r="AE30" s="16" t="n"/>
+      <c r="AF30" s="16" t="n"/>
+      <c r="AG30" s="16" t="n"/>
+      <c r="AH30" s="16" t="n"/>
+      <c r="AI30" s="16" t="n"/>
+      <c r="AJ30" s="4" t="n"/>
+      <c r="AK30" s="4">
+        <f>COUNTIF($E30:$AI30,"●")</f>
+        <v/>
+      </c>
+      <c r="AL30" s="4">
+        <f>COUNTIF($E30:$AI30,"入")</f>
+        <v/>
+      </c>
+      <c r="AM30" s="4">
+        <f>COUNTIF($E30:$AI30,"外")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="B31" s="16" t="n"/>
+      <c r="C31" s="16" t="n"/>
+      <c r="D31" s="16" t="n"/>
+      <c r="E31" s="16" t="n"/>
+      <c r="F31" s="16" t="n"/>
+      <c r="G31" s="16" t="n"/>
+      <c r="H31" s="16" t="n"/>
+      <c r="I31" s="16" t="n"/>
+      <c r="J31" s="16" t="n"/>
+      <c r="K31" s="16" t="n"/>
+      <c r="L31" s="16" t="n"/>
+      <c r="M31" s="16" t="n"/>
+      <c r="N31" s="16" t="n"/>
+      <c r="O31" s="16" t="n"/>
+      <c r="P31" s="16" t="n"/>
+      <c r="Q31" s="16" t="n"/>
+      <c r="R31" s="16" t="n"/>
+      <c r="S31" s="16" t="n"/>
+      <c r="T31" s="16" t="n"/>
+      <c r="U31" s="16" t="n"/>
+      <c r="V31" s="16" t="n"/>
+      <c r="W31" s="16" t="n"/>
+      <c r="X31" s="16" t="n"/>
+      <c r="Y31" s="16" t="n"/>
+      <c r="Z31" s="16" t="n"/>
+      <c r="AA31" s="16" t="n"/>
+      <c r="AB31" s="16" t="n"/>
+      <c r="AC31" s="16" t="n"/>
+      <c r="AD31" s="16" t="n"/>
+      <c r="AE31" s="16" t="n"/>
+      <c r="AF31" s="16" t="n"/>
+      <c r="AG31" s="16" t="n"/>
+      <c r="AH31" s="16" t="n"/>
+      <c r="AI31" s="16" t="n"/>
+      <c r="AJ31" s="4" t="n"/>
+      <c r="AK31" s="4">
+        <f>COUNTIF($E31:$AI31,"●")</f>
+        <v/>
+      </c>
+      <c r="AL31" s="4">
+        <f>COUNTIF($E31:$AI31,"入")</f>
+        <v/>
+      </c>
+      <c r="AM31" s="4">
+        <f>COUNTIF($E31:$AI31,"外")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="B32" s="16" t="n"/>
+      <c r="C32" s="16" t="n"/>
+      <c r="D32" s="16" t="n"/>
+      <c r="E32" s="16" t="n"/>
+      <c r="F32" s="16" t="n"/>
+      <c r="G32" s="16" t="n"/>
+      <c r="H32" s="16" t="n"/>
+      <c r="I32" s="16" t="n"/>
+      <c r="J32" s="16" t="n"/>
+      <c r="K32" s="16" t="n"/>
+      <c r="L32" s="16" t="n"/>
+      <c r="M32" s="16" t="n"/>
+      <c r="N32" s="16" t="n"/>
+      <c r="O32" s="16" t="n"/>
+      <c r="P32" s="16" t="n"/>
+      <c r="Q32" s="16" t="n"/>
+      <c r="R32" s="16" t="n"/>
+      <c r="S32" s="16" t="n"/>
+      <c r="T32" s="16" t="n"/>
+      <c r="U32" s="16" t="n"/>
+      <c r="V32" s="16" t="n"/>
+      <c r="W32" s="16" t="n"/>
+      <c r="X32" s="16" t="n"/>
+      <c r="Y32" s="16" t="n"/>
+      <c r="Z32" s="16" t="n"/>
+      <c r="AA32" s="16" t="n"/>
+      <c r="AB32" s="16" t="n"/>
+      <c r="AC32" s="16" t="n"/>
+      <c r="AD32" s="16" t="n"/>
+      <c r="AE32" s="16" t="n"/>
+      <c r="AF32" s="16" t="n"/>
+      <c r="AG32" s="16" t="n"/>
+      <c r="AH32" s="16" t="n"/>
+      <c r="AI32" s="16" t="n"/>
+      <c r="AJ32" s="4" t="n"/>
+      <c r="AK32" s="4">
+        <f>COUNTIF($E32:$AI32,"●")</f>
+        <v/>
+      </c>
+      <c r="AL32" s="4">
+        <f>COUNTIF($E32:$AI32,"入")</f>
+        <v/>
+      </c>
+      <c r="AM32" s="4">
+        <f>COUNTIF($E32:$AI32,"外")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="B33" s="16" t="n"/>
+      <c r="C33" s="16" t="n"/>
+      <c r="D33" s="16" t="n"/>
+      <c r="E33" s="16" t="n"/>
+      <c r="F33" s="16" t="n"/>
+      <c r="G33" s="16" t="n"/>
+      <c r="H33" s="16" t="n"/>
+      <c r="I33" s="16" t="n"/>
+      <c r="J33" s="16" t="n"/>
+      <c r="K33" s="16" t="n"/>
+      <c r="L33" s="16" t="n"/>
+      <c r="M33" s="16" t="n"/>
+      <c r="N33" s="16" t="n"/>
+      <c r="O33" s="16" t="n"/>
+      <c r="P33" s="16" t="n"/>
+      <c r="Q33" s="16" t="n"/>
+      <c r="R33" s="16" t="n"/>
+      <c r="S33" s="16" t="n"/>
+      <c r="T33" s="16" t="n"/>
+      <c r="U33" s="16" t="n"/>
+      <c r="V33" s="16" t="n"/>
+      <c r="W33" s="16" t="n"/>
+      <c r="X33" s="16" t="n"/>
+      <c r="Y33" s="16" t="n"/>
+      <c r="Z33" s="16" t="n"/>
+      <c r="AA33" s="16" t="n"/>
+      <c r="AB33" s="16" t="n"/>
+      <c r="AC33" s="16" t="n"/>
+      <c r="AD33" s="16" t="n"/>
+      <c r="AE33" s="16" t="n"/>
+      <c r="AF33" s="16" t="n"/>
+      <c r="AG33" s="16" t="n"/>
+      <c r="AH33" s="16" t="n"/>
+      <c r="AI33" s="16" t="n"/>
+      <c r="AJ33" s="4" t="n"/>
+      <c r="AK33" s="4">
+        <f>COUNTIF($E33:$AI33,"●")</f>
+        <v/>
+      </c>
+      <c r="AL33" s="4">
+        <f>COUNTIF($E33:$AI33,"入")</f>
+        <v/>
+      </c>
+      <c r="AM33" s="4">
+        <f>COUNTIF($E33:$AI33,"外")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="B34" s="16" t="n"/>
+      <c r="C34" s="16" t="n"/>
+      <c r="D34" s="16" t="n"/>
+      <c r="E34" s="16" t="n"/>
+      <c r="F34" s="16" t="n"/>
+      <c r="G34" s="16" t="n"/>
+      <c r="H34" s="16" t="n"/>
+      <c r="I34" s="16" t="n"/>
+      <c r="J34" s="16" t="n"/>
+      <c r="K34" s="16" t="n"/>
+      <c r="L34" s="16" t="n"/>
+      <c r="M34" s="16" t="n"/>
+      <c r="N34" s="16" t="n"/>
+      <c r="O34" s="16" t="n"/>
+      <c r="P34" s="16" t="n"/>
+      <c r="Q34" s="16" t="n"/>
+      <c r="R34" s="16" t="n"/>
+      <c r="S34" s="16" t="n"/>
+      <c r="T34" s="16" t="n"/>
+      <c r="U34" s="16" t="n"/>
+      <c r="V34" s="16" t="n"/>
+      <c r="W34" s="16" t="n"/>
+      <c r="X34" s="16" t="n"/>
+      <c r="Y34" s="16" t="n"/>
+      <c r="Z34" s="16" t="n"/>
+      <c r="AA34" s="16" t="n"/>
+      <c r="AB34" s="16" t="n"/>
+      <c r="AC34" s="16" t="n"/>
+      <c r="AD34" s="16" t="n"/>
+      <c r="AE34" s="16" t="n"/>
+      <c r="AF34" s="16" t="n"/>
+      <c r="AG34" s="16" t="n"/>
+      <c r="AH34" s="16" t="n"/>
+      <c r="AI34" s="16" t="n"/>
+      <c r="AJ34" s="4" t="n"/>
+      <c r="AK34" s="4">
+        <f>COUNTIF($E34:$AI34,"●")</f>
+        <v/>
+      </c>
+      <c r="AL34" s="4">
+        <f>COUNTIF($E34:$AI34,"入")</f>
+        <v/>
+      </c>
+      <c r="AM34" s="4">
+        <f>COUNTIF($E34:$AI34,"外")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="25" t="inlineStr">
+        <is>
+          <t>日別稼働数</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="n"/>
+      <c r="D35" s="4" t="n"/>
+      <c r="E35" s="4">
+        <f>COUNTIF(E$5:E$34,"●")</f>
+        <v/>
+      </c>
+      <c r="F35" s="4">
+        <f>COUNTIF(F$5:F$34,"●")</f>
+        <v/>
+      </c>
+      <c r="G35" s="4">
+        <f>COUNTIF(G$5:G$34,"●")</f>
+        <v/>
+      </c>
+      <c r="H35" s="4">
+        <f>COUNTIF(H$5:H$34,"●")</f>
+        <v/>
+      </c>
+      <c r="I35" s="4">
+        <f>COUNTIF(I$5:I$34,"●")</f>
+        <v/>
+      </c>
+      <c r="J35" s="4">
+        <f>COUNTIF(J$5:J$34,"●")</f>
+        <v/>
+      </c>
+      <c r="K35" s="4">
+        <f>COUNTIF(K$5:K$34,"●")</f>
+        <v/>
+      </c>
+      <c r="L35" s="4">
+        <f>COUNTIF(L$5:L$34,"●")</f>
+        <v/>
+      </c>
+      <c r="M35" s="4">
+        <f>COUNTIF(M$5:M$34,"●")</f>
+        <v/>
+      </c>
+      <c r="N35" s="4">
+        <f>COUNTIF(N$5:N$34,"●")</f>
+        <v/>
+      </c>
+      <c r="O35" s="4">
+        <f>COUNTIF(O$5:O$34,"●")</f>
+        <v/>
+      </c>
+      <c r="P35" s="4">
+        <f>COUNTIF(P$5:P$34,"●")</f>
+        <v/>
+      </c>
+      <c r="Q35" s="4">
+        <f>COUNTIF(Q$5:Q$34,"●")</f>
+        <v/>
+      </c>
+      <c r="R35" s="4">
+        <f>COUNTIF(R$5:R$34,"●")</f>
+        <v/>
+      </c>
+      <c r="S35" s="4">
+        <f>COUNTIF(S$5:S$34,"●")</f>
+        <v/>
+      </c>
+      <c r="T35" s="4">
+        <f>COUNTIF(T$5:T$34,"●")</f>
+        <v/>
+      </c>
+      <c r="U35" s="4">
+        <f>COUNTIF(U$5:U$34,"●")</f>
+        <v/>
+      </c>
+      <c r="V35" s="4">
+        <f>COUNTIF(V$5:V$34,"●")</f>
+        <v/>
+      </c>
+      <c r="W35" s="4">
+        <f>COUNTIF(W$5:W$34,"●")</f>
+        <v/>
+      </c>
+      <c r="X35" s="4">
+        <f>COUNTIF(X$5:X$34,"●")</f>
+        <v/>
+      </c>
+      <c r="Y35" s="4">
+        <f>COUNTIF(Y$5:Y$34,"●")</f>
+        <v/>
+      </c>
+      <c r="Z35" s="4">
+        <f>COUNTIF(Z$5:Z$34,"●")</f>
+        <v/>
+      </c>
+      <c r="AA35" s="4">
+        <f>COUNTIF(AA$5:AA$34,"●")</f>
+        <v/>
+      </c>
+      <c r="AB35" s="4">
+        <f>COUNTIF(AB$5:AB$34,"●")</f>
+        <v/>
+      </c>
+      <c r="AC35" s="4">
+        <f>COUNTIF(AC$5:AC$34,"●")</f>
+        <v/>
+      </c>
+      <c r="AD35" s="4">
+        <f>COUNTIF(AD$5:AD$34,"●")</f>
+        <v/>
+      </c>
+      <c r="AE35" s="4">
+        <f>COUNTIF(AE$5:AE$34,"●")</f>
+        <v/>
+      </c>
+      <c r="AF35" s="4">
+        <f>COUNTIF(AF$5:AF$34,"●")</f>
+        <v/>
+      </c>
+      <c r="AG35" s="4">
+        <f>COUNTIF(AG$5:AG$34,"●")</f>
+        <v/>
+      </c>
+      <c r="AH35" s="4">
+        <f>COUNTIF(AH$5:AH$34,"●")</f>
+        <v/>
+      </c>
+      <c r="AI35" s="4">
+        <f>COUNTIF(AI$5:AI$34,"●")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="25" t="inlineStr">
+        <is>
+          <t>日別入院数</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="n"/>
+      <c r="D36" s="4" t="n"/>
+      <c r="E36" s="4">
+        <f>COUNTIF(E$5:E$34,"入")</f>
+        <v/>
+      </c>
+      <c r="F36" s="4">
+        <f>COUNTIF(F$5:F$34,"入")</f>
+        <v/>
+      </c>
+      <c r="G36" s="4">
+        <f>COUNTIF(G$5:G$34,"入")</f>
+        <v/>
+      </c>
+      <c r="H36" s="4">
+        <f>COUNTIF(H$5:H$34,"入")</f>
+        <v/>
+      </c>
+      <c r="I36" s="4">
+        <f>COUNTIF(I$5:I$34,"入")</f>
+        <v/>
+      </c>
+      <c r="J36" s="4">
+        <f>COUNTIF(J$5:J$34,"入")</f>
+        <v/>
+      </c>
+      <c r="K36" s="4">
+        <f>COUNTIF(K$5:K$34,"入")</f>
+        <v/>
+      </c>
+      <c r="L36" s="4">
+        <f>COUNTIF(L$5:L$34,"入")</f>
+        <v/>
+      </c>
+      <c r="M36" s="4">
+        <f>COUNTIF(M$5:M$34,"入")</f>
+        <v/>
+      </c>
+      <c r="N36" s="4">
+        <f>COUNTIF(N$5:N$34,"入")</f>
+        <v/>
+      </c>
+      <c r="O36" s="4">
+        <f>COUNTIF(O$5:O$34,"入")</f>
+        <v/>
+      </c>
+      <c r="P36" s="4">
+        <f>COUNTIF(P$5:P$34,"入")</f>
+        <v/>
+      </c>
+      <c r="Q36" s="4">
+        <f>COUNTIF(Q$5:Q$34,"入")</f>
+        <v/>
+      </c>
+      <c r="R36" s="4">
+        <f>COUNTIF(R$5:R$34,"入")</f>
+        <v/>
+      </c>
+      <c r="S36" s="4">
+        <f>COUNTIF(S$5:S$34,"入")</f>
+        <v/>
+      </c>
+      <c r="T36" s="4">
+        <f>COUNTIF(T$5:T$34,"入")</f>
+        <v/>
+      </c>
+      <c r="U36" s="4">
+        <f>COUNTIF(U$5:U$34,"入")</f>
+        <v/>
+      </c>
+      <c r="V36" s="4">
+        <f>COUNTIF(V$5:V$34,"入")</f>
+        <v/>
+      </c>
+      <c r="W36" s="4">
+        <f>COUNTIF(W$5:W$34,"入")</f>
+        <v/>
+      </c>
+      <c r="X36" s="4">
+        <f>COUNTIF(X$5:X$34,"入")</f>
+        <v/>
+      </c>
+      <c r="Y36" s="4">
+        <f>COUNTIF(Y$5:Y$34,"入")</f>
+        <v/>
+      </c>
+      <c r="Z36" s="4">
+        <f>COUNTIF(Z$5:Z$34,"入")</f>
+        <v/>
+      </c>
+      <c r="AA36" s="4">
+        <f>COUNTIF(AA$5:AA$34,"入")</f>
+        <v/>
+      </c>
+      <c r="AB36" s="4">
+        <f>COUNTIF(AB$5:AB$34,"入")</f>
+        <v/>
+      </c>
+      <c r="AC36" s="4">
+        <f>COUNTIF(AC$5:AC$34,"入")</f>
+        <v/>
+      </c>
+      <c r="AD36" s="4">
+        <f>COUNTIF(AD$5:AD$34,"入")</f>
+        <v/>
+      </c>
+      <c r="AE36" s="4">
+        <f>COUNTIF(AE$5:AE$34,"入")</f>
+        <v/>
+      </c>
+      <c r="AF36" s="4">
+        <f>COUNTIF(AF$5:AF$34,"入")</f>
+        <v/>
+      </c>
+      <c r="AG36" s="4">
+        <f>COUNTIF(AG$5:AG$34,"入")</f>
+        <v/>
+      </c>
+      <c r="AH36" s="4">
+        <f>COUNTIF(AH$5:AH$34,"入")</f>
+        <v/>
+      </c>
+      <c r="AI36" s="4">
+        <f>COUNTIF(AI$5:AI$34,"入")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="25" t="inlineStr">
+        <is>
+          <t>日別外泊数</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="n"/>
+      <c r="D37" s="4" t="n"/>
+      <c r="E37" s="4">
+        <f>COUNTIF(E$5:E$34,"外")</f>
+        <v/>
+      </c>
+      <c r="F37" s="4">
+        <f>COUNTIF(F$5:F$34,"外")</f>
+        <v/>
+      </c>
+      <c r="G37" s="4">
+        <f>COUNTIF(G$5:G$34,"外")</f>
+        <v/>
+      </c>
+      <c r="H37" s="4">
+        <f>COUNTIF(H$5:H$34,"外")</f>
+        <v/>
+      </c>
+      <c r="I37" s="4">
+        <f>COUNTIF(I$5:I$34,"外")</f>
+        <v/>
+      </c>
+      <c r="J37" s="4">
+        <f>COUNTIF(J$5:J$34,"外")</f>
+        <v/>
+      </c>
+      <c r="K37" s="4">
+        <f>COUNTIF(K$5:K$34,"外")</f>
+        <v/>
+      </c>
+      <c r="L37" s="4">
+        <f>COUNTIF(L$5:L$34,"外")</f>
+        <v/>
+      </c>
+      <c r="M37" s="4">
+        <f>COUNTIF(M$5:M$34,"外")</f>
+        <v/>
+      </c>
+      <c r="N37" s="4">
+        <f>COUNTIF(N$5:N$34,"外")</f>
+        <v/>
+      </c>
+      <c r="O37" s="4">
+        <f>COUNTIF(O$5:O$34,"外")</f>
+        <v/>
+      </c>
+      <c r="P37" s="4">
+        <f>COUNTIF(P$5:P$34,"外")</f>
+        <v/>
+      </c>
+      <c r="Q37" s="4">
+        <f>COUNTIF(Q$5:Q$34,"外")</f>
+        <v/>
+      </c>
+      <c r="R37" s="4">
+        <f>COUNTIF(R$5:R$34,"外")</f>
+        <v/>
+      </c>
+      <c r="S37" s="4">
+        <f>COUNTIF(S$5:S$34,"外")</f>
+        <v/>
+      </c>
+      <c r="T37" s="4">
+        <f>COUNTIF(T$5:T$34,"外")</f>
+        <v/>
+      </c>
+      <c r="U37" s="4">
+        <f>COUNTIF(U$5:U$34,"外")</f>
+        <v/>
+      </c>
+      <c r="V37" s="4">
+        <f>COUNTIF(V$5:V$34,"外")</f>
+        <v/>
+      </c>
+      <c r="W37" s="4">
+        <f>COUNTIF(W$5:W$34,"外")</f>
+        <v/>
+      </c>
+      <c r="X37" s="4">
+        <f>COUNTIF(X$5:X$34,"外")</f>
+        <v/>
+      </c>
+      <c r="Y37" s="4">
+        <f>COUNTIF(Y$5:Y$34,"外")</f>
+        <v/>
+      </c>
+      <c r="Z37" s="4">
+        <f>COUNTIF(Z$5:Z$34,"外")</f>
+        <v/>
+      </c>
+      <c r="AA37" s="4">
+        <f>COUNTIF(AA$5:AA$34,"外")</f>
+        <v/>
+      </c>
+      <c r="AB37" s="4">
+        <f>COUNTIF(AB$5:AB$34,"外")</f>
+        <v/>
+      </c>
+      <c r="AC37" s="4">
+        <f>COUNTIF(AC$5:AC$34,"外")</f>
+        <v/>
+      </c>
+      <c r="AD37" s="4">
+        <f>COUNTIF(AD$5:AD$34,"外")</f>
+        <v/>
+      </c>
+      <c r="AE37" s="4">
+        <f>COUNTIF(AE$5:AE$34,"外")</f>
+        <v/>
+      </c>
+      <c r="AF37" s="4">
+        <f>COUNTIF(AF$5:AF$34,"外")</f>
+        <v/>
+      </c>
+      <c r="AG37" s="4">
+        <f>COUNTIF(AG$5:AG$34,"外")</f>
+        <v/>
+      </c>
+      <c r="AH37" s="4">
+        <f>COUNTIF(AH$5:AH$34,"外")</f>
+        <v/>
+      </c>
+      <c r="AI37" s="4">
+        <f>COUNTIF(AI$5:AI$34,"外")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>定員</t>
+        </is>
+      </c>
+      <c r="D39" s="10" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="13" t="inlineStr">
+        <is>
+          <t>※ 定員を入力すると週別稼働率が自動計算されます</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="E5:AI34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"●,入,外"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AY23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="4.2" customWidth="1" min="5" max="5"/>
+    <col width="4.2" customWidth="1" min="6" max="6"/>
+    <col width="4.2" customWidth="1" min="7" max="7"/>
+    <col width="4.2" customWidth="1" min="8" max="8"/>
+    <col width="4.2" customWidth="1" min="9" max="9"/>
+    <col width="4.2" customWidth="1" min="10" max="10"/>
+    <col width="4.2" customWidth="1" min="11" max="11"/>
+    <col width="4.2" customWidth="1" min="12" max="12"/>
+    <col width="4.2" customWidth="1" min="13" max="13"/>
+    <col width="4.2" customWidth="1" min="14" max="14"/>
+    <col width="4.2" customWidth="1" min="15" max="15"/>
+    <col width="4.2" customWidth="1" min="16" max="16"/>
+    <col width="4.2" customWidth="1" min="17" max="17"/>
+    <col width="4.2" customWidth="1" min="18" max="18"/>
+    <col width="4.2" customWidth="1" min="19" max="19"/>
+    <col width="4.2" customWidth="1" min="20" max="20"/>
+    <col width="4.2" customWidth="1" min="21" max="21"/>
+    <col width="4.2" customWidth="1" min="22" max="22"/>
+    <col width="4.2" customWidth="1" min="23" max="23"/>
+    <col width="4.2" customWidth="1" min="24" max="24"/>
+    <col width="4.2" customWidth="1" min="25" max="25"/>
+    <col width="4.2" customWidth="1" min="26" max="26"/>
+    <col width="4.2" customWidth="1" min="27" max="27"/>
+    <col width="4.2" customWidth="1" min="28" max="28"/>
+    <col width="4.2" customWidth="1" min="29" max="29"/>
+    <col width="4.2" customWidth="1" min="30" max="30"/>
+    <col width="4.2" customWidth="1" min="31" max="31"/>
+    <col width="4.2" customWidth="1" min="32" max="32"/>
+    <col width="4.2" customWidth="1" min="33" max="33"/>
+    <col width="4.2" customWidth="1" min="34" max="34"/>
+    <col width="4.2" customWidth="1" min="35" max="35"/>
+    <col width="10" customWidth="1" min="37" max="37"/>
+    <col width="10" customWidth="1" min="38" max="38"/>
+    <col width="13" customWidth="1" min="40" max="40"/>
+    <col width="13" customWidth="1" min="41" max="41"/>
+    <col width="13" customWidth="1" min="42" max="42"/>
+    <col width="13" customWidth="1" min="43" max="43"/>
+    <col width="13" customWidth="1" min="44" max="44"/>
+    <col width="13" customWidth="1" min="45" max="45"/>
+    <col width="7" customWidth="1" min="47" max="47"/>
+    <col width="7" customWidth="1" min="48" max="48"/>
+    <col width="7" customWidth="1" min="49" max="49"/>
+    <col width="7" customWidth="1" min="50" max="50"/>
+    <col width="7" customWidth="1" min="51" max="51"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>短期入所 稼働実績（●=利用 / 予=予約 / ×=キャンセル）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="AU2" s="26" t="inlineStr">
+        <is>
+          <t>▼作業列（週別 利用有無）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>利用者ID</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>利用者名（任意）</t>
+        </is>
+      </c>
+      <c r="D3" s="22" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="E3" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;1,"",DATE(設定対象年,設定対象月,1))</f>
+        <v/>
+      </c>
+      <c r="F3" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;2,"",DATE(設定対象年,設定対象月,2))</f>
+        <v/>
+      </c>
+      <c r="G3" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;3,"",DATE(設定対象年,設定対象月,3))</f>
+        <v/>
+      </c>
+      <c r="H3" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;4,"",DATE(設定対象年,設定対象月,4))</f>
+        <v/>
+      </c>
+      <c r="I3" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;5,"",DATE(設定対象年,設定対象月,5))</f>
+        <v/>
+      </c>
+      <c r="J3" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;6,"",DATE(設定対象年,設定対象月,6))</f>
+        <v/>
+      </c>
+      <c r="K3" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;7,"",DATE(設定対象年,設定対象月,7))</f>
+        <v/>
+      </c>
+      <c r="L3" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;8,"",DATE(設定対象年,設定対象月,8))</f>
+        <v/>
+      </c>
+      <c r="M3" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;9,"",DATE(設定対象年,設定対象月,9))</f>
+        <v/>
+      </c>
+      <c r="N3" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;10,"",DATE(設定対象年,設定対象月,10))</f>
+        <v/>
+      </c>
+      <c r="O3" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;11,"",DATE(設定対象年,設定対象月,11))</f>
+        <v/>
+      </c>
+      <c r="P3" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;12,"",DATE(設定対象年,設定対象月,12))</f>
+        <v/>
+      </c>
+      <c r="Q3" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;13,"",DATE(設定対象年,設定対象月,13))</f>
+        <v/>
+      </c>
+      <c r="R3" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;14,"",DATE(設定対象年,設定対象月,14))</f>
+        <v/>
+      </c>
+      <c r="S3" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;15,"",DATE(設定対象年,設定対象月,15))</f>
+        <v/>
+      </c>
+      <c r="T3" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;16,"",DATE(設定対象年,設定対象月,16))</f>
+        <v/>
+      </c>
+      <c r="U3" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;17,"",DATE(設定対象年,設定対象月,17))</f>
+        <v/>
+      </c>
+      <c r="V3" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;18,"",DATE(設定対象年,設定対象月,18))</f>
+        <v/>
+      </c>
+      <c r="W3" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;19,"",DATE(設定対象年,設定対象月,19))</f>
+        <v/>
+      </c>
+      <c r="X3" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;20,"",DATE(設定対象年,設定対象月,20))</f>
+        <v/>
+      </c>
+      <c r="Y3" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;21,"",DATE(設定対象年,設定対象月,21))</f>
+        <v/>
+      </c>
+      <c r="Z3" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;22,"",DATE(設定対象年,設定対象月,22))</f>
+        <v/>
+      </c>
+      <c r="AA3" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;23,"",DATE(設定対象年,設定対象月,23))</f>
+        <v/>
+      </c>
+      <c r="AB3" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;24,"",DATE(設定対象年,設定対象月,24))</f>
+        <v/>
+      </c>
+      <c r="AC3" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;25,"",DATE(設定対象年,設定対象月,25))</f>
+        <v/>
+      </c>
+      <c r="AD3" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;26,"",DATE(設定対象年,設定対象月,26))</f>
+        <v/>
+      </c>
+      <c r="AE3" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;27,"",DATE(設定対象年,設定対象月,27))</f>
+        <v/>
+      </c>
+      <c r="AF3" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;28,"",DATE(設定対象年,設定対象月,28))</f>
+        <v/>
+      </c>
+      <c r="AG3" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;29,"",DATE(設定対象年,設定対象月,29))</f>
+        <v/>
+      </c>
+      <c r="AH3" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;30,"",DATE(設定対象年,設定対象月,30))</f>
+        <v/>
+      </c>
+      <c r="AI3" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;31,"",DATE(設定対象年,設定対象月,31))</f>
+        <v/>
+      </c>
+      <c r="AJ3" s="4" t="n"/>
+      <c r="AK3" s="4" t="n"/>
+      <c r="AL3" s="4" t="n"/>
+      <c r="AN3" s="5" t="inlineStr">
+        <is>
+          <t>週</t>
+        </is>
+      </c>
+      <c r="AO3" s="5" t="inlineStr">
+        <is>
+          <t>日数</t>
+        </is>
+      </c>
+      <c r="AP3" s="5" t="inlineStr">
+        <is>
+          <t>稼働回数</t>
+        </is>
+      </c>
+      <c r="AQ3" s="5" t="inlineStr">
+        <is>
+          <t>稼働率</t>
+        </is>
+      </c>
+      <c r="AR3" s="5" t="inlineStr">
+        <is>
+          <t>キャンセル</t>
+        </is>
+      </c>
+      <c r="AS3" s="5" t="inlineStr">
+        <is>
+          <t>利用人数</t>
+        </is>
+      </c>
+      <c r="AU3" s="26" t="inlineStr">
+        <is>
+          <t>第1週</t>
+        </is>
+      </c>
+      <c r="AV3" s="26" t="inlineStr">
+        <is>
+          <t>第2週</t>
+        </is>
+      </c>
+      <c r="AW3" s="26" t="inlineStr">
+        <is>
+          <t>第3週</t>
+        </is>
+      </c>
+      <c r="AX3" s="26" t="inlineStr">
+        <is>
+          <t>第4週</t>
+        </is>
+      </c>
+      <c r="AY3" s="26" t="inlineStr">
+        <is>
+          <t>第5週</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="n"/>
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="24" t="inlineStr">
+        <is>
+          <t>週</t>
+        </is>
+      </c>
+      <c r="E4" s="24">
+        <f>IF(E3="","","第"&amp;ROUNDUP(1/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="F4" s="24">
+        <f>IF(F3="","","第"&amp;ROUNDUP(2/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="G4" s="24">
+        <f>IF(G3="","","第"&amp;ROUNDUP(3/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="H4" s="24">
+        <f>IF(H3="","","第"&amp;ROUNDUP(4/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="I4" s="24">
+        <f>IF(I3="","","第"&amp;ROUNDUP(5/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="J4" s="24">
+        <f>IF(J3="","","第"&amp;ROUNDUP(6/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="K4" s="24">
+        <f>IF(K3="","","第"&amp;ROUNDUP(7/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="L4" s="24">
+        <f>IF(L3="","","第"&amp;ROUNDUP(8/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="M4" s="24">
+        <f>IF(M3="","","第"&amp;ROUNDUP(9/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="N4" s="24">
+        <f>IF(N3="","","第"&amp;ROUNDUP(10/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="O4" s="24">
+        <f>IF(O3="","","第"&amp;ROUNDUP(11/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="P4" s="24">
+        <f>IF(P3="","","第"&amp;ROUNDUP(12/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="Q4" s="24">
+        <f>IF(Q3="","","第"&amp;ROUNDUP(13/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="R4" s="24">
+        <f>IF(R3="","","第"&amp;ROUNDUP(14/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="S4" s="24">
+        <f>IF(S3="","","第"&amp;ROUNDUP(15/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="T4" s="24">
+        <f>IF(T3="","","第"&amp;ROUNDUP(16/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="U4" s="24">
+        <f>IF(U3="","","第"&amp;ROUNDUP(17/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="V4" s="24">
+        <f>IF(V3="","","第"&amp;ROUNDUP(18/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="W4" s="24">
+        <f>IF(W3="","","第"&amp;ROUNDUP(19/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="X4" s="24">
+        <f>IF(X3="","","第"&amp;ROUNDUP(20/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="Y4" s="24">
+        <f>IF(Y3="","","第"&amp;ROUNDUP(21/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="Z4" s="24">
+        <f>IF(Z3="","","第"&amp;ROUNDUP(22/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="AA4" s="24">
+        <f>IF(AA3="","","第"&amp;ROUNDUP(23/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="AB4" s="24">
+        <f>IF(AB3="","","第"&amp;ROUNDUP(24/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="AC4" s="24">
+        <f>IF(AC3="","","第"&amp;ROUNDUP(25/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="AD4" s="24">
+        <f>IF(AD3="","","第"&amp;ROUNDUP(26/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="AE4" s="24">
+        <f>IF(AE3="","","第"&amp;ROUNDUP(27/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="AF4" s="24">
+        <f>IF(AF3="","","第"&amp;ROUNDUP(28/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="AG4" s="24">
+        <f>IF(AG3="","","第"&amp;ROUNDUP(29/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="AH4" s="24">
+        <f>IF(AH3="","","第"&amp;ROUNDUP(30/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="AI4" s="24">
+        <f>IF(AI3="","","第"&amp;ROUNDUP(31/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="AJ4" s="4" t="n"/>
+      <c r="AK4" s="5" t="inlineStr">
+        <is>
+          <t>利用回数</t>
+        </is>
+      </c>
+      <c r="AL4" s="5" t="inlineStr">
+        <is>
+          <t>キャンセル</t>
+        </is>
+      </c>
+      <c r="AN4" s="4" t="inlineStr">
+        <is>
+          <t>第1週</t>
+        </is>
+      </c>
+      <c r="AO4" s="4">
+        <f>COUNTIF($E$4:$AI$4,$AN4)</f>
+        <v/>
+      </c>
+      <c r="AP4" s="4">
+        <f>SUMPRODUCT(($E$4:$AI$4=$AN4)*$E$20:$AI$20)</f>
+        <v/>
+      </c>
+      <c r="AQ4" s="17">
+        <f>IFERROR($AP4/($AO4*$D$23),"")</f>
+        <v/>
+      </c>
+      <c r="AR4" s="4">
+        <f>SUMPRODUCT(($E$4:$AI$4=$AN4)*$E$21:$AI$21)</f>
+        <v/>
+      </c>
+      <c r="AS4" s="4">
+        <f>SUM($AU$5:$AU$19)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="16" t="n"/>
+      <c r="C5" s="16" t="n"/>
+      <c r="D5" s="16" t="n"/>
+      <c r="E5" s="16" t="n"/>
+      <c r="F5" s="16" t="n"/>
+      <c r="G5" s="16" t="n"/>
+      <c r="H5" s="16" t="n"/>
+      <c r="I5" s="16" t="n"/>
+      <c r="J5" s="16" t="n"/>
+      <c r="K5" s="16" t="n"/>
+      <c r="L5" s="16" t="n"/>
+      <c r="M5" s="16" t="n"/>
+      <c r="N5" s="16" t="n"/>
+      <c r="O5" s="16" t="n"/>
+      <c r="P5" s="16" t="n"/>
+      <c r="Q5" s="16" t="n"/>
+      <c r="R5" s="16" t="n"/>
+      <c r="S5" s="16" t="n"/>
+      <c r="T5" s="16" t="n"/>
+      <c r="U5" s="16" t="n"/>
+      <c r="V5" s="16" t="n"/>
+      <c r="W5" s="16" t="n"/>
+      <c r="X5" s="16" t="n"/>
+      <c r="Y5" s="16" t="n"/>
+      <c r="Z5" s="16" t="n"/>
+      <c r="AA5" s="16" t="n"/>
+      <c r="AB5" s="16" t="n"/>
+      <c r="AC5" s="16" t="n"/>
+      <c r="AD5" s="16" t="n"/>
+      <c r="AE5" s="16" t="n"/>
+      <c r="AF5" s="16" t="n"/>
+      <c r="AG5" s="16" t="n"/>
+      <c r="AH5" s="16" t="n"/>
+      <c r="AI5" s="16" t="n"/>
+      <c r="AJ5" s="4" t="n"/>
+      <c r="AK5" s="4">
+        <f>COUNTIF($E5:$AI5,"●")</f>
+        <v/>
+      </c>
+      <c r="AL5" s="4">
+        <f>COUNTIF($E5:$AI5,"×")</f>
+        <v/>
+      </c>
+      <c r="AN5" s="4" t="inlineStr">
+        <is>
+          <t>第2週</t>
+        </is>
+      </c>
+      <c r="AO5" s="4">
+        <f>COUNTIF($E$4:$AI$4,$AN5)</f>
+        <v/>
+      </c>
+      <c r="AP5" s="4">
+        <f>SUMPRODUCT(($E$4:$AI$4=$AN5)*$E$20:$AI$20)</f>
+        <v/>
+      </c>
+      <c r="AQ5" s="17">
+        <f>IFERROR($AP5/($AO5*$D$23),"")</f>
+        <v/>
+      </c>
+      <c r="AR5" s="4">
+        <f>SUMPRODUCT(($E$4:$AI$4=$AN5)*$E$21:$AI$21)</f>
+        <v/>
+      </c>
+      <c r="AS5" s="4">
+        <f>SUM($AV$5:$AV$19)</f>
+        <v/>
+      </c>
+      <c r="AU5">
+        <f>IF(SUMPRODUCT(($E$4:$AI$4=$AN4)*($E5:$AI5="●"))&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="AV5">
+        <f>IF(SUMPRODUCT(($E$4:$AI$4=$AN5)*($E5:$AI5="●"))&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="AW5">
+        <f>IF(SUMPRODUCT(($E$4:$AI$4=$AN6)*($E5:$AI5="●"))&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="AX5">
+        <f>IF(SUMPRODUCT(($E$4:$AI$4=$AN7)*($E5:$AI5="●"))&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="AY5">
+        <f>IF(SUMPRODUCT(($E$4:$AI$4=$AN8)*($E5:$AI5="●"))&gt;0,1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="16" t="n"/>
+      <c r="C6" s="16" t="n"/>
+      <c r="D6" s="16" t="n"/>
+      <c r="E6" s="16" t="n"/>
+      <c r="F6" s="16" t="n"/>
+      <c r="G6" s="16" t="n"/>
+      <c r="H6" s="16" t="n"/>
+      <c r="I6" s="16" t="n"/>
+      <c r="J6" s="16" t="n"/>
+      <c r="K6" s="16" t="n"/>
+      <c r="L6" s="16" t="n"/>
+      <c r="M6" s="16" t="n"/>
+      <c r="N6" s="16" t="n"/>
+      <c r="O6" s="16" t="n"/>
+      <c r="P6" s="16" t="n"/>
+      <c r="Q6" s="16" t="n"/>
+      <c r="R6" s="16" t="n"/>
+      <c r="S6" s="16" t="n"/>
+      <c r="T6" s="16" t="n"/>
+      <c r="U6" s="16" t="n"/>
+      <c r="V6" s="16" t="n"/>
+      <c r="W6" s="16" t="n"/>
+      <c r="X6" s="16" t="n"/>
+      <c r="Y6" s="16" t="n"/>
+      <c r="Z6" s="16" t="n"/>
+      <c r="AA6" s="16" t="n"/>
+      <c r="AB6" s="16" t="n"/>
+      <c r="AC6" s="16" t="n"/>
+      <c r="AD6" s="16" t="n"/>
+      <c r="AE6" s="16" t="n"/>
+      <c r="AF6" s="16" t="n"/>
+      <c r="AG6" s="16" t="n"/>
+      <c r="AH6" s="16" t="n"/>
+      <c r="AI6" s="16" t="n"/>
+      <c r="AJ6" s="4" t="n"/>
+      <c r="AK6" s="4">
+        <f>COUNTIF($E6:$AI6,"●")</f>
+        <v/>
+      </c>
+      <c r="AL6" s="4">
+        <f>COUNTIF($E6:$AI6,"×")</f>
+        <v/>
+      </c>
+      <c r="AN6" s="4" t="inlineStr">
+        <is>
+          <t>第3週</t>
+        </is>
+      </c>
+      <c r="AO6" s="4">
+        <f>COUNTIF($E$4:$AI$4,$AN6)</f>
+        <v/>
+      </c>
+      <c r="AP6" s="4">
+        <f>SUMPRODUCT(($E$4:$AI$4=$AN6)*$E$20:$AI$20)</f>
+        <v/>
+      </c>
+      <c r="AQ6" s="17">
+        <f>IFERROR($AP6/($AO6*$D$23),"")</f>
+        <v/>
+      </c>
+      <c r="AR6" s="4">
+        <f>SUMPRODUCT(($E$4:$AI$4=$AN6)*$E$21:$AI$21)</f>
+        <v/>
+      </c>
+      <c r="AS6" s="4">
+        <f>SUM($AW$5:$AW$19)</f>
+        <v/>
+      </c>
+      <c r="AU6">
+        <f>IF(SUMPRODUCT(($E$4:$AI$4=$AN4)*($E6:$AI6="●"))&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="AV6">
+        <f>IF(SUMPRODUCT(($E$4:$AI$4=$AN5)*($E6:$AI6="●"))&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="AW6">
+        <f>IF(SUMPRODUCT(($E$4:$AI$4=$AN6)*($E6:$AI6="●"))&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="AX6">
+        <f>IF(SUMPRODUCT(($E$4:$AI$4=$AN7)*($E6:$AI6="●"))&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="AY6">
+        <f>IF(SUMPRODUCT(($E$4:$AI$4=$AN8)*($E6:$AI6="●"))&gt;0,1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="16" t="n"/>
+      <c r="C7" s="16" t="n"/>
+      <c r="D7" s="16" t="n"/>
+      <c r="E7" s="16" t="n"/>
+      <c r="F7" s="16" t="n"/>
+      <c r="G7" s="16" t="n"/>
+      <c r="H7" s="16" t="n"/>
+      <c r="I7" s="16" t="n"/>
+      <c r="J7" s="16" t="n"/>
+      <c r="K7" s="16" t="n"/>
+      <c r="L7" s="16" t="n"/>
+      <c r="M7" s="16" t="n"/>
+      <c r="N7" s="16" t="n"/>
+      <c r="O7" s="16" t="n"/>
+      <c r="P7" s="16" t="n"/>
+      <c r="Q7" s="16" t="n"/>
+      <c r="R7" s="16" t="n"/>
+      <c r="S7" s="16" t="n"/>
+      <c r="T7" s="16" t="n"/>
+      <c r="U7" s="16" t="n"/>
+      <c r="V7" s="16" t="n"/>
+      <c r="W7" s="16" t="n"/>
+      <c r="X7" s="16" t="n"/>
+      <c r="Y7" s="16" t="n"/>
+      <c r="Z7" s="16" t="n"/>
+      <c r="AA7" s="16" t="n"/>
+      <c r="AB7" s="16" t="n"/>
+      <c r="AC7" s="16" t="n"/>
+      <c r="AD7" s="16" t="n"/>
+      <c r="AE7" s="16" t="n"/>
+      <c r="AF7" s="16" t="n"/>
+      <c r="AG7" s="16" t="n"/>
+      <c r="AH7" s="16" t="n"/>
+      <c r="AI7" s="16" t="n"/>
+      <c r="AJ7" s="4" t="n"/>
+      <c r="AK7" s="4">
+        <f>COUNTIF($E7:$AI7,"●")</f>
+        <v/>
+      </c>
+      <c r="AL7" s="4">
+        <f>COUNTIF($E7:$AI7,"×")</f>
+        <v/>
+      </c>
+      <c r="AN7" s="4" t="inlineStr">
+        <is>
+          <t>第4週</t>
+        </is>
+      </c>
+      <c r="AO7" s="4">
+        <f>COUNTIF($E$4:$AI$4,$AN7)</f>
+        <v/>
+      </c>
+      <c r="AP7" s="4">
+        <f>SUMPRODUCT(($E$4:$AI$4=$AN7)*$E$20:$AI$20)</f>
+        <v/>
+      </c>
+      <c r="AQ7" s="17">
+        <f>IFERROR($AP7/($AO7*$D$23),"")</f>
+        <v/>
+      </c>
+      <c r="AR7" s="4">
+        <f>SUMPRODUCT(($E$4:$AI$4=$AN7)*$E$21:$AI$21)</f>
+        <v/>
+      </c>
+      <c r="AS7" s="4">
+        <f>SUM($AX$5:$AX$19)</f>
+        <v/>
+      </c>
+      <c r="AU7">
+        <f>IF(SUMPRODUCT(($E$4:$AI$4=$AN4)*($E7:$AI7="●"))&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="AV7">
+        <f>IF(SUMPRODUCT(($E$4:$AI$4=$AN5)*($E7:$AI7="●"))&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="AW7">
+        <f>IF(SUMPRODUCT(($E$4:$AI$4=$AN6)*($E7:$AI7="●"))&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="AX7">
+        <f>IF(SUMPRODUCT(($E$4:$AI$4=$AN7)*($E7:$AI7="●"))&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="AY7">
+        <f>IF(SUMPRODUCT(($E$4:$AI$4=$AN8)*($E7:$AI7="●"))&gt;0,1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="16" t="n"/>
+      <c r="C8" s="16" t="n"/>
+      <c r="D8" s="16" t="n"/>
+      <c r="E8" s="16" t="n"/>
+      <c r="F8" s="16" t="n"/>
+      <c r="G8" s="16" t="n"/>
+      <c r="H8" s="16" t="n"/>
+      <c r="I8" s="16" t="n"/>
+      <c r="J8" s="16" t="n"/>
+      <c r="K8" s="16" t="n"/>
+      <c r="L8" s="16" t="n"/>
+      <c r="M8" s="16" t="n"/>
+      <c r="N8" s="16" t="n"/>
+      <c r="O8" s="16" t="n"/>
+      <c r="P8" s="16" t="n"/>
+      <c r="Q8" s="16" t="n"/>
+      <c r="R8" s="16" t="n"/>
+      <c r="S8" s="16" t="n"/>
+      <c r="T8" s="16" t="n"/>
+      <c r="U8" s="16" t="n"/>
+      <c r="V8" s="16" t="n"/>
+      <c r="W8" s="16" t="n"/>
+      <c r="X8" s="16" t="n"/>
+      <c r="Y8" s="16" t="n"/>
+      <c r="Z8" s="16" t="n"/>
+      <c r="AA8" s="16" t="n"/>
+      <c r="AB8" s="16" t="n"/>
+      <c r="AC8" s="16" t="n"/>
+      <c r="AD8" s="16" t="n"/>
+      <c r="AE8" s="16" t="n"/>
+      <c r="AF8" s="16" t="n"/>
+      <c r="AG8" s="16" t="n"/>
+      <c r="AH8" s="16" t="n"/>
+      <c r="AI8" s="16" t="n"/>
+      <c r="AJ8" s="4" t="n"/>
+      <c r="AK8" s="4">
+        <f>COUNTIF($E8:$AI8,"●")</f>
+        <v/>
+      </c>
+      <c r="AL8" s="4">
+        <f>COUNTIF($E8:$AI8,"×")</f>
+        <v/>
+      </c>
+      <c r="AN8" s="4" t="inlineStr">
+        <is>
+          <t>第5週</t>
+        </is>
+      </c>
+      <c r="AO8" s="4">
+        <f>COUNTIF($E$4:$AI$4,$AN8)</f>
+        <v/>
+      </c>
+      <c r="AP8" s="4">
+        <f>SUMPRODUCT(($E$4:$AI$4=$AN8)*$E$20:$AI$20)</f>
+        <v/>
+      </c>
+      <c r="AQ8" s="17">
+        <f>IFERROR($AP8/($AO8*$D$23),"")</f>
+        <v/>
+      </c>
+      <c r="AR8" s="4">
+        <f>SUMPRODUCT(($E$4:$AI$4=$AN8)*$E$21:$AI$21)</f>
+        <v/>
+      </c>
+      <c r="AS8" s="4">
+        <f>SUM($AY$5:$AY$19)</f>
+        <v/>
+      </c>
+      <c r="AU8">
+        <f>IF(SUMPRODUCT(($E$4:$AI$4=$AN4)*($E8:$AI8="●"))&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="AV8">
+        <f>IF(SUMPRODUCT(($E$4:$AI$4=$AN5)*($E8:$AI8="●"))&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="AW8">
+        <f>IF(SUMPRODUCT(($E$4:$AI$4=$AN6)*($E8:$AI8="●"))&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="AX8">
+        <f>IF(SUMPRODUCT(($E$4:$AI$4=$AN7)*($E8:$AI8="●"))&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="AY8">
+        <f>IF(SUMPRODUCT(($E$4:$AI$4=$AN8)*($E8:$AI8="●"))&gt;0,1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="16" t="n"/>
+      <c r="C9" s="16" t="n"/>
+      <c r="D9" s="16" t="n"/>
+      <c r="E9" s="16" t="n"/>
+      <c r="F9" s="16" t="n"/>
+      <c r="G9" s="16" t="n"/>
+      <c r="H9" s="16" t="n"/>
+      <c r="I9" s="16" t="n"/>
+      <c r="J9" s="16" t="n"/>
+      <c r="K9" s="16" t="n"/>
+      <c r="L9" s="16" t="n"/>
+      <c r="M9" s="16" t="n"/>
+      <c r="N9" s="16" t="n"/>
+      <c r="O9" s="16" t="n"/>
+      <c r="P9" s="16" t="n"/>
+      <c r="Q9" s="16" t="n"/>
+      <c r="R9" s="16" t="n"/>
+      <c r="S9" s="16" t="n"/>
+      <c r="T9" s="16" t="n"/>
+      <c r="U9" s="16" t="n"/>
+      <c r="V9" s="16" t="n"/>
+      <c r="W9" s="16" t="n"/>
+      <c r="X9" s="16" t="n"/>
+      <c r="Y9" s="16" t="n"/>
+      <c r="Z9" s="16" t="n"/>
+      <c r="AA9" s="16" t="n"/>
+      <c r="AB9" s="16" t="n"/>
+      <c r="AC9" s="16" t="n"/>
+      <c r="AD9" s="16" t="n"/>
+      <c r="AE9" s="16" t="n"/>
+      <c r="AF9" s="16" t="n"/>
+      <c r="AG9" s="16" t="n"/>
+      <c r="AH9" s="16" t="n"/>
+      <c r="AI9" s="16" t="n"/>
+      <c r="AJ9" s="4" t="n"/>
+      <c r="AK9" s="4">
+        <f>COUNTIF($E9:$AI9,"●")</f>
+        <v/>
+      </c>
+      <c r="AL9" s="4">
+        <f>COUNTIF($E9:$AI9,"×")</f>
+        <v/>
+      </c>
+      <c r="AU9">
+        <f>IF(SUMPRODUCT(($E$4:$AI$4=$AN4)*($E9:$AI9="●"))&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="AV9">
+        <f>IF(SUMPRODUCT(($E$4:$AI$4=$AN5)*($E9:$AI9="●"))&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="AW9">
+        <f>IF(SUMPRODUCT(($E$4:$AI$4=$AN6)*($E9:$AI9="●"))&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="AX9">
+        <f>IF(SUMPRODUCT(($E$4:$AI$4=$AN7)*($E9:$AI9="●"))&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="AY9">
+        <f>IF(SUMPRODUCT(($E$4:$AI$4=$AN8)*($E9:$AI9="●"))&gt;0,1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="16" t="n"/>
+      <c r="C10" s="16" t="n"/>
+      <c r="D10" s="16" t="n"/>
+      <c r="E10" s="16" t="n"/>
+      <c r="F10" s="16" t="n"/>
+      <c r="G10" s="16" t="n"/>
+      <c r="H10" s="16" t="n"/>
+      <c r="I10" s="16" t="n"/>
+      <c r="J10" s="16" t="n"/>
+      <c r="K10" s="16" t="n"/>
+      <c r="L10" s="16" t="n"/>
+      <c r="M10" s="16" t="n"/>
+      <c r="N10" s="16" t="n"/>
+      <c r="O10" s="16" t="n"/>
+      <c r="P10" s="16" t="n"/>
+      <c r="Q10" s="16" t="n"/>
+      <c r="R10" s="16" t="n"/>
+      <c r="S10" s="16" t="n"/>
+      <c r="T10" s="16" t="n"/>
+      <c r="U10" s="16" t="n"/>
+      <c r="V10" s="16" t="n"/>
+      <c r="W10" s="16" t="n"/>
+      <c r="X10" s="16" t="n"/>
+      <c r="Y10" s="16" t="n"/>
+      <c r="Z10" s="16" t="n"/>
+      <c r="AA10" s="16" t="n"/>
+      <c r="AB10" s="16" t="n"/>
+      <c r="AC10" s="16" t="n"/>
+      <c r="AD10" s="16" t="n"/>
+      <c r="AE10" s="16" t="n"/>
+      <c r="AF10" s="16" t="n"/>
+      <c r="AG10" s="16" t="n"/>
+      <c r="AH10" s="16" t="n"/>
+      <c r="AI10" s="16" t="n"/>
+      <c r="AJ10" s="4" t="n"/>
+      <c r="AK10" s="4">
+        <f>COUNTIF($E10:$AI10,"●")</f>
+        <v/>
+      </c>
+      <c r="AL10" s="4">
+        <f>COUNTIF($E10:$AI10,"×")</f>
+        <v/>
+      </c>
+      <c r="AU10">
+        <f>IF(SUMPRODUCT(($E$4:$AI$4=$AN4)*($E10:$AI10="●"))&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="AV10">
+        <f>IF(SUMPRODUCT(($E$4:$AI$4=$AN5)*($E10:$AI10="●"))&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="AW10">
+        <f>IF(SUMPRODUCT(($E$4:$AI$4=$AN6)*($E10:$AI10="●"))&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="AX10">
+        <f>IF(SUMPRODUCT(($E$4:$AI$4=$AN7)*($E10:$AI10="●"))&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="AY10">
+        <f>IF(SUMPRODUCT(($E$4:$AI$4=$AN8)*($E10:$AI10="●"))&gt;0,1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="16" t="n"/>
+      <c r="C11" s="16" t="n"/>
+      <c r="D11" s="16" t="n"/>
+      <c r="E11" s="16" t="n"/>
+      <c r="F11" s="16" t="n"/>
+      <c r="G11" s="16" t="n"/>
+      <c r="H11" s="16" t="n"/>
+      <c r="I11" s="16" t="n"/>
+      <c r="J11" s="16" t="n"/>
+      <c r="K11" s="16" t="n"/>
+      <c r="L11" s="16" t="n"/>
+      <c r="M11" s="16" t="n"/>
+      <c r="N11" s="16" t="n"/>
+      <c r="O11" s="16" t="n"/>
+      <c r="P11" s="16" t="n"/>
+      <c r="Q11" s="16" t="n"/>
+      <c r="R11" s="16" t="n"/>
+      <c r="S11" s="16" t="n"/>
+      <c r="T11" s="16" t="n"/>
+      <c r="U11" s="16" t="n"/>
+      <c r="V11" s="16" t="n"/>
+      <c r="W11" s="16" t="n"/>
+      <c r="X11" s="16" t="n"/>
+      <c r="Y11" s="16" t="n"/>
+      <c r="Z11" s="16" t="n"/>
+      <c r="AA11" s="16" t="n"/>
+      <c r="AB11" s="16" t="n"/>
+      <c r="AC11" s="16" t="n"/>
+      <c r="AD11" s="16" t="n"/>
+      <c r="AE11" s="16" t="n"/>
+      <c r="AF11" s="16" t="n"/>
+      <c r="AG11" s="16" t="n"/>
+      <c r="AH11" s="16" t="n"/>
+      <c r="AI11" s="16" t="n"/>
+      <c r="AJ11" s="4" t="n"/>
+      <c r="AK11" s="4">
+        <f>COUNTIF($E11:$AI11,"●")</f>
+        <v/>
+      </c>
+      <c r="AL11" s="4">
+        <f>COUNTIF($E11:$AI11,"×")</f>
+        <v/>
+      </c>
+      <c r="AU11">
+        <f>IF(SUMPRODUCT(($E$4:$AI$4=$AN4)*($E11:$AI11="●"))&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="AV11">
+        <f>IF(SUMPRODUCT(($E$4:$AI$4=$AN5)*($E11:$AI11="●"))&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="AW11">
+        <f>IF(SUMPRODUCT(($E$4:$AI$4=$AN6)*($E11:$AI11="●"))&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="AX11">
+        <f>IF(SUMPRODUCT(($E$4:$AI$4=$AN7)*($E11:$AI11="●"))&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="AY11">
+        <f>IF(SUMPRODUCT(($E$4:$AI$4=$AN8)*($E11:$AI11="●"))&gt;0,1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="16" t="n"/>
+      <c r="C12" s="16" t="n"/>
+      <c r="D12" s="16" t="n"/>
+      <c r="E12" s="16" t="n"/>
+      <c r="F12" s="16" t="n"/>
+      <c r="G12" s="16" t="n"/>
+      <c r="H12" s="16" t="n"/>
+      <c r="I12" s="16" t="n"/>
+      <c r="J12" s="16" t="n"/>
+      <c r="K12" s="16" t="n"/>
+      <c r="L12" s="16" t="n"/>
+      <c r="M12" s="16" t="n"/>
+      <c r="N12" s="16" t="n"/>
+      <c r="O12" s="16" t="n"/>
+      <c r="P12" s="16" t="n"/>
+      <c r="Q12" s="16" t="n"/>
+      <c r="R12" s="16" t="n"/>
+      <c r="S12" s="16" t="n"/>
+      <c r="T12" s="16" t="n"/>
+      <c r="U12" s="16" t="n"/>
+      <c r="V12" s="16" t="n"/>
+      <c r="W12" s="16" t="n"/>
+      <c r="X12" s="16" t="n"/>
+      <c r="Y12" s="16" t="n"/>
+      <c r="Z12" s="16" t="n"/>
+      <c r="AA12" s="16" t="n"/>
+      <c r="AB12" s="16" t="n"/>
+      <c r="AC12" s="16" t="n"/>
+      <c r="AD12" s="16" t="n"/>
+      <c r="AE12" s="16" t="n"/>
+      <c r="AF12" s="16" t="n"/>
+      <c r="AG12" s="16" t="n"/>
+      <c r="AH12" s="16" t="n"/>
+      <c r="AI12" s="16" t="n"/>
+      <c r="AJ12" s="4" t="n"/>
+      <c r="AK12" s="4">
+        <f>COUNTIF($E12:$AI12,"●")</f>
+        <v/>
+      </c>
+      <c r="AL12" s="4">
+        <f>COUNTIF($E12:$AI12,"×")</f>
+        <v/>
+      </c>
+      <c r="AU12">
+        <f>IF(SUMPRODUCT(($E$4:$AI$4=$AN4)*($E12:$AI12="●"))&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="AV12">
+        <f>IF(SUMPRODUCT(($E$4:$AI$4=$AN5)*($E12:$AI12="●"))&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="AW12">
+        <f>IF(SUMPRODUCT(($E$4:$AI$4=$AN6)*($E12:$AI12="●"))&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="AX12">
+        <f>IF(SUMPRODUCT(($E$4:$AI$4=$AN7)*($E12:$AI12="●"))&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="AY12">
+        <f>IF(SUMPRODUCT(($E$4:$AI$4=$AN8)*($E12:$AI12="●"))&gt;0,1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="16" t="n"/>
+      <c r="C13" s="16" t="n"/>
+      <c r="D13" s="16" t="n"/>
+      <c r="E13" s="16" t="n"/>
+      <c r="F13" s="16" t="n"/>
+      <c r="G13" s="16" t="n"/>
+      <c r="H13" s="16" t="n"/>
+      <c r="I13" s="16" t="n"/>
+      <c r="J13" s="16" t="n"/>
+      <c r="K13" s="16" t="n"/>
+      <c r="L13" s="16" t="n"/>
+      <c r="M13" s="16" t="n"/>
+      <c r="N13" s="16" t="n"/>
+      <c r="O13" s="16" t="n"/>
+      <c r="P13" s="16" t="n"/>
+      <c r="Q13" s="16" t="n"/>
+      <c r="R13" s="16" t="n"/>
+      <c r="S13" s="16" t="n"/>
+      <c r="T13" s="16" t="n"/>
+      <c r="U13" s="16" t="n"/>
+      <c r="V13" s="16" t="n"/>
+      <c r="W13" s="16" t="n"/>
+      <c r="X13" s="16" t="n"/>
+      <c r="Y13" s="16" t="n"/>
+      <c r="Z13" s="16" t="n"/>
+      <c r="AA13" s="16" t="n"/>
+      <c r="AB13" s="16" t="n"/>
+      <c r="AC13" s="16" t="n"/>
+      <c r="AD13" s="16" t="n"/>
+      <c r="AE13" s="16" t="n"/>
+      <c r="AF13" s="16" t="n"/>
+      <c r="AG13" s="16" t="n"/>
+      <c r="AH13" s="16" t="n"/>
+      <c r="AI13" s="16" t="n"/>
+      <c r="AJ13" s="4" t="n"/>
+      <c r="AK13" s="4">
+        <f>COUNTIF($E13:$AI13,"●")</f>
+        <v/>
+      </c>
+      <c r="AL13" s="4">
+        <f>COUNTIF($E13:$AI13,"×")</f>
+        <v/>
+      </c>
+      <c r="AU13">
+        <f>IF(SUMPRODUCT(($E$4:$AI$4=$AN4)*($E13:$AI13="●"))&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="AV13">
+        <f>IF(SUMPRODUCT(($E$4:$AI$4=$AN5)*($E13:$AI13="●"))&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="AW13">
+        <f>IF(SUMPRODUCT(($E$4:$AI$4=$AN6)*($E13:$AI13="●"))&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="AX13">
+        <f>IF(SUMPRODUCT(($E$4:$AI$4=$AN7)*($E13:$AI13="●"))&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="AY13">
+        <f>IF(SUMPRODUCT(($E$4:$AI$4=$AN8)*($E13:$AI13="●"))&gt;0,1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="16" t="n"/>
+      <c r="C14" s="16" t="n"/>
+      <c r="D14" s="16" t="n"/>
+      <c r="E14" s="16" t="n"/>
+      <c r="F14" s="16" t="n"/>
+      <c r="G14" s="16" t="n"/>
+      <c r="H14" s="16" t="n"/>
+      <c r="I14" s="16" t="n"/>
+      <c r="J14" s="16" t="n"/>
+      <c r="K14" s="16" t="n"/>
+      <c r="L14" s="16" t="n"/>
+      <c r="M14" s="16" t="n"/>
+      <c r="N14" s="16" t="n"/>
+      <c r="O14" s="16" t="n"/>
+      <c r="P14" s="16" t="n"/>
+      <c r="Q14" s="16" t="n"/>
+      <c r="R14" s="16" t="n"/>
+      <c r="S14" s="16" t="n"/>
+      <c r="T14" s="16" t="n"/>
+      <c r="U14" s="16" t="n"/>
+      <c r="V14" s="16" t="n"/>
+      <c r="W14" s="16" t="n"/>
+      <c r="X14" s="16" t="n"/>
+      <c r="Y14" s="16" t="n"/>
+      <c r="Z14" s="16" t="n"/>
+      <c r="AA14" s="16" t="n"/>
+      <c r="AB14" s="16" t="n"/>
+      <c r="AC14" s="16" t="n"/>
+      <c r="AD14" s="16" t="n"/>
+      <c r="AE14" s="16" t="n"/>
+      <c r="AF14" s="16" t="n"/>
+      <c r="AG14" s="16" t="n"/>
+      <c r="AH14" s="16" t="n"/>
+      <c r="AI14" s="16" t="n"/>
+      <c r="AJ14" s="4" t="n"/>
+      <c r="AK14" s="4">
+        <f>COUNTIF($E14:$AI14,"●")</f>
+        <v/>
+      </c>
+      <c r="AL14" s="4">
+        <f>COUNTIF($E14:$AI14,"×")</f>
+        <v/>
+      </c>
+      <c r="AU14">
+        <f>IF(SUMPRODUCT(($E$4:$AI$4=$AN4)*($E14:$AI14="●"))&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="AV14">
+        <f>IF(SUMPRODUCT(($E$4:$AI$4=$AN5)*($E14:$AI14="●"))&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="AW14">
+        <f>IF(SUMPRODUCT(($E$4:$AI$4=$AN6)*($E14:$AI14="●"))&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="AX14">
+        <f>IF(SUMPRODUCT(($E$4:$AI$4=$AN7)*($E14:$AI14="●"))&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="AY14">
+        <f>IF(SUMPRODUCT(($E$4:$AI$4=$AN8)*($E14:$AI14="●"))&gt;0,1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="16" t="n"/>
+      <c r="C15" s="16" t="n"/>
+      <c r="D15" s="16" t="n"/>
+      <c r="E15" s="16" t="n"/>
+      <c r="F15" s="16" t="n"/>
+      <c r="G15" s="16" t="n"/>
+      <c r="H15" s="16" t="n"/>
+      <c r="I15" s="16" t="n"/>
+      <c r="J15" s="16" t="n"/>
+      <c r="K15" s="16" t="n"/>
+      <c r="L15" s="16" t="n"/>
+      <c r="M15" s="16" t="n"/>
+      <c r="N15" s="16" t="n"/>
+      <c r="O15" s="16" t="n"/>
+      <c r="P15" s="16" t="n"/>
+      <c r="Q15" s="16" t="n"/>
+      <c r="R15" s="16" t="n"/>
+      <c r="S15" s="16" t="n"/>
+      <c r="T15" s="16" t="n"/>
+      <c r="U15" s="16" t="n"/>
+      <c r="V15" s="16" t="n"/>
+      <c r="W15" s="16" t="n"/>
+      <c r="X15" s="16" t="n"/>
+      <c r="Y15" s="16" t="n"/>
+      <c r="Z15" s="16" t="n"/>
+      <c r="AA15" s="16" t="n"/>
+      <c r="AB15" s="16" t="n"/>
+      <c r="AC15" s="16" t="n"/>
+      <c r="AD15" s="16" t="n"/>
+      <c r="AE15" s="16" t="n"/>
+      <c r="AF15" s="16" t="n"/>
+      <c r="AG15" s="16" t="n"/>
+      <c r="AH15" s="16" t="n"/>
+      <c r="AI15" s="16" t="n"/>
+      <c r="AJ15" s="4" t="n"/>
+      <c r="AK15" s="4">
+        <f>COUNTIF($E15:$AI15,"●")</f>
+        <v/>
+      </c>
+      <c r="AL15" s="4">
+        <f>COUNTIF($E15:$AI15,"×")</f>
+        <v/>
+      </c>
+      <c r="AU15">
+        <f>IF(SUMPRODUCT(($E$4:$AI$4=$AN4)*($E15:$AI15="●"))&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="AV15">
+        <f>IF(SUMPRODUCT(($E$4:$AI$4=$AN5)*($E15:$AI15="●"))&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="AW15">
+        <f>IF(SUMPRODUCT(($E$4:$AI$4=$AN6)*($E15:$AI15="●"))&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="AX15">
+        <f>IF(SUMPRODUCT(($E$4:$AI$4=$AN7)*($E15:$AI15="●"))&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="AY15">
+        <f>IF(SUMPRODUCT(($E$4:$AI$4=$AN8)*($E15:$AI15="●"))&gt;0,1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="16" t="n"/>
+      <c r="C16" s="16" t="n"/>
+      <c r="D16" s="16" t="n"/>
+      <c r="E16" s="16" t="n"/>
+      <c r="F16" s="16" t="n"/>
+      <c r="G16" s="16" t="n"/>
+      <c r="H16" s="16" t="n"/>
+      <c r="I16" s="16" t="n"/>
+      <c r="J16" s="16" t="n"/>
+      <c r="K16" s="16" t="n"/>
+      <c r="L16" s="16" t="n"/>
+      <c r="M16" s="16" t="n"/>
+      <c r="N16" s="16" t="n"/>
+      <c r="O16" s="16" t="n"/>
+      <c r="P16" s="16" t="n"/>
+      <c r="Q16" s="16" t="n"/>
+      <c r="R16" s="16" t="n"/>
+      <c r="S16" s="16" t="n"/>
+      <c r="T16" s="16" t="n"/>
+      <c r="U16" s="16" t="n"/>
+      <c r="V16" s="16" t="n"/>
+      <c r="W16" s="16" t="n"/>
+      <c r="X16" s="16" t="n"/>
+      <c r="Y16" s="16" t="n"/>
+      <c r="Z16" s="16" t="n"/>
+      <c r="AA16" s="16" t="n"/>
+      <c r="AB16" s="16" t="n"/>
+      <c r="AC16" s="16" t="n"/>
+      <c r="AD16" s="16" t="n"/>
+      <c r="AE16" s="16" t="n"/>
+      <c r="AF16" s="16" t="n"/>
+      <c r="AG16" s="16" t="n"/>
+      <c r="AH16" s="16" t="n"/>
+      <c r="AI16" s="16" t="n"/>
+      <c r="AJ16" s="4" t="n"/>
+      <c r="AK16" s="4">
+        <f>COUNTIF($E16:$AI16,"●")</f>
+        <v/>
+      </c>
+      <c r="AL16" s="4">
+        <f>COUNTIF($E16:$AI16,"×")</f>
+        <v/>
+      </c>
+      <c r="AU16">
+        <f>IF(SUMPRODUCT(($E$4:$AI$4=$AN4)*($E16:$AI16="●"))&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="AV16">
+        <f>IF(SUMPRODUCT(($E$4:$AI$4=$AN5)*($E16:$AI16="●"))&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="AW16">
+        <f>IF(SUMPRODUCT(($E$4:$AI$4=$AN6)*($E16:$AI16="●"))&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="AX16">
+        <f>IF(SUMPRODUCT(($E$4:$AI$4=$AN7)*($E16:$AI16="●"))&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="AY16">
+        <f>IF(SUMPRODUCT(($E$4:$AI$4=$AN8)*($E16:$AI16="●"))&gt;0,1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="16" t="n"/>
+      <c r="C17" s="16" t="n"/>
+      <c r="D17" s="16" t="n"/>
+      <c r="E17" s="16" t="n"/>
+      <c r="F17" s="16" t="n"/>
+      <c r="G17" s="16" t="n"/>
+      <c r="H17" s="16" t="n"/>
+      <c r="I17" s="16" t="n"/>
+      <c r="J17" s="16" t="n"/>
+      <c r="K17" s="16" t="n"/>
+      <c r="L17" s="16" t="n"/>
+      <c r="M17" s="16" t="n"/>
+      <c r="N17" s="16" t="n"/>
+      <c r="O17" s="16" t="n"/>
+      <c r="P17" s="16" t="n"/>
+      <c r="Q17" s="16" t="n"/>
+      <c r="R17" s="16" t="n"/>
+      <c r="S17" s="16" t="n"/>
+      <c r="T17" s="16" t="n"/>
+      <c r="U17" s="16" t="n"/>
+      <c r="V17" s="16" t="n"/>
+      <c r="W17" s="16" t="n"/>
+      <c r="X17" s="16" t="n"/>
+      <c r="Y17" s="16" t="n"/>
+      <c r="Z17" s="16" t="n"/>
+      <c r="AA17" s="16" t="n"/>
+      <c r="AB17" s="16" t="n"/>
+      <c r="AC17" s="16" t="n"/>
+      <c r="AD17" s="16" t="n"/>
+      <c r="AE17" s="16" t="n"/>
+      <c r="AF17" s="16" t="n"/>
+      <c r="AG17" s="16" t="n"/>
+      <c r="AH17" s="16" t="n"/>
+      <c r="AI17" s="16" t="n"/>
+      <c r="AJ17" s="4" t="n"/>
+      <c r="AK17" s="4">
+        <f>COUNTIF($E17:$AI17,"●")</f>
+        <v/>
+      </c>
+      <c r="AL17" s="4">
+        <f>COUNTIF($E17:$AI17,"×")</f>
+        <v/>
+      </c>
+      <c r="AU17">
+        <f>IF(SUMPRODUCT(($E$4:$AI$4=$AN4)*($E17:$AI17="●"))&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="AV17">
+        <f>IF(SUMPRODUCT(($E$4:$AI$4=$AN5)*($E17:$AI17="●"))&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="AW17">
+        <f>IF(SUMPRODUCT(($E$4:$AI$4=$AN6)*($E17:$AI17="●"))&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="AX17">
+        <f>IF(SUMPRODUCT(($E$4:$AI$4=$AN7)*($E17:$AI17="●"))&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="AY17">
+        <f>IF(SUMPRODUCT(($E$4:$AI$4=$AN8)*($E17:$AI17="●"))&gt;0,1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="16" t="n"/>
+      <c r="C18" s="16" t="n"/>
+      <c r="D18" s="16" t="n"/>
+      <c r="E18" s="16" t="n"/>
+      <c r="F18" s="16" t="n"/>
+      <c r="G18" s="16" t="n"/>
+      <c r="H18" s="16" t="n"/>
+      <c r="I18" s="16" t="n"/>
+      <c r="J18" s="16" t="n"/>
+      <c r="K18" s="16" t="n"/>
+      <c r="L18" s="16" t="n"/>
+      <c r="M18" s="16" t="n"/>
+      <c r="N18" s="16" t="n"/>
+      <c r="O18" s="16" t="n"/>
+      <c r="P18" s="16" t="n"/>
+      <c r="Q18" s="16" t="n"/>
+      <c r="R18" s="16" t="n"/>
+      <c r="S18" s="16" t="n"/>
+      <c r="T18" s="16" t="n"/>
+      <c r="U18" s="16" t="n"/>
+      <c r="V18" s="16" t="n"/>
+      <c r="W18" s="16" t="n"/>
+      <c r="X18" s="16" t="n"/>
+      <c r="Y18" s="16" t="n"/>
+      <c r="Z18" s="16" t="n"/>
+      <c r="AA18" s="16" t="n"/>
+      <c r="AB18" s="16" t="n"/>
+      <c r="AC18" s="16" t="n"/>
+      <c r="AD18" s="16" t="n"/>
+      <c r="AE18" s="16" t="n"/>
+      <c r="AF18" s="16" t="n"/>
+      <c r="AG18" s="16" t="n"/>
+      <c r="AH18" s="16" t="n"/>
+      <c r="AI18" s="16" t="n"/>
+      <c r="AJ18" s="4" t="n"/>
+      <c r="AK18" s="4">
+        <f>COUNTIF($E18:$AI18,"●")</f>
+        <v/>
+      </c>
+      <c r="AL18" s="4">
+        <f>COUNTIF($E18:$AI18,"×")</f>
+        <v/>
+      </c>
+      <c r="AU18">
+        <f>IF(SUMPRODUCT(($E$4:$AI$4=$AN4)*($E18:$AI18="●"))&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="AV18">
+        <f>IF(SUMPRODUCT(($E$4:$AI$4=$AN5)*($E18:$AI18="●"))&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="AW18">
+        <f>IF(SUMPRODUCT(($E$4:$AI$4=$AN6)*($E18:$AI18="●"))&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="AX18">
+        <f>IF(SUMPRODUCT(($E$4:$AI$4=$AN7)*($E18:$AI18="●"))&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="AY18">
+        <f>IF(SUMPRODUCT(($E$4:$AI$4=$AN8)*($E18:$AI18="●"))&gt;0,1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="16" t="n"/>
+      <c r="C19" s="16" t="n"/>
+      <c r="D19" s="16" t="n"/>
+      <c r="E19" s="16" t="n"/>
+      <c r="F19" s="16" t="n"/>
+      <c r="G19" s="16" t="n"/>
+      <c r="H19" s="16" t="n"/>
+      <c r="I19" s="16" t="n"/>
+      <c r="J19" s="16" t="n"/>
+      <c r="K19" s="16" t="n"/>
+      <c r="L19" s="16" t="n"/>
+      <c r="M19" s="16" t="n"/>
+      <c r="N19" s="16" t="n"/>
+      <c r="O19" s="16" t="n"/>
+      <c r="P19" s="16" t="n"/>
+      <c r="Q19" s="16" t="n"/>
+      <c r="R19" s="16" t="n"/>
+      <c r="S19" s="16" t="n"/>
+      <c r="T19" s="16" t="n"/>
+      <c r="U19" s="16" t="n"/>
+      <c r="V19" s="16" t="n"/>
+      <c r="W19" s="16" t="n"/>
+      <c r="X19" s="16" t="n"/>
+      <c r="Y19" s="16" t="n"/>
+      <c r="Z19" s="16" t="n"/>
+      <c r="AA19" s="16" t="n"/>
+      <c r="AB19" s="16" t="n"/>
+      <c r="AC19" s="16" t="n"/>
+      <c r="AD19" s="16" t="n"/>
+      <c r="AE19" s="16" t="n"/>
+      <c r="AF19" s="16" t="n"/>
+      <c r="AG19" s="16" t="n"/>
+      <c r="AH19" s="16" t="n"/>
+      <c r="AI19" s="16" t="n"/>
+      <c r="AJ19" s="4" t="n"/>
+      <c r="AK19" s="4">
+        <f>COUNTIF($E19:$AI19,"●")</f>
+        <v/>
+      </c>
+      <c r="AL19" s="4">
+        <f>COUNTIF($E19:$AI19,"×")</f>
+        <v/>
+      </c>
+      <c r="AU19">
+        <f>IF(SUMPRODUCT(($E$4:$AI$4=$AN4)*($E19:$AI19="●"))&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="AV19">
+        <f>IF(SUMPRODUCT(($E$4:$AI$4=$AN5)*($E19:$AI19="●"))&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="AW19">
+        <f>IF(SUMPRODUCT(($E$4:$AI$4=$AN6)*($E19:$AI19="●"))&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="AX19">
+        <f>IF(SUMPRODUCT(($E$4:$AI$4=$AN7)*($E19:$AI19="●"))&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="AY19">
+        <f>IF(SUMPRODUCT(($E$4:$AI$4=$AN8)*($E19:$AI19="●"))&gt;0,1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="25" t="inlineStr">
+        <is>
+          <t>日別利用数</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="n"/>
+      <c r="D20" s="4" t="n"/>
+      <c r="E20" s="4">
+        <f>COUNTIF(E$5:E$19,"●")</f>
+        <v/>
+      </c>
+      <c r="F20" s="4">
+        <f>COUNTIF(F$5:F$19,"●")</f>
+        <v/>
+      </c>
+      <c r="G20" s="4">
+        <f>COUNTIF(G$5:G$19,"●")</f>
+        <v/>
+      </c>
+      <c r="H20" s="4">
+        <f>COUNTIF(H$5:H$19,"●")</f>
+        <v/>
+      </c>
+      <c r="I20" s="4">
+        <f>COUNTIF(I$5:I$19,"●")</f>
+        <v/>
+      </c>
+      <c r="J20" s="4">
+        <f>COUNTIF(J$5:J$19,"●")</f>
+        <v/>
+      </c>
+      <c r="K20" s="4">
+        <f>COUNTIF(K$5:K$19,"●")</f>
+        <v/>
+      </c>
+      <c r="L20" s="4">
+        <f>COUNTIF(L$5:L$19,"●")</f>
+        <v/>
+      </c>
+      <c r="M20" s="4">
+        <f>COUNTIF(M$5:M$19,"●")</f>
+        <v/>
+      </c>
+      <c r="N20" s="4">
+        <f>COUNTIF(N$5:N$19,"●")</f>
+        <v/>
+      </c>
+      <c r="O20" s="4">
+        <f>COUNTIF(O$5:O$19,"●")</f>
+        <v/>
+      </c>
+      <c r="P20" s="4">
+        <f>COUNTIF(P$5:P$19,"●")</f>
+        <v/>
+      </c>
+      <c r="Q20" s="4">
+        <f>COUNTIF(Q$5:Q$19,"●")</f>
+        <v/>
+      </c>
+      <c r="R20" s="4">
+        <f>COUNTIF(R$5:R$19,"●")</f>
+        <v/>
+      </c>
+      <c r="S20" s="4">
+        <f>COUNTIF(S$5:S$19,"●")</f>
+        <v/>
+      </c>
+      <c r="T20" s="4">
+        <f>COUNTIF(T$5:T$19,"●")</f>
+        <v/>
+      </c>
+      <c r="U20" s="4">
+        <f>COUNTIF(U$5:U$19,"●")</f>
+        <v/>
+      </c>
+      <c r="V20" s="4">
+        <f>COUNTIF(V$5:V$19,"●")</f>
+        <v/>
+      </c>
+      <c r="W20" s="4">
+        <f>COUNTIF(W$5:W$19,"●")</f>
+        <v/>
+      </c>
+      <c r="X20" s="4">
+        <f>COUNTIF(X$5:X$19,"●")</f>
+        <v/>
+      </c>
+      <c r="Y20" s="4">
+        <f>COUNTIF(Y$5:Y$19,"●")</f>
+        <v/>
+      </c>
+      <c r="Z20" s="4">
+        <f>COUNTIF(Z$5:Z$19,"●")</f>
+        <v/>
+      </c>
+      <c r="AA20" s="4">
+        <f>COUNTIF(AA$5:AA$19,"●")</f>
+        <v/>
+      </c>
+      <c r="AB20" s="4">
+        <f>COUNTIF(AB$5:AB$19,"●")</f>
+        <v/>
+      </c>
+      <c r="AC20" s="4">
+        <f>COUNTIF(AC$5:AC$19,"●")</f>
+        <v/>
+      </c>
+      <c r="AD20" s="4">
+        <f>COUNTIF(AD$5:AD$19,"●")</f>
+        <v/>
+      </c>
+      <c r="AE20" s="4">
+        <f>COUNTIF(AE$5:AE$19,"●")</f>
+        <v/>
+      </c>
+      <c r="AF20" s="4">
+        <f>COUNTIF(AF$5:AF$19,"●")</f>
+        <v/>
+      </c>
+      <c r="AG20" s="4">
+        <f>COUNTIF(AG$5:AG$19,"●")</f>
+        <v/>
+      </c>
+      <c r="AH20" s="4">
+        <f>COUNTIF(AH$5:AH$19,"●")</f>
+        <v/>
+      </c>
+      <c r="AI20" s="4">
+        <f>COUNTIF(AI$5:AI$19,"●")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="25" t="inlineStr">
+        <is>
+          <t>日別キャンセル数</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="n"/>
+      <c r="D21" s="4" t="n"/>
+      <c r="E21" s="4">
+        <f>COUNTIF(E$5:E$19,"×")</f>
+        <v/>
+      </c>
+      <c r="F21" s="4">
+        <f>COUNTIF(F$5:F$19,"×")</f>
+        <v/>
+      </c>
+      <c r="G21" s="4">
+        <f>COUNTIF(G$5:G$19,"×")</f>
+        <v/>
+      </c>
+      <c r="H21" s="4">
+        <f>COUNTIF(H$5:H$19,"×")</f>
+        <v/>
+      </c>
+      <c r="I21" s="4">
+        <f>COUNTIF(I$5:I$19,"×")</f>
+        <v/>
+      </c>
+      <c r="J21" s="4">
+        <f>COUNTIF(J$5:J$19,"×")</f>
+        <v/>
+      </c>
+      <c r="K21" s="4">
+        <f>COUNTIF(K$5:K$19,"×")</f>
+        <v/>
+      </c>
+      <c r="L21" s="4">
+        <f>COUNTIF(L$5:L$19,"×")</f>
+        <v/>
+      </c>
+      <c r="M21" s="4">
+        <f>COUNTIF(M$5:M$19,"×")</f>
+        <v/>
+      </c>
+      <c r="N21" s="4">
+        <f>COUNTIF(N$5:N$19,"×")</f>
+        <v/>
+      </c>
+      <c r="O21" s="4">
+        <f>COUNTIF(O$5:O$19,"×")</f>
+        <v/>
+      </c>
+      <c r="P21" s="4">
+        <f>COUNTIF(P$5:P$19,"×")</f>
+        <v/>
+      </c>
+      <c r="Q21" s="4">
+        <f>COUNTIF(Q$5:Q$19,"×")</f>
+        <v/>
+      </c>
+      <c r="R21" s="4">
+        <f>COUNTIF(R$5:R$19,"×")</f>
+        <v/>
+      </c>
+      <c r="S21" s="4">
+        <f>COUNTIF(S$5:S$19,"×")</f>
+        <v/>
+      </c>
+      <c r="T21" s="4">
+        <f>COUNTIF(T$5:T$19,"×")</f>
+        <v/>
+      </c>
+      <c r="U21" s="4">
+        <f>COUNTIF(U$5:U$19,"×")</f>
+        <v/>
+      </c>
+      <c r="V21" s="4">
+        <f>COUNTIF(V$5:V$19,"×")</f>
+        <v/>
+      </c>
+      <c r="W21" s="4">
+        <f>COUNTIF(W$5:W$19,"×")</f>
+        <v/>
+      </c>
+      <c r="X21" s="4">
+        <f>COUNTIF(X$5:X$19,"×")</f>
+        <v/>
+      </c>
+      <c r="Y21" s="4">
+        <f>COUNTIF(Y$5:Y$19,"×")</f>
+        <v/>
+      </c>
+      <c r="Z21" s="4">
+        <f>COUNTIF(Z$5:Z$19,"×")</f>
+        <v/>
+      </c>
+      <c r="AA21" s="4">
+        <f>COUNTIF(AA$5:AA$19,"×")</f>
+        <v/>
+      </c>
+      <c r="AB21" s="4">
+        <f>COUNTIF(AB$5:AB$19,"×")</f>
+        <v/>
+      </c>
+      <c r="AC21" s="4">
+        <f>COUNTIF(AC$5:AC$19,"×")</f>
+        <v/>
+      </c>
+      <c r="AD21" s="4">
+        <f>COUNTIF(AD$5:AD$19,"×")</f>
+        <v/>
+      </c>
+      <c r="AE21" s="4">
+        <f>COUNTIF(AE$5:AE$19,"×")</f>
+        <v/>
+      </c>
+      <c r="AF21" s="4">
+        <f>COUNTIF(AF$5:AF$19,"×")</f>
+        <v/>
+      </c>
+      <c r="AG21" s="4">
+        <f>COUNTIF(AG$5:AG$19,"×")</f>
+        <v/>
+      </c>
+      <c r="AH21" s="4">
+        <f>COUNTIF(AH$5:AH$19,"×")</f>
+        <v/>
+      </c>
+      <c r="AI21" s="4">
+        <f>COUNTIF(AI$5:AI$19,"×")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>申請床数</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="n">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="E5:AI19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"●,予,×"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AO10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="4.2" customWidth="1" min="5" max="5"/>
+    <col width="4.2" customWidth="1" min="6" max="6"/>
+    <col width="4.2" customWidth="1" min="7" max="7"/>
+    <col width="4.2" customWidth="1" min="8" max="8"/>
+    <col width="4.2" customWidth="1" min="9" max="9"/>
+    <col width="4.2" customWidth="1" min="10" max="10"/>
+    <col width="4.2" customWidth="1" min="11" max="11"/>
+    <col width="4.2" customWidth="1" min="12" max="12"/>
+    <col width="4.2" customWidth="1" min="13" max="13"/>
+    <col width="4.2" customWidth="1" min="14" max="14"/>
+    <col width="4.2" customWidth="1" min="15" max="15"/>
+    <col width="4.2" customWidth="1" min="16" max="16"/>
+    <col width="4.2" customWidth="1" min="17" max="17"/>
+    <col width="4.2" customWidth="1" min="18" max="18"/>
+    <col width="4.2" customWidth="1" min="19" max="19"/>
+    <col width="4.2" customWidth="1" min="20" max="20"/>
+    <col width="4.2" customWidth="1" min="21" max="21"/>
+    <col width="4.2" customWidth="1" min="22" max="22"/>
+    <col width="4.2" customWidth="1" min="23" max="23"/>
+    <col width="4.2" customWidth="1" min="24" max="24"/>
+    <col width="4.2" customWidth="1" min="25" max="25"/>
+    <col width="4.2" customWidth="1" min="26" max="26"/>
+    <col width="4.2" customWidth="1" min="27" max="27"/>
+    <col width="4.2" customWidth="1" min="28" max="28"/>
+    <col width="4.2" customWidth="1" min="29" max="29"/>
+    <col width="4.2" customWidth="1" min="30" max="30"/>
+    <col width="4.2" customWidth="1" min="31" max="31"/>
+    <col width="4.2" customWidth="1" min="32" max="32"/>
+    <col width="4.2" customWidth="1" min="33" max="33"/>
+    <col width="4.2" customWidth="1" min="34" max="34"/>
+    <col width="4.2" customWidth="1" min="35" max="35"/>
+    <col width="11" customWidth="1" min="37" max="37"/>
+    <col width="13" customWidth="1" min="40" max="40"/>
+    <col width="13" customWidth="1" min="41" max="41"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>営業行動（訪問・郵送・FAX等の接点件数を日別に入力）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>営業チャネル</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>月間目標</t>
+        </is>
+      </c>
+      <c r="D3" s="22" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="E3" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;1,"",DATE(設定対象年,設定対象月,1))</f>
+        <v/>
+      </c>
+      <c r="F3" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;2,"",DATE(設定対象年,設定対象月,2))</f>
+        <v/>
+      </c>
+      <c r="G3" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;3,"",DATE(設定対象年,設定対象月,3))</f>
+        <v/>
+      </c>
+      <c r="H3" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;4,"",DATE(設定対象年,設定対象月,4))</f>
+        <v/>
+      </c>
+      <c r="I3" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;5,"",DATE(設定対象年,設定対象月,5))</f>
+        <v/>
+      </c>
+      <c r="J3" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;6,"",DATE(設定対象年,設定対象月,6))</f>
+        <v/>
+      </c>
+      <c r="K3" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;7,"",DATE(設定対象年,設定対象月,7))</f>
+        <v/>
+      </c>
+      <c r="L3" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;8,"",DATE(設定対象年,設定対象月,8))</f>
+        <v/>
+      </c>
+      <c r="M3" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;9,"",DATE(設定対象年,設定対象月,9))</f>
+        <v/>
+      </c>
+      <c r="N3" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;10,"",DATE(設定対象年,設定対象月,10))</f>
+        <v/>
+      </c>
+      <c r="O3" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;11,"",DATE(設定対象年,設定対象月,11))</f>
+        <v/>
+      </c>
+      <c r="P3" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;12,"",DATE(設定対象年,設定対象月,12))</f>
+        <v/>
+      </c>
+      <c r="Q3" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;13,"",DATE(設定対象年,設定対象月,13))</f>
+        <v/>
+      </c>
+      <c r="R3" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;14,"",DATE(設定対象年,設定対象月,14))</f>
+        <v/>
+      </c>
+      <c r="S3" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;15,"",DATE(設定対象年,設定対象月,15))</f>
+        <v/>
+      </c>
+      <c r="T3" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;16,"",DATE(設定対象年,設定対象月,16))</f>
+        <v/>
+      </c>
+      <c r="U3" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;17,"",DATE(設定対象年,設定対象月,17))</f>
+        <v/>
+      </c>
+      <c r="V3" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;18,"",DATE(設定対象年,設定対象月,18))</f>
+        <v/>
+      </c>
+      <c r="W3" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;19,"",DATE(設定対象年,設定対象月,19))</f>
+        <v/>
+      </c>
+      <c r="X3" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;20,"",DATE(設定対象年,設定対象月,20))</f>
+        <v/>
+      </c>
+      <c r="Y3" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;21,"",DATE(設定対象年,設定対象月,21))</f>
+        <v/>
+      </c>
+      <c r="Z3" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;22,"",DATE(設定対象年,設定対象月,22))</f>
+        <v/>
+      </c>
+      <c r="AA3" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;23,"",DATE(設定対象年,設定対象月,23))</f>
+        <v/>
+      </c>
+      <c r="AB3" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;24,"",DATE(設定対象年,設定対象月,24))</f>
+        <v/>
+      </c>
+      <c r="AC3" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;25,"",DATE(設定対象年,設定対象月,25))</f>
+        <v/>
+      </c>
+      <c r="AD3" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;26,"",DATE(設定対象年,設定対象月,26))</f>
+        <v/>
+      </c>
+      <c r="AE3" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;27,"",DATE(設定対象年,設定対象月,27))</f>
+        <v/>
+      </c>
+      <c r="AF3" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;28,"",DATE(設定対象年,設定対象月,28))</f>
+        <v/>
+      </c>
+      <c r="AG3" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;29,"",DATE(設定対象年,設定対象月,29))</f>
+        <v/>
+      </c>
+      <c r="AH3" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;30,"",DATE(設定対象年,設定対象月,30))</f>
+        <v/>
+      </c>
+      <c r="AI3" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;31,"",DATE(設定対象年,設定対象月,31))</f>
+        <v/>
+      </c>
+      <c r="AJ3" s="4" t="n"/>
+      <c r="AK3" s="4" t="n"/>
+      <c r="AN3" s="5" t="inlineStr">
+        <is>
+          <t>週</t>
+        </is>
+      </c>
+      <c r="AO3" s="5" t="inlineStr">
+        <is>
+          <t>接点件数</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="n"/>
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="24" t="inlineStr">
+        <is>
+          <t>週</t>
+        </is>
+      </c>
+      <c r="E4" s="24">
+        <f>IF(E3="","","第"&amp;ROUNDUP(1/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="F4" s="24">
+        <f>IF(F3="","","第"&amp;ROUNDUP(2/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="G4" s="24">
+        <f>IF(G3="","","第"&amp;ROUNDUP(3/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="H4" s="24">
+        <f>IF(H3="","","第"&amp;ROUNDUP(4/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="I4" s="24">
+        <f>IF(I3="","","第"&amp;ROUNDUP(5/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="J4" s="24">
+        <f>IF(J3="","","第"&amp;ROUNDUP(6/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="K4" s="24">
+        <f>IF(K3="","","第"&amp;ROUNDUP(7/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="L4" s="24">
+        <f>IF(L3="","","第"&amp;ROUNDUP(8/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="M4" s="24">
+        <f>IF(M3="","","第"&amp;ROUNDUP(9/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="N4" s="24">
+        <f>IF(N3="","","第"&amp;ROUNDUP(10/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="O4" s="24">
+        <f>IF(O3="","","第"&amp;ROUNDUP(11/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="P4" s="24">
+        <f>IF(P3="","","第"&amp;ROUNDUP(12/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="Q4" s="24">
+        <f>IF(Q3="","","第"&amp;ROUNDUP(13/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="R4" s="24">
+        <f>IF(R3="","","第"&amp;ROUNDUP(14/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="S4" s="24">
+        <f>IF(S3="","","第"&amp;ROUNDUP(15/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="T4" s="24">
+        <f>IF(T3="","","第"&amp;ROUNDUP(16/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="U4" s="24">
+        <f>IF(U3="","","第"&amp;ROUNDUP(17/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="V4" s="24">
+        <f>IF(V3="","","第"&amp;ROUNDUP(18/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="W4" s="24">
+        <f>IF(W3="","","第"&amp;ROUNDUP(19/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="X4" s="24">
+        <f>IF(X3="","","第"&amp;ROUNDUP(20/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="Y4" s="24">
+        <f>IF(Y3="","","第"&amp;ROUNDUP(21/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="Z4" s="24">
+        <f>IF(Z3="","","第"&amp;ROUNDUP(22/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="AA4" s="24">
+        <f>IF(AA3="","","第"&amp;ROUNDUP(23/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="AB4" s="24">
+        <f>IF(AB3="","","第"&amp;ROUNDUP(24/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="AC4" s="24">
+        <f>IF(AC3="","","第"&amp;ROUNDUP(25/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="AD4" s="24">
+        <f>IF(AD3="","","第"&amp;ROUNDUP(26/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="AE4" s="24">
+        <f>IF(AE3="","","第"&amp;ROUNDUP(27/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="AF4" s="24">
+        <f>IF(AF3="","","第"&amp;ROUNDUP(28/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="AG4" s="24">
+        <f>IF(AG3="","","第"&amp;ROUNDUP(29/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="AH4" s="24">
+        <f>IF(AH3="","","第"&amp;ROUNDUP(30/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="AI4" s="24">
+        <f>IF(AI3="","","第"&amp;ROUNDUP(31/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="AJ4" s="4" t="n"/>
+      <c r="AK4" s="5" t="inlineStr">
+        <is>
+          <t>月間合計</t>
+        </is>
+      </c>
+      <c r="AN4" s="4" t="inlineStr">
+        <is>
+          <t>第1週</t>
+        </is>
+      </c>
+      <c r="AO4" s="4">
+        <f>SUMPRODUCT(($E$4:$AI$4=$AN4)*($E$10:$AI$10))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>相談支援事業所</t>
+        </is>
+      </c>
+      <c r="C5" s="16" t="n"/>
+      <c r="D5" s="16" t="n"/>
+      <c r="E5" s="16" t="n"/>
+      <c r="F5" s="16" t="n"/>
+      <c r="G5" s="16" t="n"/>
+      <c r="H5" s="16" t="n"/>
+      <c r="I5" s="16" t="n"/>
+      <c r="J5" s="16" t="n"/>
+      <c r="K5" s="16" t="n"/>
+      <c r="L5" s="16" t="n"/>
+      <c r="M5" s="16" t="n"/>
+      <c r="N5" s="16" t="n"/>
+      <c r="O5" s="16" t="n"/>
+      <c r="P5" s="16" t="n"/>
+      <c r="Q5" s="16" t="n"/>
+      <c r="R5" s="16" t="n"/>
+      <c r="S5" s="16" t="n"/>
+      <c r="T5" s="16" t="n"/>
+      <c r="U5" s="16" t="n"/>
+      <c r="V5" s="16" t="n"/>
+      <c r="W5" s="16" t="n"/>
+      <c r="X5" s="16" t="n"/>
+      <c r="Y5" s="16" t="n"/>
+      <c r="Z5" s="16" t="n"/>
+      <c r="AA5" s="16" t="n"/>
+      <c r="AB5" s="16" t="n"/>
+      <c r="AC5" s="16" t="n"/>
+      <c r="AD5" s="16" t="n"/>
+      <c r="AE5" s="16" t="n"/>
+      <c r="AF5" s="16" t="n"/>
+      <c r="AG5" s="16" t="n"/>
+      <c r="AH5" s="16" t="n"/>
+      <c r="AI5" s="16" t="n"/>
+      <c r="AJ5" s="4" t="n"/>
+      <c r="AK5" s="4">
+        <f>SUM($E5:$AI5)</f>
+        <v/>
+      </c>
+      <c r="AN5" s="4" t="inlineStr">
+        <is>
+          <t>第2週</t>
+        </is>
+      </c>
+      <c r="AO5" s="4">
+        <f>SUMPRODUCT(($E$4:$AI$4=$AN5)*($E$10:$AI$10))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>基幹相談支援事業所</t>
+        </is>
+      </c>
+      <c r="C6" s="16" t="n"/>
+      <c r="D6" s="16" t="n"/>
+      <c r="E6" s="16" t="n"/>
+      <c r="F6" s="16" t="n"/>
+      <c r="G6" s="16" t="n"/>
+      <c r="H6" s="16" t="n"/>
+      <c r="I6" s="16" t="n"/>
+      <c r="J6" s="16" t="n"/>
+      <c r="K6" s="16" t="n"/>
+      <c r="L6" s="16" t="n"/>
+      <c r="M6" s="16" t="n"/>
+      <c r="N6" s="16" t="n"/>
+      <c r="O6" s="16" t="n"/>
+      <c r="P6" s="16" t="n"/>
+      <c r="Q6" s="16" t="n"/>
+      <c r="R6" s="16" t="n"/>
+      <c r="S6" s="16" t="n"/>
+      <c r="T6" s="16" t="n"/>
+      <c r="U6" s="16" t="n"/>
+      <c r="V6" s="16" t="n"/>
+      <c r="W6" s="16" t="n"/>
+      <c r="X6" s="16" t="n"/>
+      <c r="Y6" s="16" t="n"/>
+      <c r="Z6" s="16" t="n"/>
+      <c r="AA6" s="16" t="n"/>
+      <c r="AB6" s="16" t="n"/>
+      <c r="AC6" s="16" t="n"/>
+      <c r="AD6" s="16" t="n"/>
+      <c r="AE6" s="16" t="n"/>
+      <c r="AF6" s="16" t="n"/>
+      <c r="AG6" s="16" t="n"/>
+      <c r="AH6" s="16" t="n"/>
+      <c r="AI6" s="16" t="n"/>
+      <c r="AJ6" s="4" t="n"/>
+      <c r="AK6" s="4">
+        <f>SUM($E6:$AI6)</f>
+        <v/>
+      </c>
+      <c r="AN6" s="4" t="inlineStr">
+        <is>
+          <t>第3週</t>
+        </is>
+      </c>
+      <c r="AO6" s="4">
+        <f>SUMPRODUCT(($E$4:$AI$4=$AN6)*($E$10:$AI$10))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>障がい福祉課、生活保護課</t>
+        </is>
+      </c>
+      <c r="C7" s="16" t="n"/>
+      <c r="D7" s="16" t="n"/>
+      <c r="E7" s="16" t="n"/>
+      <c r="F7" s="16" t="n"/>
+      <c r="G7" s="16" t="n"/>
+      <c r="H7" s="16" t="n"/>
+      <c r="I7" s="16" t="n"/>
+      <c r="J7" s="16" t="n"/>
+      <c r="K7" s="16" t="n"/>
+      <c r="L7" s="16" t="n"/>
+      <c r="M7" s="16" t="n"/>
+      <c r="N7" s="16" t="n"/>
+      <c r="O7" s="16" t="n"/>
+      <c r="P7" s="16" t="n"/>
+      <c r="Q7" s="16" t="n"/>
+      <c r="R7" s="16" t="n"/>
+      <c r="S7" s="16" t="n"/>
+      <c r="T7" s="16" t="n"/>
+      <c r="U7" s="16" t="n"/>
+      <c r="V7" s="16" t="n"/>
+      <c r="W7" s="16" t="n"/>
+      <c r="X7" s="16" t="n"/>
+      <c r="Y7" s="16" t="n"/>
+      <c r="Z7" s="16" t="n"/>
+      <c r="AA7" s="16" t="n"/>
+      <c r="AB7" s="16" t="n"/>
+      <c r="AC7" s="16" t="n"/>
+      <c r="AD7" s="16" t="n"/>
+      <c r="AE7" s="16" t="n"/>
+      <c r="AF7" s="16" t="n"/>
+      <c r="AG7" s="16" t="n"/>
+      <c r="AH7" s="16" t="n"/>
+      <c r="AI7" s="16" t="n"/>
+      <c r="AJ7" s="4" t="n"/>
+      <c r="AK7" s="4">
+        <f>SUM($E7:$AI7)</f>
+        <v/>
+      </c>
+      <c r="AN7" s="4" t="inlineStr">
+        <is>
+          <t>第4週</t>
+        </is>
+      </c>
+      <c r="AO7" s="4">
+        <f>SUMPRODUCT(($E$4:$AI$4=$AN7)*($E$10:$AI$10))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>病棟のある病院</t>
+        </is>
+      </c>
+      <c r="C8" s="16" t="n"/>
+      <c r="D8" s="16" t="n"/>
+      <c r="E8" s="16" t="n"/>
+      <c r="F8" s="16" t="n"/>
+      <c r="G8" s="16" t="n"/>
+      <c r="H8" s="16" t="n"/>
+      <c r="I8" s="16" t="n"/>
+      <c r="J8" s="16" t="n"/>
+      <c r="K8" s="16" t="n"/>
+      <c r="L8" s="16" t="n"/>
+      <c r="M8" s="16" t="n"/>
+      <c r="N8" s="16" t="n"/>
+      <c r="O8" s="16" t="n"/>
+      <c r="P8" s="16" t="n"/>
+      <c r="Q8" s="16" t="n"/>
+      <c r="R8" s="16" t="n"/>
+      <c r="S8" s="16" t="n"/>
+      <c r="T8" s="16" t="n"/>
+      <c r="U8" s="16" t="n"/>
+      <c r="V8" s="16" t="n"/>
+      <c r="W8" s="16" t="n"/>
+      <c r="X8" s="16" t="n"/>
+      <c r="Y8" s="16" t="n"/>
+      <c r="Z8" s="16" t="n"/>
+      <c r="AA8" s="16" t="n"/>
+      <c r="AB8" s="16" t="n"/>
+      <c r="AC8" s="16" t="n"/>
+      <c r="AD8" s="16" t="n"/>
+      <c r="AE8" s="16" t="n"/>
+      <c r="AF8" s="16" t="n"/>
+      <c r="AG8" s="16" t="n"/>
+      <c r="AH8" s="16" t="n"/>
+      <c r="AI8" s="16" t="n"/>
+      <c r="AJ8" s="4" t="n"/>
+      <c r="AK8" s="4">
+        <f>SUM($E8:$AI8)</f>
+        <v/>
+      </c>
+      <c r="AN8" s="4" t="inlineStr">
+        <is>
+          <t>第5週</t>
+        </is>
+      </c>
+      <c r="AO8" s="4">
+        <f>SUMPRODUCT(($E$4:$AI$4=$AN8)*($E$10:$AI$10))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>就労支援、生活介護、宿泊訓練</t>
+        </is>
+      </c>
+      <c r="C9" s="16" t="n"/>
+      <c r="D9" s="16" t="n"/>
+      <c r="E9" s="16" t="n"/>
+      <c r="F9" s="16" t="n"/>
+      <c r="G9" s="16" t="n"/>
+      <c r="H9" s="16" t="n"/>
+      <c r="I9" s="16" t="n"/>
+      <c r="J9" s="16" t="n"/>
+      <c r="K9" s="16" t="n"/>
+      <c r="L9" s="16" t="n"/>
+      <c r="M9" s="16" t="n"/>
+      <c r="N9" s="16" t="n"/>
+      <c r="O9" s="16" t="n"/>
+      <c r="P9" s="16" t="n"/>
+      <c r="Q9" s="16" t="n"/>
+      <c r="R9" s="16" t="n"/>
+      <c r="S9" s="16" t="n"/>
+      <c r="T9" s="16" t="n"/>
+      <c r="U9" s="16" t="n"/>
+      <c r="V9" s="16" t="n"/>
+      <c r="W9" s="16" t="n"/>
+      <c r="X9" s="16" t="n"/>
+      <c r="Y9" s="16" t="n"/>
+      <c r="Z9" s="16" t="n"/>
+      <c r="AA9" s="16" t="n"/>
+      <c r="AB9" s="16" t="n"/>
+      <c r="AC9" s="16" t="n"/>
+      <c r="AD9" s="16" t="n"/>
+      <c r="AE9" s="16" t="n"/>
+      <c r="AF9" s="16" t="n"/>
+      <c r="AG9" s="16" t="n"/>
+      <c r="AH9" s="16" t="n"/>
+      <c r="AI9" s="16" t="n"/>
+      <c r="AJ9" s="4" t="n"/>
+      <c r="AK9" s="4">
+        <f>SUM($E9:$AI9)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n"/>
+      <c r="B10" s="27" t="inlineStr">
+        <is>
+          <t>合計</t>
+        </is>
+      </c>
+      <c r="C10" s="4">
+        <f>SUM($C5:$C9)</f>
+        <v/>
+      </c>
+      <c r="D10" s="4" t="n"/>
+      <c r="E10" s="4">
+        <f>SUM(E5:E9)</f>
+        <v/>
+      </c>
+      <c r="F10" s="4">
+        <f>SUM(F5:F9)</f>
+        <v/>
+      </c>
+      <c r="G10" s="4">
+        <f>SUM(G5:G9)</f>
+        <v/>
+      </c>
+      <c r="H10" s="4">
+        <f>SUM(H5:H9)</f>
+        <v/>
+      </c>
+      <c r="I10" s="4">
+        <f>SUM(I5:I9)</f>
+        <v/>
+      </c>
+      <c r="J10" s="4">
+        <f>SUM(J5:J9)</f>
+        <v/>
+      </c>
+      <c r="K10" s="4">
+        <f>SUM(K5:K9)</f>
+        <v/>
+      </c>
+      <c r="L10" s="4">
+        <f>SUM(L5:L9)</f>
+        <v/>
+      </c>
+      <c r="M10" s="4">
+        <f>SUM(M5:M9)</f>
+        <v/>
+      </c>
+      <c r="N10" s="4">
+        <f>SUM(N5:N9)</f>
+        <v/>
+      </c>
+      <c r="O10" s="4">
+        <f>SUM(O5:O9)</f>
+        <v/>
+      </c>
+      <c r="P10" s="4">
+        <f>SUM(P5:P9)</f>
+        <v/>
+      </c>
+      <c r="Q10" s="4">
+        <f>SUM(Q5:Q9)</f>
+        <v/>
+      </c>
+      <c r="R10" s="4">
+        <f>SUM(R5:R9)</f>
+        <v/>
+      </c>
+      <c r="S10" s="4">
+        <f>SUM(S5:S9)</f>
+        <v/>
+      </c>
+      <c r="T10" s="4">
+        <f>SUM(T5:T9)</f>
+        <v/>
+      </c>
+      <c r="U10" s="4">
+        <f>SUM(U5:U9)</f>
+        <v/>
+      </c>
+      <c r="V10" s="4">
+        <f>SUM(V5:V9)</f>
+        <v/>
+      </c>
+      <c r="W10" s="4">
+        <f>SUM(W5:W9)</f>
+        <v/>
+      </c>
+      <c r="X10" s="4">
+        <f>SUM(X5:X9)</f>
+        <v/>
+      </c>
+      <c r="Y10" s="4">
+        <f>SUM(Y5:Y9)</f>
+        <v/>
+      </c>
+      <c r="Z10" s="4">
+        <f>SUM(Z5:Z9)</f>
+        <v/>
+      </c>
+      <c r="AA10" s="4">
+        <f>SUM(AA5:AA9)</f>
+        <v/>
+      </c>
+      <c r="AB10" s="4">
+        <f>SUM(AB5:AB9)</f>
+        <v/>
+      </c>
+      <c r="AC10" s="4">
+        <f>SUM(AC5:AC9)</f>
+        <v/>
+      </c>
+      <c r="AD10" s="4">
+        <f>SUM(AD5:AD9)</f>
+        <v/>
+      </c>
+      <c r="AE10" s="4">
+        <f>SUM(AE5:AE9)</f>
+        <v/>
+      </c>
+      <c r="AF10" s="4">
+        <f>SUM(AF5:AF9)</f>
+        <v/>
+      </c>
+      <c r="AG10" s="4">
+        <f>SUM(AG5:AG9)</f>
+        <v/>
+      </c>
+      <c r="AH10" s="4">
+        <f>SUM(AH5:AH9)</f>
+        <v/>
+      </c>
+      <c r="AI10" s="4">
+        <f>SUM(AI5:AI9)</f>
+        <v/>
+      </c>
+      <c r="AJ10" s="4" t="n"/>
+      <c r="AK10" s="4">
+        <f>SUM($E10:$AI10)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AQ51"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="4.2" customWidth="1" min="9" max="9"/>
+    <col width="4.2" customWidth="1" min="10" max="10"/>
+    <col width="4.2" customWidth="1" min="11" max="11"/>
+    <col width="4.2" customWidth="1" min="12" max="12"/>
+    <col width="4.2" customWidth="1" min="13" max="13"/>
+    <col width="4.2" customWidth="1" min="14" max="14"/>
+    <col width="4.2" customWidth="1" min="15" max="15"/>
+    <col width="4.2" customWidth="1" min="16" max="16"/>
+    <col width="4.2" customWidth="1" min="17" max="17"/>
+    <col width="4.2" customWidth="1" min="18" max="18"/>
+    <col width="4.2" customWidth="1" min="19" max="19"/>
+    <col width="4.2" customWidth="1" min="20" max="20"/>
+    <col width="4.2" customWidth="1" min="21" max="21"/>
+    <col width="4.2" customWidth="1" min="22" max="22"/>
+    <col width="4.2" customWidth="1" min="23" max="23"/>
+    <col width="4.2" customWidth="1" min="24" max="24"/>
+    <col width="4.2" customWidth="1" min="25" max="25"/>
+    <col width="4.2" customWidth="1" min="26" max="26"/>
+    <col width="4.2" customWidth="1" min="27" max="27"/>
+    <col width="4.2" customWidth="1" min="28" max="28"/>
+    <col width="4.2" customWidth="1" min="29" max="29"/>
+    <col width="4.2" customWidth="1" min="30" max="30"/>
+    <col width="4.2" customWidth="1" min="31" max="31"/>
+    <col width="4.2" customWidth="1" min="32" max="32"/>
+    <col width="4.2" customWidth="1" min="33" max="33"/>
+    <col width="4.2" customWidth="1" min="34" max="34"/>
+    <col width="4.2" customWidth="1" min="35" max="35"/>
+    <col width="13" customWidth="1" min="40" max="40"/>
+    <col width="13" customWidth="1" min="41" max="41"/>
+    <col width="13" customWidth="1" min="42" max="42"/>
+    <col width="13" customWidth="1" min="43" max="43"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>加算要件の実績管理（夜勤職員加配・重度障害者支援体制・福祉専門職員配置）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="28" t="inlineStr">
+        <is>
+          <t>■夜勤職員加配加算（●=加配配置日）</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>配置単位</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>対象</t>
+        </is>
+      </c>
+      <c r="D4" s="22" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="E4" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;1,"",DATE(設定対象年,設定対象月,1))</f>
+        <v/>
+      </c>
+      <c r="F4" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;2,"",DATE(設定対象年,設定対象月,2))</f>
+        <v/>
+      </c>
+      <c r="G4" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;3,"",DATE(設定対象年,設定対象月,3))</f>
+        <v/>
+      </c>
+      <c r="H4" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;4,"",DATE(設定対象年,設定対象月,4))</f>
+        <v/>
+      </c>
+      <c r="I4" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;5,"",DATE(設定対象年,設定対象月,5))</f>
+        <v/>
+      </c>
+      <c r="J4" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;6,"",DATE(設定対象年,設定対象月,6))</f>
+        <v/>
+      </c>
+      <c r="K4" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;7,"",DATE(設定対象年,設定対象月,7))</f>
+        <v/>
+      </c>
+      <c r="L4" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;8,"",DATE(設定対象年,設定対象月,8))</f>
+        <v/>
+      </c>
+      <c r="M4" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;9,"",DATE(設定対象年,設定対象月,9))</f>
+        <v/>
+      </c>
+      <c r="N4" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;10,"",DATE(設定対象年,設定対象月,10))</f>
+        <v/>
+      </c>
+      <c r="O4" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;11,"",DATE(設定対象年,設定対象月,11))</f>
+        <v/>
+      </c>
+      <c r="P4" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;12,"",DATE(設定対象年,設定対象月,12))</f>
+        <v/>
+      </c>
+      <c r="Q4" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;13,"",DATE(設定対象年,設定対象月,13))</f>
+        <v/>
+      </c>
+      <c r="R4" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;14,"",DATE(設定対象年,設定対象月,14))</f>
+        <v/>
+      </c>
+      <c r="S4" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;15,"",DATE(設定対象年,設定対象月,15))</f>
+        <v/>
+      </c>
+      <c r="T4" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;16,"",DATE(設定対象年,設定対象月,16))</f>
+        <v/>
+      </c>
+      <c r="U4" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;17,"",DATE(設定対象年,設定対象月,17))</f>
+        <v/>
+      </c>
+      <c r="V4" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;18,"",DATE(設定対象年,設定対象月,18))</f>
+        <v/>
+      </c>
+      <c r="W4" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;19,"",DATE(設定対象年,設定対象月,19))</f>
+        <v/>
+      </c>
+      <c r="X4" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;20,"",DATE(設定対象年,設定対象月,20))</f>
+        <v/>
+      </c>
+      <c r="Y4" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;21,"",DATE(設定対象年,設定対象月,21))</f>
+        <v/>
+      </c>
+      <c r="Z4" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;22,"",DATE(設定対象年,設定対象月,22))</f>
+        <v/>
+      </c>
+      <c r="AA4" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;23,"",DATE(設定対象年,設定対象月,23))</f>
+        <v/>
+      </c>
+      <c r="AB4" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;24,"",DATE(設定対象年,設定対象月,24))</f>
+        <v/>
+      </c>
+      <c r="AC4" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;25,"",DATE(設定対象年,設定対象月,25))</f>
+        <v/>
+      </c>
+      <c r="AD4" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;26,"",DATE(設定対象年,設定対象月,26))</f>
+        <v/>
+      </c>
+      <c r="AE4" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;27,"",DATE(設定対象年,設定対象月,27))</f>
+        <v/>
+      </c>
+      <c r="AF4" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;28,"",DATE(設定対象年,設定対象月,28))</f>
+        <v/>
+      </c>
+      <c r="AG4" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;29,"",DATE(設定対象年,設定対象月,29))</f>
+        <v/>
+      </c>
+      <c r="AH4" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;30,"",DATE(設定対象年,設定対象月,30))</f>
+        <v/>
+      </c>
+      <c r="AI4" s="23">
+        <f>IF(DAY(EOMONTH(DATE(設定対象年,設定対象月,1),0))&lt;31,"",DATE(設定対象年,設定対象月,31))</f>
+        <v/>
+      </c>
+      <c r="AJ4" s="4" t="n"/>
+      <c r="AK4" s="4" t="n"/>
+      <c r="AN4" s="5" t="inlineStr">
+        <is>
+          <t>週</t>
+        </is>
+      </c>
+      <c r="AO4" s="5" t="inlineStr">
+        <is>
+          <t>日数</t>
+        </is>
+      </c>
+      <c r="AP4" s="5" t="inlineStr">
+        <is>
+          <t>算定日数</t>
+        </is>
+      </c>
+      <c r="AQ4" s="5" t="inlineStr">
+        <is>
+          <t>取得率</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="n"/>
+      <c r="B5" s="4" t="n"/>
+      <c r="C5" s="4" t="n"/>
+      <c r="D5" s="24" t="inlineStr">
+        <is>
+          <t>週</t>
+        </is>
+      </c>
+      <c r="E5" s="24">
+        <f>IF(E4="","","第"&amp;ROUNDUP(1/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="F5" s="24">
+        <f>IF(F4="","","第"&amp;ROUNDUP(2/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="G5" s="24">
+        <f>IF(G4="","","第"&amp;ROUNDUP(3/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="H5" s="24">
+        <f>IF(H4="","","第"&amp;ROUNDUP(4/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="I5" s="24">
+        <f>IF(I4="","","第"&amp;ROUNDUP(5/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="J5" s="24">
+        <f>IF(J4="","","第"&amp;ROUNDUP(6/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="K5" s="24">
+        <f>IF(K4="","","第"&amp;ROUNDUP(7/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="L5" s="24">
+        <f>IF(L4="","","第"&amp;ROUNDUP(8/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="M5" s="24">
+        <f>IF(M4="","","第"&amp;ROUNDUP(9/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="N5" s="24">
+        <f>IF(N4="","","第"&amp;ROUNDUP(10/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="O5" s="24">
+        <f>IF(O4="","","第"&amp;ROUNDUP(11/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="P5" s="24">
+        <f>IF(P4="","","第"&amp;ROUNDUP(12/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="Q5" s="24">
+        <f>IF(Q4="","","第"&amp;ROUNDUP(13/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="R5" s="24">
+        <f>IF(R4="","","第"&amp;ROUNDUP(14/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="S5" s="24">
+        <f>IF(S4="","","第"&amp;ROUNDUP(15/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="T5" s="24">
+        <f>IF(T4="","","第"&amp;ROUNDUP(16/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="U5" s="24">
+        <f>IF(U4="","","第"&amp;ROUNDUP(17/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="V5" s="24">
+        <f>IF(V4="","","第"&amp;ROUNDUP(18/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="W5" s="24">
+        <f>IF(W4="","","第"&amp;ROUNDUP(19/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="X5" s="24">
+        <f>IF(X4="","","第"&amp;ROUNDUP(20/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="Y5" s="24">
+        <f>IF(Y4="","","第"&amp;ROUNDUP(21/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="Z5" s="24">
+        <f>IF(Z4="","","第"&amp;ROUNDUP(22/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="AA5" s="24">
+        <f>IF(AA4="","","第"&amp;ROUNDUP(23/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="AB5" s="24">
+        <f>IF(AB4="","","第"&amp;ROUNDUP(24/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="AC5" s="24">
+        <f>IF(AC4="","","第"&amp;ROUNDUP(25/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="AD5" s="24">
+        <f>IF(AD4="","","第"&amp;ROUNDUP(26/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="AE5" s="24">
+        <f>IF(AE4="","","第"&amp;ROUNDUP(27/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="AF5" s="24">
+        <f>IF(AF4="","","第"&amp;ROUNDUP(28/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="AG5" s="24">
+        <f>IF(AG4="","","第"&amp;ROUNDUP(29/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="AH5" s="24">
+        <f>IF(AH4="","","第"&amp;ROUNDUP(30/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="AI5" s="24">
+        <f>IF(AI4="","","第"&amp;ROUNDUP(31/7,0)&amp;"週")</f>
+        <v/>
+      </c>
+      <c r="AJ5" s="4" t="n"/>
+      <c r="AK5" s="5" t="inlineStr">
+        <is>
+          <t>算定日数</t>
+        </is>
+      </c>
+      <c r="AN5" s="4" t="inlineStr">
+        <is>
+          <t>第1週</t>
+        </is>
+      </c>
+      <c r="AO5" s="4">
+        <f>COUNTIF($E$5:$AI$5,$AN5)</f>
+        <v/>
+      </c>
+      <c r="AP5" s="4">
+        <f>SUMPRODUCT(($E$5:$AI$5=$AN5)*$E$8:$AI$8)</f>
+        <v/>
+      </c>
+      <c r="AQ5" s="17">
+        <f>IFERROR($AP5/($AO5*COUNTA($B$6:$B$7)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>1階部</t>
+        </is>
+      </c>
+      <c r="C6" s="16" t="inlineStr">
+        <is>
+          <t>対象</t>
+        </is>
+      </c>
+      <c r="D6" s="16" t="n"/>
+      <c r="E6" s="16" t="n"/>
+      <c r="F6" s="16" t="n"/>
+      <c r="G6" s="16" t="n"/>
+      <c r="H6" s="16" t="n"/>
+      <c r="I6" s="16" t="n"/>
+      <c r="J6" s="16" t="n"/>
+      <c r="K6" s="16" t="n"/>
+      <c r="L6" s="16" t="n"/>
+      <c r="M6" s="16" t="n"/>
+      <c r="N6" s="16" t="n"/>
+      <c r="O6" s="16" t="n"/>
+      <c r="P6" s="16" t="n"/>
+      <c r="Q6" s="16" t="n"/>
+      <c r="R6" s="16" t="n"/>
+      <c r="S6" s="16" t="n"/>
+      <c r="T6" s="16" t="n"/>
+      <c r="U6" s="16" t="n"/>
+      <c r="V6" s="16" t="n"/>
+      <c r="W6" s="16" t="n"/>
+      <c r="X6" s="16" t="n"/>
+      <c r="Y6" s="16" t="n"/>
+      <c r="Z6" s="16" t="n"/>
+      <c r="AA6" s="16" t="n"/>
+      <c r="AB6" s="16" t="n"/>
+      <c r="AC6" s="16" t="n"/>
+      <c r="AD6" s="16" t="n"/>
+      <c r="AE6" s="16" t="n"/>
+      <c r="AF6" s="16" t="n"/>
+      <c r="AG6" s="16" t="n"/>
+      <c r="AH6" s="16" t="n"/>
+      <c r="AI6" s="16" t="n"/>
+      <c r="AJ6" s="4" t="n"/>
+      <c r="AK6" s="4">
+        <f>COUNTIF($E6:$AI6,"●")</f>
+        <v/>
+      </c>
+      <c r="AN6" s="4" t="inlineStr">
+        <is>
+          <t>第2週</t>
+        </is>
+      </c>
+      <c r="AO6" s="4">
+        <f>COUNTIF($E$5:$AI$5,$AN6)</f>
+        <v/>
+      </c>
+      <c r="AP6" s="4">
+        <f>SUMPRODUCT(($E$5:$AI$5=$AN6)*$E$8:$AI$8)</f>
+        <v/>
+      </c>
+      <c r="AQ6" s="17">
+        <f>IFERROR($AP6/($AO6*COUNTA($B$6:$B$7)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>2階部</t>
+        </is>
+      </c>
+      <c r="C7" s="16" t="inlineStr">
+        <is>
+          <t>対象</t>
+        </is>
+      </c>
+      <c r="D7" s="16" t="n"/>
+      <c r="E7" s="16" t="n"/>
+      <c r="F7" s="16" t="n"/>
+      <c r="G7" s="16" t="n"/>
+      <c r="H7" s="16" t="n"/>
+      <c r="I7" s="16" t="n"/>
+      <c r="J7" s="16" t="n"/>
+      <c r="K7" s="16" t="n"/>
+      <c r="L7" s="16" t="n"/>
+      <c r="M7" s="16" t="n"/>
+      <c r="N7" s="16" t="n"/>
+      <c r="O7" s="16" t="n"/>
+      <c r="P7" s="16" t="n"/>
+      <c r="Q7" s="16" t="n"/>
+      <c r="R7" s="16" t="n"/>
+      <c r="S7" s="16" t="n"/>
+      <c r="T7" s="16" t="n"/>
+      <c r="U7" s="16" t="n"/>
+      <c r="V7" s="16" t="n"/>
+      <c r="W7" s="16" t="n"/>
+      <c r="X7" s="16" t="n"/>
+      <c r="Y7" s="16" t="n"/>
+      <c r="Z7" s="16" t="n"/>
+      <c r="AA7" s="16" t="n"/>
+      <c r="AB7" s="16" t="n"/>
+      <c r="AC7" s="16" t="n"/>
+      <c r="AD7" s="16" t="n"/>
+      <c r="AE7" s="16" t="n"/>
+      <c r="AF7" s="16" t="n"/>
+      <c r="AG7" s="16" t="n"/>
+      <c r="AH7" s="16" t="n"/>
+      <c r="AI7" s="16" t="n"/>
+      <c r="AJ7" s="4" t="n"/>
+      <c r="AK7" s="4">
+        <f>COUNTIF($E7:$AI7,"●")</f>
+        <v/>
+      </c>
+      <c r="AN7" s="4" t="inlineStr">
+        <is>
+          <t>第3週</t>
+        </is>
+      </c>
+      <c r="AO7" s="4">
+        <f>COUNTIF($E$5:$AI$5,$AN7)</f>
+        <v/>
+      </c>
+      <c r="AP7" s="4">
+        <f>SUMPRODUCT(($E$5:$AI$5=$AN7)*$E$8:$AI$8)</f>
+        <v/>
+      </c>
+      <c r="AQ7" s="17">
+        <f>IFERROR($AP7/($AO7*COUNTA($B$6:$B$7)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="25" t="inlineStr">
+        <is>
+          <t>日別算定数</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="n"/>
+      <c r="D8" s="4" t="n"/>
+      <c r="E8" s="4">
+        <f>COUNTIF(E$6:E$7,"●")</f>
+        <v/>
+      </c>
+      <c r="F8" s="4">
+        <f>COUNTIF(F$6:F$7,"●")</f>
+        <v/>
+      </c>
+      <c r="G8" s="4">
+        <f>COUNTIF(G$6:G$7,"●")</f>
+        <v/>
+      </c>
+      <c r="H8" s="4">
+        <f>COUNTIF(H$6:H$7,"●")</f>
+        <v/>
+      </c>
+      <c r="I8" s="4">
+        <f>COUNTIF(I$6:I$7,"●")</f>
+        <v/>
+      </c>
+      <c r="J8" s="4">
+        <f>COUNTIF(J$6:J$7,"●")</f>
+        <v/>
+      </c>
+      <c r="K8" s="4">
+        <f>COUNTIF(K$6:K$7,"●")</f>
+        <v/>
+      </c>
+      <c r="L8" s="4">
+        <f>COUNTIF(L$6:L$7,"●")</f>
+        <v/>
+      </c>
+      <c r="M8" s="4">
+        <f>COUNTIF(M$6:M$7,"●")</f>
+        <v/>
+      </c>
+      <c r="N8" s="4">
+        <f>COUNTIF(N$6:N$7,"●")</f>
+        <v/>
+      </c>
+      <c r="O8" s="4">
+        <f>COUNTIF(O$6:O$7,"●")</f>
+        <v/>
+      </c>
+      <c r="P8" s="4">
+        <f>COUNTIF(P$6:P$7,"●")</f>
+        <v/>
+      </c>
+      <c r="Q8" s="4">
+        <f>COUNTIF(Q$6:Q$7,"●")</f>
+        <v/>
+      </c>
+      <c r="R8" s="4">
+        <f>COUNTIF(R$6:R$7,"●")</f>
+        <v/>
+      </c>
+      <c r="S8" s="4">
+        <f>COUNTIF(S$6:S$7,"●")</f>
+        <v/>
+      </c>
+      <c r="T8" s="4">
+        <f>COUNTIF(T$6:T$7,"●")</f>
+        <v/>
+      </c>
+      <c r="U8" s="4">
+        <f>COUNTIF(U$6:U$7,"●")</f>
+        <v/>
+      </c>
+      <c r="V8" s="4">
+        <f>COUNTIF(V$6:V$7,"●")</f>
+        <v/>
+      </c>
+      <c r="W8" s="4">
+        <f>COUNTIF(W$6:W$7,"●")</f>
+        <v/>
+      </c>
+      <c r="X8" s="4">
+        <f>COUNTIF(X$6:X$7,"●")</f>
+        <v/>
+      </c>
+      <c r="Y8" s="4">
+        <f>COUNTIF(Y$6:Y$7,"●")</f>
+        <v/>
+      </c>
+      <c r="Z8" s="4">
+        <f>COUNTIF(Z$6:Z$7,"●")</f>
+        <v/>
+      </c>
+      <c r="AA8" s="4">
+        <f>COUNTIF(AA$6:AA$7,"●")</f>
+        <v/>
+      </c>
+      <c r="AB8" s="4">
+        <f>COUNTIF(AB$6:AB$7,"●")</f>
+        <v/>
+      </c>
+      <c r="AC8" s="4">
+        <f>COUNTIF(AC$6:AC$7,"●")</f>
+        <v/>
+      </c>
+      <c r="AD8" s="4">
+        <f>COUNTIF(AD$6:AD$7,"●")</f>
+        <v/>
+      </c>
+      <c r="AE8" s="4">
+        <f>COUNTIF(AE$6:AE$7,"●")</f>
+        <v/>
+      </c>
+      <c r="AF8" s="4">
+        <f>COUNTIF(AF$6:AF$7,"●")</f>
+        <v/>
+      </c>
+      <c r="AG8" s="4">
+        <f>COUNTIF(AG$6:AG$7,"●")</f>
+        <v/>
+      </c>
+      <c r="AH8" s="4">
+        <f>COUNTIF(AH$6:AH$7,"●")</f>
+        <v/>
+      </c>
+      <c r="AI8" s="4">
+        <f>COUNTIF(AI$6:AI$7,"●")</f>
+        <v/>
+      </c>
+      <c r="AN8" s="4" t="inlineStr">
+        <is>
+          <t>第4週</t>
+        </is>
+      </c>
+      <c r="AO8" s="4">
+        <f>COUNTIF($E$5:$AI$5,$AN8)</f>
+        <v/>
+      </c>
+      <c r="AP8" s="4">
+        <f>SUMPRODUCT(($E$5:$AI$5=$AN8)*$E$8:$AI$8)</f>
+        <v/>
+      </c>
+      <c r="AQ8" s="17">
+        <f>IFERROR($AP8/($AO8*COUNTA($B$6:$B$7)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="AN9" s="4" t="inlineStr">
+        <is>
+          <t>第5週</t>
+        </is>
+      </c>
+      <c r="AO9" s="4">
+        <f>COUNTIF($E$5:$AI$5,$AN9)</f>
+        <v/>
+      </c>
+      <c r="AP9" s="4">
+        <f>SUMPRODUCT(($E$5:$AI$5=$AN9)*$E$8:$AI$8)</f>
+        <v/>
+      </c>
+      <c r="AQ9" s="17">
+        <f>IFERROR($AP9/($AO9*COUNTA($B$6:$B$7)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="28" t="inlineStr">
+        <is>
+          <t>■重度障害者支援体制加算（対象者ごとの計画・記録）</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>利用者ID</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>利用者名（任意）</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>計画作成</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>記録作成</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>確認日</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>確認者</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B13" s="16" t="n"/>
+      <c r="C13" s="16" t="n"/>
+      <c r="D13" s="16" t="n"/>
+      <c r="E13" s="16" t="n"/>
+      <c r="F13" s="18" t="n"/>
+      <c r="G13" s="16" t="n"/>
+      <c r="H13" s="16" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B14" s="16" t="n"/>
+      <c r="C14" s="16" t="n"/>
+      <c r="D14" s="16" t="n"/>
+      <c r="E14" s="16" t="n"/>
+      <c r="F14" s="18" t="n"/>
+      <c r="G14" s="16" t="n"/>
+      <c r="H14" s="16" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B15" s="16" t="n"/>
+      <c r="C15" s="16" t="n"/>
+      <c r="D15" s="16" t="n"/>
+      <c r="E15" s="16" t="n"/>
+      <c r="F15" s="18" t="n"/>
+      <c r="G15" s="16" t="n"/>
+      <c r="H15" s="16" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B16" s="16" t="n"/>
+      <c r="C16" s="16" t="n"/>
+      <c r="D16" s="16" t="n"/>
+      <c r="E16" s="16" t="n"/>
+      <c r="F16" s="18" t="n"/>
+      <c r="G16" s="16" t="n"/>
+      <c r="H16" s="16" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B17" s="16" t="n"/>
+      <c r="C17" s="16" t="n"/>
+      <c r="D17" s="16" t="n"/>
+      <c r="E17" s="16" t="n"/>
+      <c r="F17" s="18" t="n"/>
+      <c r="G17" s="16" t="n"/>
+      <c r="H17" s="16" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B18" s="16" t="n"/>
+      <c r="C18" s="16" t="n"/>
+      <c r="D18" s="16" t="n"/>
+      <c r="E18" s="16" t="n"/>
+      <c r="F18" s="18" t="n"/>
+      <c r="G18" s="16" t="n"/>
+      <c r="H18" s="16" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B19" s="16" t="n"/>
+      <c r="C19" s="16" t="n"/>
+      <c r="D19" s="16" t="n"/>
+      <c r="E19" s="16" t="n"/>
+      <c r="F19" s="18" t="n"/>
+      <c r="G19" s="16" t="n"/>
+      <c r="H19" s="16" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B20" s="16" t="n"/>
+      <c r="C20" s="16" t="n"/>
+      <c r="D20" s="16" t="n"/>
+      <c r="E20" s="16" t="n"/>
+      <c r="F20" s="18" t="n"/>
+      <c r="G20" s="16" t="n"/>
+      <c r="H20" s="16" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B21" s="16" t="n"/>
+      <c r="C21" s="16" t="n"/>
+      <c r="D21" s="16" t="n"/>
+      <c r="E21" s="16" t="n"/>
+      <c r="F21" s="18" t="n"/>
+      <c r="G21" s="16" t="n"/>
+      <c r="H21" s="16" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="B22" s="16" t="n"/>
+      <c r="C22" s="16" t="n"/>
+      <c r="D22" s="16" t="n"/>
+      <c r="E22" s="16" t="n"/>
+      <c r="F22" s="18" t="n"/>
+      <c r="G22" s="16" t="n"/>
+      <c r="H22" s="16" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="13" t="inlineStr">
+        <is>
+          <t>判定：計画・記録がすべて〇なら算定可</t>
+        </is>
+      </c>
+      <c r="D24">
+        <f>IF(COUNTIF($D13:$E22,"✕")&gt;0,"要対応","問題なし")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="28" t="inlineStr">
+        <is>
+          <t>■福祉専門職員配置等加算</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>職員名</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>常勤/非常勤</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>社福</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>介福</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>精保</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>公認心理師</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>勤続3年以上</t>
+        </is>
+      </c>
+      <c r="I27" s="29" t="inlineStr">
+        <is>
+          <t>有資格</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B28" s="16" t="n"/>
+      <c r="C28" s="16" t="n"/>
+      <c r="D28" s="16" t="n"/>
+      <c r="E28" s="16" t="n"/>
+      <c r="F28" s="16" t="n"/>
+      <c r="G28" s="16" t="n"/>
+      <c r="H28" s="16" t="n"/>
+      <c r="I28">
+        <f>IF($B28="","",IF(COUNTIF($D28:$G28,"〇")&gt;0,1,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B29" s="16" t="n"/>
+      <c r="C29" s="16" t="n"/>
+      <c r="D29" s="16" t="n"/>
+      <c r="E29" s="16" t="n"/>
+      <c r="F29" s="16" t="n"/>
+      <c r="G29" s="16" t="n"/>
+      <c r="H29" s="16" t="n"/>
+      <c r="I29">
+        <f>IF($B29="","",IF(COUNTIF($D29:$G29,"〇")&gt;0,1,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B30" s="16" t="n"/>
+      <c r="C30" s="16" t="n"/>
+      <c r="D30" s="16" t="n"/>
+      <c r="E30" s="16" t="n"/>
+      <c r="F30" s="16" t="n"/>
+      <c r="G30" s="16" t="n"/>
+      <c r="H30" s="16" t="n"/>
+      <c r="I30">
+        <f>IF($B30="","",IF(COUNTIF($D30:$G30,"〇")&gt;0,1,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B31" s="16" t="n"/>
+      <c r="C31" s="16" t="n"/>
+      <c r="D31" s="16" t="n"/>
+      <c r="E31" s="16" t="n"/>
+      <c r="F31" s="16" t="n"/>
+      <c r="G31" s="16" t="n"/>
+      <c r="H31" s="16" t="n"/>
+      <c r="I31">
+        <f>IF($B31="","",IF(COUNTIF($D31:$G31,"〇")&gt;0,1,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B32" s="16" t="n"/>
+      <c r="C32" s="16" t="n"/>
+      <c r="D32" s="16" t="n"/>
+      <c r="E32" s="16" t="n"/>
+      <c r="F32" s="16" t="n"/>
+      <c r="G32" s="16" t="n"/>
+      <c r="H32" s="16" t="n"/>
+      <c r="I32">
+        <f>IF($B32="","",IF(COUNTIF($D32:$G32,"〇")&gt;0,1,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B33" s="16" t="n"/>
+      <c r="C33" s="16" t="n"/>
+      <c r="D33" s="16" t="n"/>
+      <c r="E33" s="16" t="n"/>
+      <c r="F33" s="16" t="n"/>
+      <c r="G33" s="16" t="n"/>
+      <c r="H33" s="16" t="n"/>
+      <c r="I33">
+        <f>IF($B33="","",IF(COUNTIF($D33:$G33,"〇")&gt;0,1,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B34" s="16" t="n"/>
+      <c r="C34" s="16" t="n"/>
+      <c r="D34" s="16" t="n"/>
+      <c r="E34" s="16" t="n"/>
+      <c r="F34" s="16" t="n"/>
+      <c r="G34" s="16" t="n"/>
+      <c r="H34" s="16" t="n"/>
+      <c r="I34">
+        <f>IF($B34="","",IF(COUNTIF($D34:$G34,"〇")&gt;0,1,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B35" s="16" t="n"/>
+      <c r="C35" s="16" t="n"/>
+      <c r="D35" s="16" t="n"/>
+      <c r="E35" s="16" t="n"/>
+      <c r="F35" s="16" t="n"/>
+      <c r="G35" s="16" t="n"/>
+      <c r="H35" s="16" t="n"/>
+      <c r="I35">
+        <f>IF($B35="","",IF(COUNTIF($D35:$G35,"〇")&gt;0,1,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B36" s="16" t="n"/>
+      <c r="C36" s="16" t="n"/>
+      <c r="D36" s="16" t="n"/>
+      <c r="E36" s="16" t="n"/>
+      <c r="F36" s="16" t="n"/>
+      <c r="G36" s="16" t="n"/>
+      <c r="H36" s="16" t="n"/>
+      <c r="I36">
+        <f>IF($B36="","",IF(COUNTIF($D36:$G36,"〇")&gt;0,1,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="B37" s="16" t="n"/>
+      <c r="C37" s="16" t="n"/>
+      <c r="D37" s="16" t="n"/>
+      <c r="E37" s="16" t="n"/>
+      <c r="F37" s="16" t="n"/>
+      <c r="G37" s="16" t="n"/>
+      <c r="H37" s="16" t="n"/>
+      <c r="I37">
+        <f>IF($B37="","",IF(COUNTIF($D37:$G37,"〇")&gt;0,1,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="B38" s="16" t="n"/>
+      <c r="C38" s="16" t="n"/>
+      <c r="D38" s="16" t="n"/>
+      <c r="E38" s="16" t="n"/>
+      <c r="F38" s="16" t="n"/>
+      <c r="G38" s="16" t="n"/>
+      <c r="H38" s="16" t="n"/>
+      <c r="I38">
+        <f>IF($B38="","",IF(COUNTIF($D38:$G38,"〇")&gt;0,1,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="B39" s="16" t="n"/>
+      <c r="C39" s="16" t="n"/>
+      <c r="D39" s="16" t="n"/>
+      <c r="E39" s="16" t="n"/>
+      <c r="F39" s="16" t="n"/>
+      <c r="G39" s="16" t="n"/>
+      <c r="H39" s="16" t="n"/>
+      <c r="I39">
+        <f>IF($B39="","",IF(COUNTIF($D39:$G39,"〇")&gt;0,1,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="B40" s="16" t="n"/>
+      <c r="C40" s="16" t="n"/>
+      <c r="D40" s="16" t="n"/>
+      <c r="E40" s="16" t="n"/>
+      <c r="F40" s="16" t="n"/>
+      <c r="G40" s="16" t="n"/>
+      <c r="H40" s="16" t="n"/>
+      <c r="I40">
+        <f>IF($B40="","",IF(COUNTIF($D40:$G40,"〇")&gt;0,1,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="B41" s="16" t="n"/>
+      <c r="C41" s="16" t="n"/>
+      <c r="D41" s="16" t="n"/>
+      <c r="E41" s="16" t="n"/>
+      <c r="F41" s="16" t="n"/>
+      <c r="G41" s="16" t="n"/>
+      <c r="H41" s="16" t="n"/>
+      <c r="I41">
+        <f>IF($B41="","",IF(COUNTIF($D41:$G41,"〇")&gt;0,1,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B42" s="16" t="n"/>
+      <c r="C42" s="16" t="n"/>
+      <c r="D42" s="16" t="n"/>
+      <c r="E42" s="16" t="n"/>
+      <c r="F42" s="16" t="n"/>
+      <c r="G42" s="16" t="n"/>
+      <c r="H42" s="16" t="n"/>
+      <c r="I42">
+        <f>IF($B42="","",IF(COUNTIF($D42:$G42,"〇")&gt;0,1,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="B43" s="16" t="n"/>
+      <c r="C43" s="16" t="n"/>
+      <c r="D43" s="16" t="n"/>
+      <c r="E43" s="16" t="n"/>
+      <c r="F43" s="16" t="n"/>
+      <c r="G43" s="16" t="n"/>
+      <c r="H43" s="16" t="n"/>
+      <c r="I43">
+        <f>IF($B43="","",IF(COUNTIF($D43:$G43,"〇")&gt;0,1,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="B44" s="16" t="n"/>
+      <c r="C44" s="16" t="n"/>
+      <c r="D44" s="16" t="n"/>
+      <c r="E44" s="16" t="n"/>
+      <c r="F44" s="16" t="n"/>
+      <c r="G44" s="16" t="n"/>
+      <c r="H44" s="16" t="n"/>
+      <c r="I44">
+        <f>IF($B44="","",IF(COUNTIF($D44:$G44,"〇")&gt;0,1,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="B45" s="16" t="n"/>
+      <c r="C45" s="16" t="n"/>
+      <c r="D45" s="16" t="n"/>
+      <c r="E45" s="16" t="n"/>
+      <c r="F45" s="16" t="n"/>
+      <c r="G45" s="16" t="n"/>
+      <c r="H45" s="16" t="n"/>
+      <c r="I45">
+        <f>IF($B45="","",IF(COUNTIF($D45:$G45,"〇")&gt;0,1,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="B46" s="16" t="n"/>
+      <c r="C46" s="16" t="n"/>
+      <c r="D46" s="16" t="n"/>
+      <c r="E46" s="16" t="n"/>
+      <c r="F46" s="16" t="n"/>
+      <c r="G46" s="16" t="n"/>
+      <c r="H46" s="16" t="n"/>
+      <c r="I46">
+        <f>IF($B46="","",IF(COUNTIF($D46:$G46,"〇")&gt;0,1,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="B47" s="16" t="n"/>
+      <c r="C47" s="16" t="n"/>
+      <c r="D47" s="16" t="n"/>
+      <c r="E47" s="16" t="n"/>
+      <c r="F47" s="16" t="n"/>
+      <c r="G47" s="16" t="n"/>
+      <c r="H47" s="16" t="n"/>
+      <c r="I47">
+        <f>IF($B47="","",IF(COUNTIF($D47:$G47,"〇")&gt;0,1,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>常勤数</t>
+        </is>
+      </c>
+      <c r="B49">
+        <f>COUNTIF($C28:$C47,"常勤")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>常勤比率</t>
+        </is>
+      </c>
+      <c r="B50" s="30">
+        <f>IFERROR($B49/COUNTA($B28:$B47),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>有資格者比率（Ⅰ要件35%）</t>
+        </is>
+      </c>
+      <c r="B51" s="30">
+        <f>IFERROR(SUM($I28:$I47)/COUNTA($B28:$B47),"")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="4">
+    <dataValidation sqref="E6:AI7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"●,✕"</formula1>
+    </dataValidation>
+    <dataValidation sqref="D13:E22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"〇,✕,対象外"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C28:C47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"常勤,非常勤"</formula1>
+    </dataValidation>
+    <dataValidation sqref="D28:H47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"〇"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q63"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="28" customWidth="1" min="17" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>案件ID</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>対象施設</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>kintone名/イニシャル</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>希望種別</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>相談元</t>
+        </is>
+      </c>
+      <c r="G1" s="5" t="inlineStr">
+        <is>
+          <t>発掘日</t>
+        </is>
+      </c>
+      <c r="H1" s="5" t="inlineStr">
+        <is>
+          <t>見学日</t>
+        </is>
+      </c>
+      <c r="I1" s="5" t="inlineStr">
+        <is>
+          <t>体験日</t>
+        </is>
+      </c>
+      <c r="J1" s="5" t="inlineStr">
+        <is>
+          <t>実調日</t>
+        </is>
+      </c>
+      <c r="K1" s="5" t="inlineStr">
+        <is>
+          <t>契約日</t>
+        </is>
+      </c>
+      <c r="L1" s="5" t="inlineStr">
+        <is>
+          <t>入居/利用開始日</t>
+        </is>
+      </c>
+      <c r="M1" s="5" t="inlineStr">
+        <is>
+          <t>ステータス</t>
+        </is>
+      </c>
+      <c r="N1" s="5" t="inlineStr">
+        <is>
+          <t>次回追客日</t>
+        </is>
+      </c>
+      <c r="O1" s="5" t="inlineStr">
+        <is>
+          <t>担当者</t>
+        </is>
+      </c>
+      <c r="P1" s="5" t="inlineStr">
+        <is>
+          <t>停滞日数</t>
+        </is>
+      </c>
+      <c r="Q1" s="5" t="inlineStr">
+        <is>
+          <t>メモ</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4">
+        <f>IF($C2="","","C"&amp;TEXT(ROW()-1,"000"))</f>
+        <v/>
+      </c>
+      <c r="B2" s="4">
+        <f>IF($C2="","",設定対象施設)</f>
+        <v/>
+      </c>
+      <c r="C2" s="16" t="n"/>
+      <c r="D2" s="16" t="n"/>
+      <c r="E2" s="16" t="n"/>
+      <c r="F2" s="16" t="n"/>
+      <c r="G2" s="18" t="n"/>
+      <c r="H2" s="18" t="n"/>
+      <c r="I2" s="18" t="n"/>
+      <c r="J2" s="18" t="n"/>
+      <c r="K2" s="18" t="n"/>
+      <c r="L2" s="18" t="n"/>
+      <c r="M2" s="16" t="n"/>
+      <c r="N2" s="18" t="n"/>
+      <c r="O2" s="16" t="n"/>
+      <c r="P2" s="4">
+        <f>IF($C2="","",IF($M2="入居","—",TODAY()-MAX($G2:$L2)))</f>
+        <v/>
+      </c>
+      <c r="Q2" s="16" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4">
+        <f>IF($C3="","","C"&amp;TEXT(ROW()-1,"000"))</f>
+        <v/>
+      </c>
+      <c r="B3" s="4">
+        <f>IF($C3="","",設定対象施設)</f>
+        <v/>
+      </c>
+      <c r="C3" s="16" t="n"/>
+      <c r="D3" s="16" t="n"/>
+      <c r="E3" s="16" t="n"/>
+      <c r="F3" s="16" t="n"/>
+      <c r="G3" s="18" t="n"/>
+      <c r="H3" s="18" t="n"/>
+      <c r="I3" s="18" t="n"/>
+      <c r="J3" s="18" t="n"/>
+      <c r="K3" s="18" t="n"/>
+      <c r="L3" s="18" t="n"/>
+      <c r="M3" s="16" t="n"/>
+      <c r="N3" s="18" t="n"/>
+      <c r="O3" s="16" t="n"/>
+      <c r="P3" s="4">
+        <f>IF($C3="","",IF($M3="入居","—",TODAY()-MAX($G3:$L3)))</f>
+        <v/>
+      </c>
+      <c r="Q3" s="16" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="4">
+        <f>IF($C4="","","C"&amp;TEXT(ROW()-1,"000"))</f>
+        <v/>
+      </c>
+      <c r="B4" s="4">
+        <f>IF($C4="","",設定対象施設)</f>
+        <v/>
+      </c>
+      <c r="C4" s="16" t="n"/>
+      <c r="D4" s="16" t="n"/>
+      <c r="E4" s="16" t="n"/>
+      <c r="F4" s="16" t="n"/>
+      <c r="G4" s="18" t="n"/>
+      <c r="H4" s="18" t="n"/>
+      <c r="I4" s="18" t="n"/>
+      <c r="J4" s="18" t="n"/>
+      <c r="K4" s="18" t="n"/>
+      <c r="L4" s="18" t="n"/>
+      <c r="M4" s="16" t="n"/>
+      <c r="N4" s="18" t="n"/>
+      <c r="O4" s="16" t="n"/>
+      <c r="P4" s="4">
+        <f>IF($C4="","",IF($M4="入居","—",TODAY()-MAX($G4:$L4)))</f>
+        <v/>
+      </c>
+      <c r="Q4" s="16" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="4">
+        <f>IF($C5="","","C"&amp;TEXT(ROW()-1,"000"))</f>
+        <v/>
+      </c>
+      <c r="B5" s="4">
+        <f>IF($C5="","",設定対象施設)</f>
+        <v/>
+      </c>
+      <c r="C5" s="16" t="n"/>
+      <c r="D5" s="16" t="n"/>
+      <c r="E5" s="16" t="n"/>
+      <c r="F5" s="16" t="n"/>
+      <c r="G5" s="18" t="n"/>
+      <c r="H5" s="18" t="n"/>
+      <c r="I5" s="18" t="n"/>
+      <c r="J5" s="18" t="n"/>
+      <c r="K5" s="18" t="n"/>
+      <c r="L5" s="18" t="n"/>
+      <c r="M5" s="16" t="n"/>
+      <c r="N5" s="18" t="n"/>
+      <c r="O5" s="16" t="n"/>
+      <c r="P5" s="4">
+        <f>IF($C5="","",IF($M5="入居","—",TODAY()-MAX($G5:$L5)))</f>
+        <v/>
+      </c>
+      <c r="Q5" s="16" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="4">
+        <f>IF($C6="","","C"&amp;TEXT(ROW()-1,"000"))</f>
+        <v/>
+      </c>
+      <c r="B6" s="4">
+        <f>IF($C6="","",設定対象施設)</f>
+        <v/>
+      </c>
+      <c r="C6" s="16" t="n"/>
+      <c r="D6" s="16" t="n"/>
+      <c r="E6" s="16" t="n"/>
+      <c r="F6" s="16" t="n"/>
+      <c r="G6" s="18" t="n"/>
+      <c r="H6" s="18" t="n"/>
+      <c r="I6" s="18" t="n"/>
+      <c r="J6" s="18" t="n"/>
+      <c r="K6" s="18" t="n"/>
+      <c r="L6" s="18" t="n"/>
+      <c r="M6" s="16" t="n"/>
+      <c r="N6" s="18" t="n"/>
+      <c r="O6" s="16" t="n"/>
+      <c r="P6" s="4">
+        <f>IF($C6="","",IF($M6="入居","—",TODAY()-MAX($G6:$L6)))</f>
+        <v/>
+      </c>
+      <c r="Q6" s="16" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4">
+        <f>IF($C7="","","C"&amp;TEXT(ROW()-1,"000"))</f>
+        <v/>
+      </c>
+      <c r="B7" s="4">
+        <f>IF($C7="","",設定対象施設)</f>
+        <v/>
+      </c>
+      <c r="C7" s="16" t="n"/>
+      <c r="D7" s="16" t="n"/>
+      <c r="E7" s="16" t="n"/>
+      <c r="F7" s="16" t="n"/>
+      <c r="G7" s="18" t="n"/>
+      <c r="H7" s="18" t="n"/>
+      <c r="I7" s="18" t="n"/>
+      <c r="J7" s="18" t="n"/>
+      <c r="K7" s="18" t="n"/>
+      <c r="L7" s="18" t="n"/>
+      <c r="M7" s="16" t="n"/>
+      <c r="N7" s="18" t="n"/>
+      <c r="O7" s="16" t="n"/>
+      <c r="P7" s="4">
+        <f>IF($C7="","",IF($M7="入居","—",TODAY()-MAX($G7:$L7)))</f>
+        <v/>
+      </c>
+      <c r="Q7" s="16" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4">
+        <f>IF($C8="","","C"&amp;TEXT(ROW()-1,"000"))</f>
+        <v/>
+      </c>
+      <c r="B8" s="4">
+        <f>IF($C8="","",設定対象施設)</f>
+        <v/>
+      </c>
+      <c r="C8" s="16" t="n"/>
+      <c r="D8" s="16" t="n"/>
+      <c r="E8" s="16" t="n"/>
+      <c r="F8" s="16" t="n"/>
+      <c r="G8" s="18" t="n"/>
+      <c r="H8" s="18" t="n"/>
+      <c r="I8" s="18" t="n"/>
+      <c r="J8" s="18" t="n"/>
+      <c r="K8" s="18" t="n"/>
+      <c r="L8" s="18" t="n"/>
+      <c r="M8" s="16" t="n"/>
+      <c r="N8" s="18" t="n"/>
+      <c r="O8" s="16" t="n"/>
+      <c r="P8" s="4">
+        <f>IF($C8="","",IF($M8="入居","—",TODAY()-MAX($G8:$L8)))</f>
+        <v/>
+      </c>
+      <c r="Q8" s="16" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="4">
+        <f>IF($C9="","","C"&amp;TEXT(ROW()-1,"000"))</f>
+        <v/>
+      </c>
+      <c r="B9" s="4">
+        <f>IF($C9="","",設定対象施設)</f>
+        <v/>
+      </c>
+      <c r="C9" s="16" t="n"/>
+      <c r="D9" s="16" t="n"/>
+      <c r="E9" s="16" t="n"/>
+      <c r="F9" s="16" t="n"/>
+      <c r="G9" s="18" t="n"/>
+      <c r="H9" s="18" t="n"/>
+      <c r="I9" s="18" t="n"/>
+      <c r="J9" s="18" t="n"/>
+      <c r="K9" s="18" t="n"/>
+      <c r="L9" s="18" t="n"/>
+      <c r="M9" s="16" t="n"/>
+      <c r="N9" s="18" t="n"/>
+      <c r="O9" s="16" t="n"/>
+      <c r="P9" s="4">
+        <f>IF($C9="","",IF($M9="入居","—",TODAY()-MAX($G9:$L9)))</f>
+        <v/>
+      </c>
+      <c r="Q9" s="16" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="4">
+        <f>IF($C10="","","C"&amp;TEXT(ROW()-1,"000"))</f>
+        <v/>
+      </c>
+      <c r="B10" s="4">
+        <f>IF($C10="","",設定対象施設)</f>
+        <v/>
+      </c>
+      <c r="C10" s="16" t="n"/>
+      <c r="D10" s="16" t="n"/>
+      <c r="E10" s="16" t="n"/>
+      <c r="F10" s="16" t="n"/>
+      <c r="G10" s="18" t="n"/>
+      <c r="H10" s="18" t="n"/>
+      <c r="I10" s="18" t="n"/>
+      <c r="J10" s="18" t="n"/>
+      <c r="K10" s="18" t="n"/>
+      <c r="L10" s="18" t="n"/>
+      <c r="M10" s="16" t="n"/>
+      <c r="N10" s="18" t="n"/>
+      <c r="O10" s="16" t="n"/>
+      <c r="P10" s="4">
+        <f>IF($C10="","",IF($M10="入居","—",TODAY()-MAX($G10:$L10)))</f>
+        <v/>
+      </c>
+      <c r="Q10" s="16" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="4">
+        <f>IF($C11="","","C"&amp;TEXT(ROW()-1,"000"))</f>
+        <v/>
+      </c>
+      <c r="B11" s="4">
+        <f>IF($C11="","",設定対象施設)</f>
+        <v/>
+      </c>
+      <c r="C11" s="16" t="n"/>
+      <c r="D11" s="16" t="n"/>
+      <c r="E11" s="16" t="n"/>
+      <c r="F11" s="16" t="n"/>
+      <c r="G11" s="18" t="n"/>
+      <c r="H11" s="18" t="n"/>
+      <c r="I11" s="18" t="n"/>
+      <c r="J11" s="18" t="n"/>
+      <c r="K11" s="18" t="n"/>
+      <c r="L11" s="18" t="n"/>
+      <c r="M11" s="16" t="n"/>
+      <c r="N11" s="18" t="n"/>
+      <c r="O11" s="16" t="n"/>
+      <c r="P11" s="4">
+        <f>IF($C11="","",IF($M11="入居","—",TODAY()-MAX($G11:$L11)))</f>
+        <v/>
+      </c>
+      <c r="Q11" s="16" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="4">
+        <f>IF($C12="","","C"&amp;TEXT(ROW()-1,"000"))</f>
+        <v/>
+      </c>
+      <c r="B12" s="4">
+        <f>IF($C12="","",設定対象施設)</f>
+        <v/>
+      </c>
+      <c r="C12" s="16" t="n"/>
+      <c r="D12" s="16" t="n"/>
+      <c r="E12" s="16" t="n"/>
+      <c r="F12" s="16" t="n"/>
+      <c r="G12" s="18" t="n"/>
+      <c r="H12" s="18" t="n"/>
+      <c r="I12" s="18" t="n"/>
+      <c r="J12" s="18" t="n"/>
+      <c r="K12" s="18" t="n"/>
+      <c r="L12" s="18" t="n"/>
+      <c r="M12" s="16" t="n"/>
+      <c r="N12" s="18" t="n"/>
+      <c r="O12" s="16" t="n"/>
+      <c r="P12" s="4">
+        <f>IF($C12="","",IF($M12="入居","—",TODAY()-MAX($G12:$L12)))</f>
+        <v/>
+      </c>
+      <c r="Q12" s="16" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="4">
+        <f>IF($C13="","","C"&amp;TEXT(ROW()-1,"000"))</f>
+        <v/>
+      </c>
+      <c r="B13" s="4">
+        <f>IF($C13="","",設定対象施設)</f>
+        <v/>
+      </c>
+      <c r="C13" s="16" t="n"/>
+      <c r="D13" s="16" t="n"/>
+      <c r="E13" s="16" t="n"/>
+      <c r="F13" s="16" t="n"/>
+      <c r="G13" s="18" t="n"/>
+      <c r="H13" s="18" t="n"/>
+      <c r="I13" s="18" t="n"/>
+      <c r="J13" s="18" t="n"/>
+      <c r="K13" s="18" t="n"/>
+      <c r="L13" s="18" t="n"/>
+      <c r="M13" s="16" t="n"/>
+      <c r="N13" s="18" t="n"/>
+      <c r="O13" s="16" t="n"/>
+      <c r="P13" s="4">
+        <f>IF($C13="","",IF($M13="入居","—",TODAY()-MAX($G13:$L13)))</f>
+        <v/>
+      </c>
+      <c r="Q13" s="16" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="4">
+        <f>IF($C14="","","C"&amp;TEXT(ROW()-1,"000"))</f>
+        <v/>
+      </c>
+      <c r="B14" s="4">
+        <f>IF($C14="","",設定対象施設)</f>
+        <v/>
+      </c>
+      <c r="C14" s="16" t="n"/>
+      <c r="D14" s="16" t="n"/>
+      <c r="E14" s="16" t="n"/>
+      <c r="F14" s="16" t="n"/>
+      <c r="G14" s="18" t="n"/>
+      <c r="H14" s="18" t="n"/>
+      <c r="I14" s="18" t="n"/>
+      <c r="J14" s="18" t="n"/>
+      <c r="K14" s="18" t="n"/>
+      <c r="L14" s="18" t="n"/>
+      <c r="M14" s="16" t="n"/>
+      <c r="N14" s="18" t="n"/>
+      <c r="O14" s="16" t="n"/>
+      <c r="P14" s="4">
+        <f>IF($C14="","",IF($M14="入居","—",TODAY()-MAX($G14:$L14)))</f>
+        <v/>
+      </c>
+      <c r="Q14" s="16" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="4">
+        <f>IF($C15="","","C"&amp;TEXT(ROW()-1,"000"))</f>
+        <v/>
+      </c>
+      <c r="B15" s="4">
+        <f>IF($C15="","",設定対象施設)</f>
+        <v/>
+      </c>
+      <c r="C15" s="16" t="n"/>
+      <c r="D15" s="16" t="n"/>
+      <c r="E15" s="16" t="n"/>
+      <c r="F15" s="16" t="n"/>
+      <c r="G15" s="18" t="n"/>
+      <c r="H15" s="18" t="n"/>
+      <c r="I15" s="18" t="n"/>
+      <c r="J15" s="18" t="n"/>
+      <c r="K15" s="18" t="n"/>
+      <c r="L15" s="18" t="n"/>
+      <c r="M15" s="16" t="n"/>
+      <c r="N15" s="18" t="n"/>
+      <c r="O15" s="16" t="n"/>
+      <c r="P15" s="4">
+        <f>IF($C15="","",IF($M15="入居","—",TODAY()-MAX($G15:$L15)))</f>
+        <v/>
+      </c>
+      <c r="Q15" s="16" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="4">
+        <f>IF($C16="","","C"&amp;TEXT(ROW()-1,"000"))</f>
+        <v/>
+      </c>
+      <c r="B16" s="4">
+        <f>IF($C16="","",設定対象施設)</f>
+        <v/>
+      </c>
+      <c r="C16" s="16" t="n"/>
+      <c r="D16" s="16" t="n"/>
+      <c r="E16" s="16" t="n"/>
+      <c r="F16" s="16" t="n"/>
+      <c r="G16" s="18" t="n"/>
+      <c r="H16" s="18" t="n"/>
+      <c r="I16" s="18" t="n"/>
+      <c r="J16" s="18" t="n"/>
+      <c r="K16" s="18" t="n"/>
+      <c r="L16" s="18" t="n"/>
+      <c r="M16" s="16" t="n"/>
+      <c r="N16" s="18" t="n"/>
+      <c r="O16" s="16" t="n"/>
+      <c r="P16" s="4">
+        <f>IF($C16="","",IF($M16="入居","—",TODAY()-MAX($G16:$L16)))</f>
+        <v/>
+      </c>
+      <c r="Q16" s="16" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="4">
+        <f>IF($C17="","","C"&amp;TEXT(ROW()-1,"000"))</f>
+        <v/>
+      </c>
+      <c r="B17" s="4">
+        <f>IF($C17="","",設定対象施設)</f>
+        <v/>
+      </c>
+      <c r="C17" s="16" t="n"/>
+      <c r="D17" s="16" t="n"/>
+      <c r="E17" s="16" t="n"/>
+      <c r="F17" s="16" t="n"/>
+      <c r="G17" s="18" t="n"/>
+      <c r="H17" s="18" t="n"/>
+      <c r="I17" s="18" t="n"/>
+      <c r="J17" s="18" t="n"/>
+      <c r="K17" s="18" t="n"/>
+      <c r="L17" s="18" t="n"/>
+      <c r="M17" s="16" t="n"/>
+      <c r="N17" s="18" t="n"/>
+      <c r="O17" s="16" t="n"/>
+      <c r="P17" s="4">
+        <f>IF($C17="","",IF($M17="入居","—",TODAY()-MAX($G17:$L17)))</f>
+        <v/>
+      </c>
+      <c r="Q17" s="16" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="4">
+        <f>IF($C18="","","C"&amp;TEXT(ROW()-1,"000"))</f>
+        <v/>
+      </c>
+      <c r="B18" s="4">
+        <f>IF($C18="","",設定対象施設)</f>
+        <v/>
+      </c>
+      <c r="C18" s="16" t="n"/>
+      <c r="D18" s="16" t="n"/>
+      <c r="E18" s="16" t="n"/>
+      <c r="F18" s="16" t="n"/>
+      <c r="G18" s="18" t="n"/>
+      <c r="H18" s="18" t="n"/>
+      <c r="I18" s="18" t="n"/>
+      <c r="J18" s="18" t="n"/>
+      <c r="K18" s="18" t="n"/>
+      <c r="L18" s="18" t="n"/>
+      <c r="M18" s="16" t="n"/>
+      <c r="N18" s="18" t="n"/>
+      <c r="O18" s="16" t="n"/>
+      <c r="P18" s="4">
+        <f>IF($C18="","",IF($M18="入居","—",TODAY()-MAX($G18:$L18)))</f>
+        <v/>
+      </c>
+      <c r="Q18" s="16" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="4">
+        <f>IF($C19="","","C"&amp;TEXT(ROW()-1,"000"))</f>
+        <v/>
+      </c>
+      <c r="B19" s="4">
+        <f>IF($C19="","",設定対象施設)</f>
+        <v/>
+      </c>
+      <c r="C19" s="16" t="n"/>
+      <c r="D19" s="16" t="n"/>
+      <c r="E19" s="16" t="n"/>
+      <c r="F19" s="16" t="n"/>
+      <c r="G19" s="18" t="n"/>
+      <c r="H19" s="18" t="n"/>
+      <c r="I19" s="18" t="n"/>
+      <c r="J19" s="18" t="n"/>
+      <c r="K19" s="18" t="n"/>
+      <c r="L19" s="18" t="n"/>
+      <c r="M19" s="16" t="n"/>
+      <c r="N19" s="18" t="n"/>
+      <c r="O19" s="16" t="n"/>
+      <c r="P19" s="4">
+        <f>IF($C19="","",IF($M19="入居","—",TODAY()-MAX($G19:$L19)))</f>
+        <v/>
+      </c>
+      <c r="Q19" s="16" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="4">
+        <f>IF($C20="","","C"&amp;TEXT(ROW()-1,"000"))</f>
+        <v/>
+      </c>
+      <c r="B20" s="4">
+        <f>IF($C20="","",設定対象施設)</f>
+        <v/>
+      </c>
+      <c r="C20" s="16" t="n"/>
+      <c r="D20" s="16" t="n"/>
+      <c r="E20" s="16" t="n"/>
+      <c r="F20" s="16" t="n"/>
+      <c r="G20" s="18" t="n"/>
+      <c r="H20" s="18" t="n"/>
+      <c r="I20" s="18" t="n"/>
+      <c r="J20" s="18" t="n"/>
+      <c r="K20" s="18" t="n"/>
+      <c r="L20" s="18" t="n"/>
+      <c r="M20" s="16" t="n"/>
+      <c r="N20" s="18" t="n"/>
+      <c r="O20" s="16" t="n"/>
+      <c r="P20" s="4">
+        <f>IF($C20="","",IF($M20="入居","—",TODAY()-MAX($G20:$L20)))</f>
+        <v/>
+      </c>
+      <c r="Q20" s="16" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="4">
+        <f>IF($C21="","","C"&amp;TEXT(ROW()-1,"000"))</f>
+        <v/>
+      </c>
+      <c r="B21" s="4">
+        <f>IF($C21="","",設定対象施設)</f>
+        <v/>
+      </c>
+      <c r="C21" s="16" t="n"/>
+      <c r="D21" s="16" t="n"/>
+      <c r="E21" s="16" t="n"/>
+      <c r="F21" s="16" t="n"/>
+      <c r="G21" s="18" t="n"/>
+      <c r="H21" s="18" t="n"/>
+      <c r="I21" s="18" t="n"/>
+      <c r="J21" s="18" t="n"/>
+      <c r="K21" s="18" t="n"/>
+      <c r="L21" s="18" t="n"/>
+      <c r="M21" s="16" t="n"/>
+      <c r="N21" s="18" t="n"/>
+      <c r="O21" s="16" t="n"/>
+      <c r="P21" s="4">
+        <f>IF($C21="","",IF($M21="入居","—",TODAY()-MAX($G21:$L21)))</f>
+        <v/>
+      </c>
+      <c r="Q21" s="16" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="4">
+        <f>IF($C22="","","C"&amp;TEXT(ROW()-1,"000"))</f>
+        <v/>
+      </c>
+      <c r="B22" s="4">
+        <f>IF($C22="","",設定対象施設)</f>
+        <v/>
+      </c>
+      <c r="C22" s="16" t="n"/>
+      <c r="D22" s="16" t="n"/>
+      <c r="E22" s="16" t="n"/>
+      <c r="F22" s="16" t="n"/>
+      <c r="G22" s="18" t="n"/>
+      <c r="H22" s="18" t="n"/>
+      <c r="I22" s="18" t="n"/>
+      <c r="J22" s="18" t="n"/>
+      <c r="K22" s="18" t="n"/>
+      <c r="L22" s="18" t="n"/>
+      <c r="M22" s="16" t="n"/>
+      <c r="N22" s="18" t="n"/>
+      <c r="O22" s="16" t="n"/>
+      <c r="P22" s="4">
+        <f>IF($C22="","",IF($M22="入居","—",TODAY()-MAX($G22:$L22)))</f>
+        <v/>
+      </c>
+      <c r="Q22" s="16" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="4">
+        <f>IF($C23="","","C"&amp;TEXT(ROW()-1,"000"))</f>
+        <v/>
+      </c>
+      <c r="B23" s="4">
+        <f>IF($C23="","",設定対象施設)</f>
+        <v/>
+      </c>
+      <c r="C23" s="16" t="n"/>
+      <c r="D23" s="16" t="n"/>
+      <c r="E23" s="16" t="n"/>
+      <c r="F23" s="16" t="n"/>
+      <c r="G23" s="18" t="n"/>
+      <c r="H23" s="18" t="n"/>
+      <c r="I23" s="18" t="n"/>
+      <c r="J23" s="18" t="n"/>
+      <c r="K23" s="18" t="n"/>
+      <c r="L23" s="18" t="n"/>
+      <c r="M23" s="16" t="n"/>
+      <c r="N23" s="18" t="n"/>
+      <c r="O23" s="16" t="n"/>
+      <c r="P23" s="4">
+        <f>IF($C23="","",IF($M23="入居","—",TODAY()-MAX($G23:$L23)))</f>
+        <v/>
+      </c>
+      <c r="Q23" s="16" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="4">
+        <f>IF($C24="","","C"&amp;TEXT(ROW()-1,"000"))</f>
+        <v/>
+      </c>
+      <c r="B24" s="4">
+        <f>IF($C24="","",設定対象施設)</f>
+        <v/>
+      </c>
+      <c r="C24" s="16" t="n"/>
+      <c r="D24" s="16" t="n"/>
+      <c r="E24" s="16" t="n"/>
+      <c r="F24" s="16" t="n"/>
+      <c r="G24" s="18" t="n"/>
+      <c r="H24" s="18" t="n"/>
+      <c r="I24" s="18" t="n"/>
+      <c r="J24" s="18" t="n"/>
+      <c r="K24" s="18" t="n"/>
+      <c r="L24" s="18" t="n"/>
+      <c r="M24" s="16" t="n"/>
+      <c r="N24" s="18" t="n"/>
+      <c r="O24" s="16" t="n"/>
+      <c r="P24" s="4">
+        <f>IF($C24="","",IF($M24="入居","—",TODAY()-MAX($G24:$L24)))</f>
+        <v/>
+      </c>
+      <c r="Q24" s="16" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="4">
+        <f>IF($C25="","","C"&amp;TEXT(ROW()-1,"000"))</f>
+        <v/>
+      </c>
+      <c r="B25" s="4">
+        <f>IF($C25="","",設定対象施設)</f>
+        <v/>
+      </c>
+      <c r="C25" s="16" t="n"/>
+      <c r="D25" s="16" t="n"/>
+      <c r="E25" s="16" t="n"/>
+      <c r="F25" s="16" t="n"/>
+      <c r="G25" s="18" t="n"/>
+      <c r="H25" s="18" t="n"/>
+      <c r="I25" s="18" t="n"/>
+      <c r="J25" s="18" t="n"/>
+      <c r="K25" s="18" t="n"/>
+      <c r="L25" s="18" t="n"/>
+      <c r="M25" s="16" t="n"/>
+      <c r="N25" s="18" t="n"/>
+      <c r="O25" s="16" t="n"/>
+      <c r="P25" s="4">
+        <f>IF($C25="","",IF($M25="入居","—",TODAY()-MAX($G25:$L25)))</f>
+        <v/>
+      </c>
+      <c r="Q25" s="16" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="4">
+        <f>IF($C26="","","C"&amp;TEXT(ROW()-1,"000"))</f>
+        <v/>
+      </c>
+      <c r="B26" s="4">
+        <f>IF($C26="","",設定対象施設)</f>
+        <v/>
+      </c>
+      <c r="C26" s="16" t="n"/>
+      <c r="D26" s="16" t="n"/>
+      <c r="E26" s="16" t="n"/>
+      <c r="F26" s="16" t="n"/>
+      <c r="G26" s="18" t="n"/>
+      <c r="H26" s="18" t="n"/>
+      <c r="I26" s="18" t="n"/>
+      <c r="J26" s="18" t="n"/>
+      <c r="K26" s="18" t="n"/>
+      <c r="L26" s="18" t="n"/>
+      <c r="M26" s="16" t="n"/>
+      <c r="N26" s="18" t="n"/>
+      <c r="O26" s="16" t="n"/>
+      <c r="P26" s="4">
+        <f>IF($C26="","",IF($M26="入居","—",TODAY()-MAX($G26:$L26)))</f>
+        <v/>
+      </c>
+      <c r="Q26" s="16" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="4">
+        <f>IF($C27="","","C"&amp;TEXT(ROW()-1,"000"))</f>
+        <v/>
+      </c>
+      <c r="B27" s="4">
+        <f>IF($C27="","",設定対象施設)</f>
+        <v/>
+      </c>
+      <c r="C27" s="16" t="n"/>
+      <c r="D27" s="16" t="n"/>
+      <c r="E27" s="16" t="n"/>
+      <c r="F27" s="16" t="n"/>
+      <c r="G27" s="18" t="n"/>
+      <c r="H27" s="18" t="n"/>
+      <c r="I27" s="18" t="n"/>
+      <c r="J27" s="18" t="n"/>
+      <c r="K27" s="18" t="n"/>
+      <c r="L27" s="18" t="n"/>
+      <c r="M27" s="16" t="n"/>
+      <c r="N27" s="18" t="n"/>
+      <c r="O27" s="16" t="n"/>
+      <c r="P27" s="4">
+        <f>IF($C27="","",IF($M27="入居","—",TODAY()-MAX($G27:$L27)))</f>
+        <v/>
+      </c>
+      <c r="Q27" s="16" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="4">
+        <f>IF($C28="","","C"&amp;TEXT(ROW()-1,"000"))</f>
+        <v/>
+      </c>
+      <c r="B28" s="4">
+        <f>IF($C28="","",設定対象施設)</f>
+        <v/>
+      </c>
+      <c r="C28" s="16" t="n"/>
+      <c r="D28" s="16" t="n"/>
+      <c r="E28" s="16" t="n"/>
+      <c r="F28" s="16" t="n"/>
+      <c r="G28" s="18" t="n"/>
+      <c r="H28" s="18" t="n"/>
+      <c r="I28" s="18" t="n"/>
+      <c r="J28" s="18" t="n"/>
+      <c r="K28" s="18" t="n"/>
+      <c r="L28" s="18" t="n"/>
+      <c r="M28" s="16" t="n"/>
+      <c r="N28" s="18" t="n"/>
+      <c r="O28" s="16" t="n"/>
+      <c r="P28" s="4">
+        <f>IF($C28="","",IF($M28="入居","—",TODAY()-MAX($G28:$L28)))</f>
+        <v/>
+      </c>
+      <c r="Q28" s="16" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="4">
+        <f>IF($C29="","","C"&amp;TEXT(ROW()-1,"000"))</f>
+        <v/>
+      </c>
+      <c r="B29" s="4">
+        <f>IF($C29="","",設定対象施設)</f>
+        <v/>
+      </c>
+      <c r="C29" s="16" t="n"/>
+      <c r="D29" s="16" t="n"/>
+      <c r="E29" s="16" t="n"/>
+      <c r="F29" s="16" t="n"/>
+      <c r="G29" s="18" t="n"/>
+      <c r="H29" s="18" t="n"/>
+      <c r="I29" s="18" t="n"/>
+      <c r="J29" s="18" t="n"/>
+      <c r="K29" s="18" t="n"/>
+      <c r="L29" s="18" t="n"/>
+      <c r="M29" s="16" t="n"/>
+      <c r="N29" s="18" t="n"/>
+      <c r="O29" s="16" t="n"/>
+      <c r="P29" s="4">
+        <f>IF($C29="","",IF($M29="入居","—",TODAY()-MAX($G29:$L29)))</f>
+        <v/>
+      </c>
+      <c r="Q29" s="16" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="4">
+        <f>IF($C30="","","C"&amp;TEXT(ROW()-1,"000"))</f>
+        <v/>
+      </c>
+      <c r="B30" s="4">
+        <f>IF($C30="","",設定対象施設)</f>
+        <v/>
+      </c>
+      <c r="C30" s="16" t="n"/>
+      <c r="D30" s="16" t="n"/>
+      <c r="E30" s="16" t="n"/>
+      <c r="F30" s="16" t="n"/>
+      <c r="G30" s="18" t="n"/>
+      <c r="H30" s="18" t="n"/>
+      <c r="I30" s="18" t="n"/>
+      <c r="J30" s="18" t="n"/>
+      <c r="K30" s="18" t="n"/>
+      <c r="L30" s="18" t="n"/>
+      <c r="M30" s="16" t="n"/>
+      <c r="N30" s="18" t="n"/>
+      <c r="O30" s="16" t="n"/>
+      <c r="P30" s="4">
+        <f>IF($C30="","",IF($M30="入居","—",TODAY()-MAX($G30:$L30)))</f>
+        <v/>
+      </c>
+      <c r="Q30" s="16" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="4">
+        <f>IF($C31="","","C"&amp;TEXT(ROW()-1,"000"))</f>
+        <v/>
+      </c>
+      <c r="B31" s="4">
+        <f>IF($C31="","",設定対象施設)</f>
+        <v/>
+      </c>
+      <c r="C31" s="16" t="n"/>
+      <c r="D31" s="16" t="n"/>
+      <c r="E31" s="16" t="n"/>
+      <c r="F31" s="16" t="n"/>
+      <c r="G31" s="18" t="n"/>
+      <c r="H31" s="18" t="n"/>
+      <c r="I31" s="18" t="n"/>
+      <c r="J31" s="18" t="n"/>
+      <c r="K31" s="18" t="n"/>
+      <c r="L31" s="18" t="n"/>
+      <c r="M31" s="16" t="n"/>
+      <c r="N31" s="18" t="n"/>
+      <c r="O31" s="16" t="n"/>
+      <c r="P31" s="4">
+        <f>IF($C31="","",IF($M31="入居","—",TODAY()-MAX($G31:$L31)))</f>
+        <v/>
+      </c>
+      <c r="Q31" s="16" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="4">
+        <f>IF($C32="","","C"&amp;TEXT(ROW()-1,"000"))</f>
+        <v/>
+      </c>
+      <c r="B32" s="4">
+        <f>IF($C32="","",設定対象施設)</f>
+        <v/>
+      </c>
+      <c r="C32" s="16" t="n"/>
+      <c r="D32" s="16" t="n"/>
+      <c r="E32" s="16" t="n"/>
+      <c r="F32" s="16" t="n"/>
+      <c r="G32" s="18" t="n"/>
+      <c r="H32" s="18" t="n"/>
+      <c r="I32" s="18" t="n"/>
+      <c r="J32" s="18" t="n"/>
+      <c r="K32" s="18" t="n"/>
+      <c r="L32" s="18" t="n"/>
+      <c r="M32" s="16" t="n"/>
+      <c r="N32" s="18" t="n"/>
+      <c r="O32" s="16" t="n"/>
+      <c r="P32" s="4">
+        <f>IF($C32="","",IF($M32="入居","—",TODAY()-MAX($G32:$L32)))</f>
+        <v/>
+      </c>
+      <c r="Q32" s="16" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="4">
+        <f>IF($C33="","","C"&amp;TEXT(ROW()-1,"000"))</f>
+        <v/>
+      </c>
+      <c r="B33" s="4">
+        <f>IF($C33="","",設定対象施設)</f>
+        <v/>
+      </c>
+      <c r="C33" s="16" t="n"/>
+      <c r="D33" s="16" t="n"/>
+      <c r="E33" s="16" t="n"/>
+      <c r="F33" s="16" t="n"/>
+      <c r="G33" s="18" t="n"/>
+      <c r="H33" s="18" t="n"/>
+      <c r="I33" s="18" t="n"/>
+      <c r="J33" s="18" t="n"/>
+      <c r="K33" s="18" t="n"/>
+      <c r="L33" s="18" t="n"/>
+      <c r="M33" s="16" t="n"/>
+      <c r="N33" s="18" t="n"/>
+      <c r="O33" s="16" t="n"/>
+      <c r="P33" s="4">
+        <f>IF($C33="","",IF($M33="入居","—",TODAY()-MAX($G33:$L33)))</f>
+        <v/>
+      </c>
+      <c r="Q33" s="16" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="4">
+        <f>IF($C34="","","C"&amp;TEXT(ROW()-1,"000"))</f>
+        <v/>
+      </c>
+      <c r="B34" s="4">
+        <f>IF($C34="","",設定対象施設)</f>
+        <v/>
+      </c>
+      <c r="C34" s="16" t="n"/>
+      <c r="D34" s="16" t="n"/>
+      <c r="E34" s="16" t="n"/>
+      <c r="F34" s="16" t="n"/>
+      <c r="G34" s="18" t="n"/>
+      <c r="H34" s="18" t="n"/>
+      <c r="I34" s="18" t="n"/>
+      <c r="J34" s="18" t="n"/>
+      <c r="K34" s="18" t="n"/>
+      <c r="L34" s="18" t="n"/>
+      <c r="M34" s="16" t="n"/>
+      <c r="N34" s="18" t="n"/>
+      <c r="O34" s="16" t="n"/>
+      <c r="P34" s="4">
+        <f>IF($C34="","",IF($M34="入居","—",TODAY()-MAX($G34:$L34)))</f>
+        <v/>
+      </c>
+      <c r="Q34" s="16" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="4">
+        <f>IF($C35="","","C"&amp;TEXT(ROW()-1,"000"))</f>
+        <v/>
+      </c>
+      <c r="B35" s="4">
+        <f>IF($C35="","",設定対象施設)</f>
+        <v/>
+      </c>
+      <c r="C35" s="16" t="n"/>
+      <c r="D35" s="16" t="n"/>
+      <c r="E35" s="16" t="n"/>
+      <c r="F35" s="16" t="n"/>
+      <c r="G35" s="18" t="n"/>
+      <c r="H35" s="18" t="n"/>
+      <c r="I35" s="18" t="n"/>
+      <c r="J35" s="18" t="n"/>
+      <c r="K35" s="18" t="n"/>
+      <c r="L35" s="18" t="n"/>
+      <c r="M35" s="16" t="n"/>
+      <c r="N35" s="18" t="n"/>
+      <c r="O35" s="16" t="n"/>
+      <c r="P35" s="4">
+        <f>IF($C35="","",IF($M35="入居","—",TODAY()-MAX($G35:$L35)))</f>
+        <v/>
+      </c>
+      <c r="Q35" s="16" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="4">
+        <f>IF($C36="","","C"&amp;TEXT(ROW()-1,"000"))</f>
+        <v/>
+      </c>
+      <c r="B36" s="4">
+        <f>IF($C36="","",設定対象施設)</f>
+        <v/>
+      </c>
+      <c r="C36" s="16" t="n"/>
+      <c r="D36" s="16" t="n"/>
+      <c r="E36" s="16" t="n"/>
+      <c r="F36" s="16" t="n"/>
+      <c r="G36" s="18" t="n"/>
+      <c r="H36" s="18" t="n"/>
+      <c r="I36" s="18" t="n"/>
+      <c r="J36" s="18" t="n"/>
+      <c r="K36" s="18" t="n"/>
+      <c r="L36" s="18" t="n"/>
+      <c r="M36" s="16" t="n"/>
+      <c r="N36" s="18" t="n"/>
+      <c r="O36" s="16" t="n"/>
+      <c r="P36" s="4">
+        <f>IF($C36="","",IF($M36="入居","—",TODAY()-MAX($G36:$L36)))</f>
+        <v/>
+      </c>
+      <c r="Q36" s="16" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="4">
+        <f>IF($C37="","","C"&amp;TEXT(ROW()-1,"000"))</f>
+        <v/>
+      </c>
+      <c r="B37" s="4">
+        <f>IF($C37="","",設定対象施設)</f>
+        <v/>
+      </c>
+      <c r="C37" s="16" t="n"/>
+      <c r="D37" s="16" t="n"/>
+      <c r="E37" s="16" t="n"/>
+      <c r="F37" s="16" t="n"/>
+      <c r="G37" s="18" t="n"/>
+      <c r="H37" s="18" t="n"/>
+      <c r="I37" s="18" t="n"/>
+      <c r="J37" s="18" t="n"/>
+      <c r="K37" s="18" t="n"/>
+      <c r="L37" s="18" t="n"/>
+      <c r="M37" s="16" t="n"/>
+      <c r="N37" s="18" t="n"/>
+      <c r="O37" s="16" t="n"/>
+      <c r="P37" s="4">
+        <f>IF($C37="","",IF($M37="入居","—",TODAY()-MAX($G37:$L37)))</f>
+        <v/>
+      </c>
+      <c r="Q37" s="16" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="4">
+        <f>IF($C38="","","C"&amp;TEXT(ROW()-1,"000"))</f>
+        <v/>
+      </c>
+      <c r="B38" s="4">
+        <f>IF($C38="","",設定対象施設)</f>
+        <v/>
+      </c>
+      <c r="C38" s="16" t="n"/>
+      <c r="D38" s="16" t="n"/>
+      <c r="E38" s="16" t="n"/>
+      <c r="F38" s="16" t="n"/>
+      <c r="G38" s="18" t="n"/>
+      <c r="H38" s="18" t="n"/>
+      <c r="I38" s="18" t="n"/>
+      <c r="J38" s="18" t="n"/>
+      <c r="K38" s="18" t="n"/>
+      <c r="L38" s="18" t="n"/>
+      <c r="M38" s="16" t="n"/>
+      <c r="N38" s="18" t="n"/>
+      <c r="O38" s="16" t="n"/>
+      <c r="P38" s="4">
+        <f>IF($C38="","",IF($M38="入居","—",TODAY()-MAX($G38:$L38)))</f>
+        <v/>
+      </c>
+      <c r="Q38" s="16" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="4">
+        <f>IF($C39="","","C"&amp;TEXT(ROW()-1,"000"))</f>
+        <v/>
+      </c>
+      <c r="B39" s="4">
+        <f>IF($C39="","",設定対象施設)</f>
+        <v/>
+      </c>
+      <c r="C39" s="16" t="n"/>
+      <c r="D39" s="16" t="n"/>
+      <c r="E39" s="16" t="n"/>
+      <c r="F39" s="16" t="n"/>
+      <c r="G39" s="18" t="n"/>
+      <c r="H39" s="18" t="n"/>
+      <c r="I39" s="18" t="n"/>
+      <c r="J39" s="18" t="n"/>
+      <c r="K39" s="18" t="n"/>
+      <c r="L39" s="18" t="n"/>
+      <c r="M39" s="16" t="n"/>
+      <c r="N39" s="18" t="n"/>
+      <c r="O39" s="16" t="n"/>
+      <c r="P39" s="4">
+        <f>IF($C39="","",IF($M39="入居","—",TODAY()-MAX($G39:$L39)))</f>
+        <v/>
+      </c>
+      <c r="Q39" s="16" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="4">
+        <f>IF($C40="","","C"&amp;TEXT(ROW()-1,"000"))</f>
+        <v/>
+      </c>
+      <c r="B40" s="4">
+        <f>IF($C40="","",設定対象施設)</f>
+        <v/>
+      </c>
+      <c r="C40" s="16" t="n"/>
+      <c r="D40" s="16" t="n"/>
+      <c r="E40" s="16" t="n"/>
+      <c r="F40" s="16" t="n"/>
+      <c r="G40" s="18" t="n"/>
+      <c r="H40" s="18" t="n"/>
+      <c r="I40" s="18" t="n"/>
+      <c r="J40" s="18" t="n"/>
+      <c r="K40" s="18" t="n"/>
+      <c r="L40" s="18" t="n"/>
+      <c r="M40" s="16" t="n"/>
+      <c r="N40" s="18" t="n"/>
+      <c r="O40" s="16" t="n"/>
+      <c r="P40" s="4">
+        <f>IF($C40="","",IF($M40="入居","—",TODAY()-MAX($G40:$L40)))</f>
+        <v/>
+      </c>
+      <c r="Q40" s="16" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="4">
+        <f>IF($C41="","","C"&amp;TEXT(ROW()-1,"000"))</f>
+        <v/>
+      </c>
+      <c r="B41" s="4">
+        <f>IF($C41="","",設定対象施設)</f>
+        <v/>
+      </c>
+      <c r="C41" s="16" t="n"/>
+      <c r="D41" s="16" t="n"/>
+      <c r="E41" s="16" t="n"/>
+      <c r="F41" s="16" t="n"/>
+      <c r="G41" s="18" t="n"/>
+      <c r="H41" s="18" t="n"/>
+      <c r="I41" s="18" t="n"/>
+      <c r="J41" s="18" t="n"/>
+      <c r="K41" s="18" t="n"/>
+      <c r="L41" s="18" t="n"/>
+      <c r="M41" s="16" t="n"/>
+      <c r="N41" s="18" t="n"/>
+      <c r="O41" s="16" t="n"/>
+      <c r="P41" s="4">
+        <f>IF($C41="","",IF($M41="入居","—",TODAY()-MAX($G41:$L41)))</f>
+        <v/>
+      </c>
+      <c r="Q41" s="16" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="4">
+        <f>IF($C42="","","C"&amp;TEXT(ROW()-1,"000"))</f>
+        <v/>
+      </c>
+      <c r="B42" s="4">
+        <f>IF($C42="","",設定対象施設)</f>
+        <v/>
+      </c>
+      <c r="C42" s="16" t="n"/>
+      <c r="D42" s="16" t="n"/>
+      <c r="E42" s="16" t="n"/>
+      <c r="F42" s="16" t="n"/>
+      <c r="G42" s="18" t="n"/>
+      <c r="H42" s="18" t="n"/>
+      <c r="I42" s="18" t="n"/>
+      <c r="J42" s="18" t="n"/>
+      <c r="K42" s="18" t="n"/>
+      <c r="L42" s="18" t="n"/>
+      <c r="M42" s="16" t="n"/>
+      <c r="N42" s="18" t="n"/>
+      <c r="O42" s="16" t="n"/>
+      <c r="P42" s="4">
+        <f>IF($C42="","",IF($M42="入居","—",TODAY()-MAX($G42:$L42)))</f>
+        <v/>
+      </c>
+      <c r="Q42" s="16" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="4">
+        <f>IF($C43="","","C"&amp;TEXT(ROW()-1,"000"))</f>
+        <v/>
+      </c>
+      <c r="B43" s="4">
+        <f>IF($C43="","",設定対象施設)</f>
+        <v/>
+      </c>
+      <c r="C43" s="16" t="n"/>
+      <c r="D43" s="16" t="n"/>
+      <c r="E43" s="16" t="n"/>
+      <c r="F43" s="16" t="n"/>
+      <c r="G43" s="18" t="n"/>
+      <c r="H43" s="18" t="n"/>
+      <c r="I43" s="18" t="n"/>
+      <c r="J43" s="18" t="n"/>
+      <c r="K43" s="18" t="n"/>
+      <c r="L43" s="18" t="n"/>
+      <c r="M43" s="16" t="n"/>
+      <c r="N43" s="18" t="n"/>
+      <c r="O43" s="16" t="n"/>
+      <c r="P43" s="4">
+        <f>IF($C43="","",IF($M43="入居","—",TODAY()-MAX($G43:$L43)))</f>
+        <v/>
+      </c>
+      <c r="Q43" s="16" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="4">
+        <f>IF($C44="","","C"&amp;TEXT(ROW()-1,"000"))</f>
+        <v/>
+      </c>
+      <c r="B44" s="4">
+        <f>IF($C44="","",設定対象施設)</f>
+        <v/>
+      </c>
+      <c r="C44" s="16" t="n"/>
+      <c r="D44" s="16" t="n"/>
+      <c r="E44" s="16" t="n"/>
+      <c r="F44" s="16" t="n"/>
+      <c r="G44" s="18" t="n"/>
+      <c r="H44" s="18" t="n"/>
+      <c r="I44" s="18" t="n"/>
+      <c r="J44" s="18" t="n"/>
+      <c r="K44" s="18" t="n"/>
+      <c r="L44" s="18" t="n"/>
+      <c r="M44" s="16" t="n"/>
+      <c r="N44" s="18" t="n"/>
+      <c r="O44" s="16" t="n"/>
+      <c r="P44" s="4">
+        <f>IF($C44="","",IF($M44="入居","—",TODAY()-MAX($G44:$L44)))</f>
+        <v/>
+      </c>
+      <c r="Q44" s="16" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="4">
+        <f>IF($C45="","","C"&amp;TEXT(ROW()-1,"000"))</f>
+        <v/>
+      </c>
+      <c r="B45" s="4">
+        <f>IF($C45="","",設定対象施設)</f>
+        <v/>
+      </c>
+      <c r="C45" s="16" t="n"/>
+      <c r="D45" s="16" t="n"/>
+      <c r="E45" s="16" t="n"/>
+      <c r="F45" s="16" t="n"/>
+      <c r="G45" s="18" t="n"/>
+      <c r="H45" s="18" t="n"/>
+      <c r="I45" s="18" t="n"/>
+      <c r="J45" s="18" t="n"/>
+      <c r="K45" s="18" t="n"/>
+      <c r="L45" s="18" t="n"/>
+      <c r="M45" s="16" t="n"/>
+      <c r="N45" s="18" t="n"/>
+      <c r="O45" s="16" t="n"/>
+      <c r="P45" s="4">
+        <f>IF($C45="","",IF($M45="入居","—",TODAY()-MAX($G45:$L45)))</f>
+        <v/>
+      </c>
+      <c r="Q45" s="16" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="4">
+        <f>IF($C46="","","C"&amp;TEXT(ROW()-1,"000"))</f>
+        <v/>
+      </c>
+      <c r="B46" s="4">
+        <f>IF($C46="","",設定対象施設)</f>
+        <v/>
+      </c>
+      <c r="C46" s="16" t="n"/>
+      <c r="D46" s="16" t="n"/>
+      <c r="E46" s="16" t="n"/>
+      <c r="F46" s="16" t="n"/>
+      <c r="G46" s="18" t="n"/>
+      <c r="H46" s="18" t="n"/>
+      <c r="I46" s="18" t="n"/>
+      <c r="J46" s="18" t="n"/>
+      <c r="K46" s="18" t="n"/>
+      <c r="L46" s="18" t="n"/>
+      <c r="M46" s="16" t="n"/>
+      <c r="N46" s="18" t="n"/>
+      <c r="O46" s="16" t="n"/>
+      <c r="P46" s="4">
+        <f>IF($C46="","",IF($M46="入居","—",TODAY()-MAX($G46:$L46)))</f>
+        <v/>
+      </c>
+      <c r="Q46" s="16" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="4">
+        <f>IF($C47="","","C"&amp;TEXT(ROW()-1,"000"))</f>
+        <v/>
+      </c>
+      <c r="B47" s="4">
+        <f>IF($C47="","",設定対象施設)</f>
+        <v/>
+      </c>
+      <c r="C47" s="16" t="n"/>
+      <c r="D47" s="16" t="n"/>
+      <c r="E47" s="16" t="n"/>
+      <c r="F47" s="16" t="n"/>
+      <c r="G47" s="18" t="n"/>
+      <c r="H47" s="18" t="n"/>
+      <c r="I47" s="18" t="n"/>
+      <c r="J47" s="18" t="n"/>
+      <c r="K47" s="18" t="n"/>
+      <c r="L47" s="18" t="n"/>
+      <c r="M47" s="16" t="n"/>
+      <c r="N47" s="18" t="n"/>
+      <c r="O47" s="16" t="n"/>
+      <c r="P47" s="4">
+        <f>IF($C47="","",IF($M47="入居","—",TODAY()-MAX($G47:$L47)))</f>
+        <v/>
+      </c>
+      <c r="Q47" s="16" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="4">
+        <f>IF($C48="","","C"&amp;TEXT(ROW()-1,"000"))</f>
+        <v/>
+      </c>
+      <c r="B48" s="4">
+        <f>IF($C48="","",設定対象施設)</f>
+        <v/>
+      </c>
+      <c r="C48" s="16" t="n"/>
+      <c r="D48" s="16" t="n"/>
+      <c r="E48" s="16" t="n"/>
+      <c r="F48" s="16" t="n"/>
+      <c r="G48" s="18" t="n"/>
+      <c r="H48" s="18" t="n"/>
+      <c r="I48" s="18" t="n"/>
+      <c r="J48" s="18" t="n"/>
+      <c r="K48" s="18" t="n"/>
+      <c r="L48" s="18" t="n"/>
+      <c r="M48" s="16" t="n"/>
+      <c r="N48" s="18" t="n"/>
+      <c r="O48" s="16" t="n"/>
+      <c r="P48" s="4">
+        <f>IF($C48="","",IF($M48="入居","—",TODAY()-MAX($G48:$L48)))</f>
+        <v/>
+      </c>
+      <c r="Q48" s="16" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="4">
+        <f>IF($C49="","","C"&amp;TEXT(ROW()-1,"000"))</f>
+        <v/>
+      </c>
+      <c r="B49" s="4">
+        <f>IF($C49="","",設定対象施設)</f>
+        <v/>
+      </c>
+      <c r="C49" s="16" t="n"/>
+      <c r="D49" s="16" t="n"/>
+      <c r="E49" s="16" t="n"/>
+      <c r="F49" s="16" t="n"/>
+      <c r="G49" s="18" t="n"/>
+      <c r="H49" s="18" t="n"/>
+      <c r="I49" s="18" t="n"/>
+      <c r="J49" s="18" t="n"/>
+      <c r="K49" s="18" t="n"/>
+      <c r="L49" s="18" t="n"/>
+      <c r="M49" s="16" t="n"/>
+      <c r="N49" s="18" t="n"/>
+      <c r="O49" s="16" t="n"/>
+      <c r="P49" s="4">
+        <f>IF($C49="","",IF($M49="入居","—",TODAY()-MAX($G49:$L49)))</f>
+        <v/>
+      </c>
+      <c r="Q49" s="16" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="4">
+        <f>IF($C50="","","C"&amp;TEXT(ROW()-1,"000"))</f>
+        <v/>
+      </c>
+      <c r="B50" s="4">
+        <f>IF($C50="","",設定対象施設)</f>
+        <v/>
+      </c>
+      <c r="C50" s="16" t="n"/>
+      <c r="D50" s="16" t="n"/>
+      <c r="E50" s="16" t="n"/>
+      <c r="F50" s="16" t="n"/>
+      <c r="G50" s="18" t="n"/>
+      <c r="H50" s="18" t="n"/>
+      <c r="I50" s="18" t="n"/>
+      <c r="J50" s="18" t="n"/>
+      <c r="K50" s="18" t="n"/>
+      <c r="L50" s="18" t="n"/>
+      <c r="M50" s="16" t="n"/>
+      <c r="N50" s="18" t="n"/>
+      <c r="O50" s="16" t="n"/>
+      <c r="P50" s="4">
+        <f>IF($C50="","",IF($M50="入居","—",TODAY()-MAX($G50:$L50)))</f>
+        <v/>
+      </c>
+      <c r="Q50" s="16" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="4">
+        <f>IF($C51="","","C"&amp;TEXT(ROW()-1,"000"))</f>
+        <v/>
+      </c>
+      <c r="B51" s="4">
+        <f>IF($C51="","",設定対象施設)</f>
+        <v/>
+      </c>
+      <c r="C51" s="16" t="n"/>
+      <c r="D51" s="16" t="n"/>
+      <c r="E51" s="16" t="n"/>
+      <c r="F51" s="16" t="n"/>
+      <c r="G51" s="18" t="n"/>
+      <c r="H51" s="18" t="n"/>
+      <c r="I51" s="18" t="n"/>
+      <c r="J51" s="18" t="n"/>
+      <c r="K51" s="18" t="n"/>
+      <c r="L51" s="18" t="n"/>
+      <c r="M51" s="16" t="n"/>
+      <c r="N51" s="18" t="n"/>
+      <c r="O51" s="16" t="n"/>
+      <c r="P51" s="4">
+        <f>IF($C51="","",IF($M51="入居","—",TODAY()-MAX($G51:$L51)))</f>
+        <v/>
+      </c>
+      <c r="Q51" s="16" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="4">
+        <f>IF($C52="","","C"&amp;TEXT(ROW()-1,"000"))</f>
+        <v/>
+      </c>
+      <c r="B52" s="4">
+        <f>IF($C52="","",設定対象施設)</f>
+        <v/>
+      </c>
+      <c r="C52" s="16" t="n"/>
+      <c r="D52" s="16" t="n"/>
+      <c r="E52" s="16" t="n"/>
+      <c r="F52" s="16" t="n"/>
+      <c r="G52" s="18" t="n"/>
+      <c r="H52" s="18" t="n"/>
+      <c r="I52" s="18" t="n"/>
+      <c r="J52" s="18" t="n"/>
+      <c r="K52" s="18" t="n"/>
+      <c r="L52" s="18" t="n"/>
+      <c r="M52" s="16" t="n"/>
+      <c r="N52" s="18" t="n"/>
+      <c r="O52" s="16" t="n"/>
+      <c r="P52" s="4">
+        <f>IF($C52="","",IF($M52="入居","—",TODAY()-MAX($G52:$L52)))</f>
+        <v/>
+      </c>
+      <c r="Q52" s="16" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="4">
+        <f>IF($C53="","","C"&amp;TEXT(ROW()-1,"000"))</f>
+        <v/>
+      </c>
+      <c r="B53" s="4">
+        <f>IF($C53="","",設定対象施設)</f>
+        <v/>
+      </c>
+      <c r="C53" s="16" t="n"/>
+      <c r="D53" s="16" t="n"/>
+      <c r="E53" s="16" t="n"/>
+      <c r="F53" s="16" t="n"/>
+      <c r="G53" s="18" t="n"/>
+      <c r="H53" s="18" t="n"/>
+      <c r="I53" s="18" t="n"/>
+      <c r="J53" s="18" t="n"/>
+      <c r="K53" s="18" t="n"/>
+      <c r="L53" s="18" t="n"/>
+      <c r="M53" s="16" t="n"/>
+      <c r="N53" s="18" t="n"/>
+      <c r="O53" s="16" t="n"/>
+      <c r="P53" s="4">
+        <f>IF($C53="","",IF($M53="入居","—",TODAY()-MAX($G53:$L53)))</f>
+        <v/>
+      </c>
+      <c r="Q53" s="16" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="4">
+        <f>IF($C54="","","C"&amp;TEXT(ROW()-1,"000"))</f>
+        <v/>
+      </c>
+      <c r="B54" s="4">
+        <f>IF($C54="","",設定対象施設)</f>
+        <v/>
+      </c>
+      <c r="C54" s="16" t="n"/>
+      <c r="D54" s="16" t="n"/>
+      <c r="E54" s="16" t="n"/>
+      <c r="F54" s="16" t="n"/>
+      <c r="G54" s="18" t="n"/>
+      <c r="H54" s="18" t="n"/>
+      <c r="I54" s="18" t="n"/>
+      <c r="J54" s="18" t="n"/>
+      <c r="K54" s="18" t="n"/>
+      <c r="L54" s="18" t="n"/>
+      <c r="M54" s="16" t="n"/>
+      <c r="N54" s="18" t="n"/>
+      <c r="O54" s="16" t="n"/>
+      <c r="P54" s="4">
+        <f>IF($C54="","",IF($M54="入居","—",TODAY()-MAX($G54:$L54)))</f>
+        <v/>
+      </c>
+      <c r="Q54" s="16" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="4">
+        <f>IF($C55="","","C"&amp;TEXT(ROW()-1,"000"))</f>
+        <v/>
+      </c>
+      <c r="B55" s="4">
+        <f>IF($C55="","",設定対象施設)</f>
+        <v/>
+      </c>
+      <c r="C55" s="16" t="n"/>
+      <c r="D55" s="16" t="n"/>
+      <c r="E55" s="16" t="n"/>
+      <c r="F55" s="16" t="n"/>
+      <c r="G55" s="18" t="n"/>
+      <c r="H55" s="18" t="n"/>
+      <c r="I55" s="18" t="n"/>
+      <c r="J55" s="18" t="n"/>
+      <c r="K55" s="18" t="n"/>
+      <c r="L55" s="18" t="n"/>
+      <c r="M55" s="16" t="n"/>
+      <c r="N55" s="18" t="n"/>
+      <c r="O55" s="16" t="n"/>
+      <c r="P55" s="4">
+        <f>IF($C55="","",IF($M55="入居","—",TODAY()-MAX($G55:$L55)))</f>
+        <v/>
+      </c>
+      <c r="Q55" s="16" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="4">
+        <f>IF($C56="","","C"&amp;TEXT(ROW()-1,"000"))</f>
+        <v/>
+      </c>
+      <c r="B56" s="4">
+        <f>IF($C56="","",設定対象施設)</f>
+        <v/>
+      </c>
+      <c r="C56" s="16" t="n"/>
+      <c r="D56" s="16" t="n"/>
+      <c r="E56" s="16" t="n"/>
+      <c r="F56" s="16" t="n"/>
+      <c r="G56" s="18" t="n"/>
+      <c r="H56" s="18" t="n"/>
+      <c r="I56" s="18" t="n"/>
+      <c r="J56" s="18" t="n"/>
+      <c r="K56" s="18" t="n"/>
+      <c r="L56" s="18" t="n"/>
+      <c r="M56" s="16" t="n"/>
+      <c r="N56" s="18" t="n"/>
+      <c r="O56" s="16" t="n"/>
+      <c r="P56" s="4">
+        <f>IF($C56="","",IF($M56="入居","—",TODAY()-MAX($G56:$L56)))</f>
+        <v/>
+      </c>
+      <c r="Q56" s="16" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="4">
+        <f>IF($C57="","","C"&amp;TEXT(ROW()-1,"000"))</f>
+        <v/>
+      </c>
+      <c r="B57" s="4">
+        <f>IF($C57="","",設定対象施設)</f>
+        <v/>
+      </c>
+      <c r="C57" s="16" t="n"/>
+      <c r="D57" s="16" t="n"/>
+      <c r="E57" s="16" t="n"/>
+      <c r="F57" s="16" t="n"/>
+      <c r="G57" s="18" t="n"/>
+      <c r="H57" s="18" t="n"/>
+      <c r="I57" s="18" t="n"/>
+      <c r="J57" s="18" t="n"/>
+      <c r="K57" s="18" t="n"/>
+      <c r="L57" s="18" t="n"/>
+      <c r="M57" s="16" t="n"/>
+      <c r="N57" s="18" t="n"/>
+      <c r="O57" s="16" t="n"/>
+      <c r="P57" s="4">
+        <f>IF($C57="","",IF($M57="入居","—",TODAY()-MAX($G57:$L57)))</f>
+        <v/>
+      </c>
+      <c r="Q57" s="16" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="4">
+        <f>IF($C58="","","C"&amp;TEXT(ROW()-1,"000"))</f>
+        <v/>
+      </c>
+      <c r="B58" s="4">
+        <f>IF($C58="","",設定対象施設)</f>
+        <v/>
+      </c>
+      <c r="C58" s="16" t="n"/>
+      <c r="D58" s="16" t="n"/>
+      <c r="E58" s="16" t="n"/>
+      <c r="F58" s="16" t="n"/>
+      <c r="G58" s="18" t="n"/>
+      <c r="H58" s="18" t="n"/>
+      <c r="I58" s="18" t="n"/>
+      <c r="J58" s="18" t="n"/>
+      <c r="K58" s="18" t="n"/>
+      <c r="L58" s="18" t="n"/>
+      <c r="M58" s="16" t="n"/>
+      <c r="N58" s="18" t="n"/>
+      <c r="O58" s="16" t="n"/>
+      <c r="P58" s="4">
+        <f>IF($C58="","",IF($M58="入居","—",TODAY()-MAX($G58:$L58)))</f>
+        <v/>
+      </c>
+      <c r="Q58" s="16" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="4">
+        <f>IF($C59="","","C"&amp;TEXT(ROW()-1,"000"))</f>
+        <v/>
+      </c>
+      <c r="B59" s="4">
+        <f>IF($C59="","",設定対象施設)</f>
+        <v/>
+      </c>
+      <c r="C59" s="16" t="n"/>
+      <c r="D59" s="16" t="n"/>
+      <c r="E59" s="16" t="n"/>
+      <c r="F59" s="16" t="n"/>
+      <c r="G59" s="18" t="n"/>
+      <c r="H59" s="18" t="n"/>
+      <c r="I59" s="18" t="n"/>
+      <c r="J59" s="18" t="n"/>
+      <c r="K59" s="18" t="n"/>
+      <c r="L59" s="18" t="n"/>
+      <c r="M59" s="16" t="n"/>
+      <c r="N59" s="18" t="n"/>
+      <c r="O59" s="16" t="n"/>
+      <c r="P59" s="4">
+        <f>IF($C59="","",IF($M59="入居","—",TODAY()-MAX($G59:$L59)))</f>
+        <v/>
+      </c>
+      <c r="Q59" s="16" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="4">
+        <f>IF($C60="","","C"&amp;TEXT(ROW()-1,"000"))</f>
+        <v/>
+      </c>
+      <c r="B60" s="4">
+        <f>IF($C60="","",設定対象施設)</f>
+        <v/>
+      </c>
+      <c r="C60" s="16" t="n"/>
+      <c r="D60" s="16" t="n"/>
+      <c r="E60" s="16" t="n"/>
+      <c r="F60" s="16" t="n"/>
+      <c r="G60" s="18" t="n"/>
+      <c r="H60" s="18" t="n"/>
+      <c r="I60" s="18" t="n"/>
+      <c r="J60" s="18" t="n"/>
+      <c r="K60" s="18" t="n"/>
+      <c r="L60" s="18" t="n"/>
+      <c r="M60" s="16" t="n"/>
+      <c r="N60" s="18" t="n"/>
+      <c r="O60" s="16" t="n"/>
+      <c r="P60" s="4">
+        <f>IF($C60="","",IF($M60="入居","—",TODAY()-MAX($G60:$L60)))</f>
+        <v/>
+      </c>
+      <c r="Q60" s="16" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="4">
+        <f>IF($C61="","","C"&amp;TEXT(ROW()-1,"000"))</f>
+        <v/>
+      </c>
+      <c r="B61" s="4">
+        <f>IF($C61="","",設定対象施設)</f>
+        <v/>
+      </c>
+      <c r="C61" s="16" t="n"/>
+      <c r="D61" s="16" t="n"/>
+      <c r="E61" s="16" t="n"/>
+      <c r="F61" s="16" t="n"/>
+      <c r="G61" s="18" t="n"/>
+      <c r="H61" s="18" t="n"/>
+      <c r="I61" s="18" t="n"/>
+      <c r="J61" s="18" t="n"/>
+      <c r="K61" s="18" t="n"/>
+      <c r="L61" s="18" t="n"/>
+      <c r="M61" s="16" t="n"/>
+      <c r="N61" s="18" t="n"/>
+      <c r="O61" s="16" t="n"/>
+      <c r="P61" s="4">
+        <f>IF($C61="","",IF($M61="入居","—",TODAY()-MAX($G61:$L61)))</f>
+        <v/>
+      </c>
+      <c r="Q61" s="16" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="13" t="inlineStr">
+        <is>
+          <t>※ 停滞日数が14日を超えた案件は赤表示。週次で追客日を再設定してください。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:Q61"/>
+  <conditionalFormatting sqref="P2:P61">
+    <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="0">
+      <formula>14</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="4">
+    <dataValidation sqref="D2:D61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"SS,入居,将来参考,入居待機"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F2:F61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"相談支援,基幹相談,病院,行政,家族,本人,他事業所"</formula1>
+    </dataValidation>
+    <dataValidation sqref="M2:M61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"発掘,追客,見学,体験,実調,契約,入居,見送り"</formula1>
+    </dataValidation>
+    <dataValidation sqref="O2:O61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>担当者リスト</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -3093,7 +11398,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:F21"/>
+  <dimension ref="B2:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -3236,99 +11541,156 @@
     <row r="15">
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>週の基準日（自動計算）</t>
+          <t>週の定義（自動計算）</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>※ 集計期間は旧シートの『7日／14日／21日／28日時点』と同じ、月内日付での区切りです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>週</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>基準日</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t>入力締切（翌営業日想定）</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>第1週</t>
-        </is>
-      </c>
-      <c r="C17" s="15">
-        <f>IF($B$11="","",$B$11)</f>
-        <v/>
-      </c>
-      <c r="D17" s="15">
-        <f>IF($C17="","",$C17+1)</f>
-        <v/>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>集計開始日</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>集計終了日</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>PDCA会議日</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>入力締切</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>第2週</t>
+          <t>第1週</t>
         </is>
       </c>
       <c r="C18" s="15">
-        <f>IF($C17="","",$C17+7)</f>
+        <f>IF(DAY(EOMONTH(DATE($B$7,$B$9,1),0))&lt;1,"",DATE($B$7,$B$9,1))</f>
         <v/>
       </c>
       <c r="D18" s="15">
-        <f>IF($C18="","",$C18+1)</f>
+        <f>IF($C18="","",MIN(EOMONTH(DATE($B$7,$B$9,1),0),DATE($B$7,$B$9,7)))</f>
+        <v/>
+      </c>
+      <c r="E18" s="15">
+        <f>IF($B$11="","",$B$11)</f>
+        <v/>
+      </c>
+      <c r="F18" s="15">
+        <f>IF($E18="","",$E18-1)</f>
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>第3週</t>
+          <t>第2週</t>
         </is>
       </c>
       <c r="C19" s="15">
-        <f>IF($C18="","",$C18+7)</f>
+        <f>IF(DAY(EOMONTH(DATE($B$7,$B$9,1),0))&lt;8,"",DATE($B$7,$B$9,8))</f>
         <v/>
       </c>
       <c r="D19" s="15">
-        <f>IF($C19="","",$C19+1)</f>
+        <f>IF($C19="","",MIN(EOMONTH(DATE($B$7,$B$9,1),0),DATE($B$7,$B$9,14)))</f>
+        <v/>
+      </c>
+      <c r="E19" s="15">
+        <f>IF($E18="","",$E18+7)</f>
+        <v/>
+      </c>
+      <c r="F19" s="15">
+        <f>IF($E19="","",$E19-1)</f>
         <v/>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>第4週</t>
+          <t>第3週</t>
         </is>
       </c>
       <c r="C20" s="15">
-        <f>IF($C19="","",$C19+7)</f>
+        <f>IF(DAY(EOMONTH(DATE($B$7,$B$9,1),0))&lt;15,"",DATE($B$7,$B$9,15))</f>
         <v/>
       </c>
       <c r="D20" s="15">
-        <f>IF($C20="","",$C20+1)</f>
+        <f>IF($C20="","",MIN(EOMONTH(DATE($B$7,$B$9,1),0),DATE($B$7,$B$9,21)))</f>
+        <v/>
+      </c>
+      <c r="E20" s="15">
+        <f>IF($E19="","",$E19+7)</f>
+        <v/>
+      </c>
+      <c r="F20" s="15">
+        <f>IF($E20="","",$E20-1)</f>
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="4" t="inlineStr">
         <is>
+          <t>第4週</t>
+        </is>
+      </c>
+      <c r="C21" s="15">
+        <f>IF(DAY(EOMONTH(DATE($B$7,$B$9,1),0))&lt;22,"",DATE($B$7,$B$9,22))</f>
+        <v/>
+      </c>
+      <c r="D21" s="15">
+        <f>IF($C21="","",MIN(EOMONTH(DATE($B$7,$B$9,1),0),DATE($B$7,$B$9,28)))</f>
+        <v/>
+      </c>
+      <c r="E21" s="15">
+        <f>IF($E20="","",$E20+7)</f>
+        <v/>
+      </c>
+      <c r="F21" s="15">
+        <f>IF($E21="","",$E21-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="4" t="inlineStr">
+        <is>
           <t>第5週</t>
         </is>
       </c>
-      <c r="C21" s="15">
-        <f>IF($C20="","",$C20+7)</f>
-        <v/>
-      </c>
-      <c r="D21" s="15">
-        <f>IF($C21="","",$C21+1)</f>
+      <c r="C22" s="15">
+        <f>IF(DAY(EOMONTH(DATE($B$7,$B$9,1),0))&lt;29,"",DATE($B$7,$B$9,29))</f>
+        <v/>
+      </c>
+      <c r="D22" s="15">
+        <f>IF($C22="","",MIN(EOMONTH(DATE($B$7,$B$9,1),0),DATE($B$7,$B$9,35)))</f>
+        <v/>
+      </c>
+      <c r="E22" s="15">
+        <f>IF($E21="","",$E21+7)</f>
+        <v/>
+      </c>
+      <c r="F22" s="15">
+        <f>IF($E22="","",$E22-1)</f>
         <v/>
       </c>
     </row>
@@ -5797,7 +14159,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O46"/>
+  <dimension ref="A1:P48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5815,6 +14177,7 @@
     <col width="16" customWidth="1" min="13" max="13"/>
     <col width="34" customWidth="1" min="14" max="14"/>
     <col width="34" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -5893,6 +14256,11 @@
           <t>次週アクション（Act）</t>
         </is>
       </c>
+      <c r="P1" s="5" t="inlineStr">
+        <is>
+          <t>実績（手入力上書き）</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="18" t="n"/>
@@ -5929,7 +14297,10 @@
         </is>
       </c>
       <c r="I2" s="19" t="n"/>
-      <c r="J2" s="19" t="n"/>
+      <c r="J2" s="17">
+        <f>IF($P2&lt;&gt;"",$P2,IFERROR(INDEX('10_月次_GH稼働'!$AQ$4:$AQ$8,MATCH($E2,'10_月次_GH稼働'!$AN$4:$AN$8,0)),""))</f>
+        <v/>
+      </c>
       <c r="K2" s="17">
         <f>IFERROR(IF($I2=0,"",$J2/$I2),"")</f>
         <v/>
@@ -5941,6 +14312,7 @@
       <c r="M2" s="16" t="n"/>
       <c r="N2" s="16" t="n"/>
       <c r="O2" s="16" t="n"/>
+      <c r="P2" s="16" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="18" t="n"/>
@@ -5977,7 +14349,10 @@
         </is>
       </c>
       <c r="I3" s="16" t="n"/>
-      <c r="J3" s="16" t="n"/>
+      <c r="J3" s="4">
+        <f>IF($P3&lt;&gt;"",$P3,IFERROR(INDEX('12_月次_営業行動'!$AO$4:$AO$8,MATCH($E3,'12_月次_営業行動'!$AN$4:$AN$8,0)),""))</f>
+        <v/>
+      </c>
       <c r="K3" s="17">
         <f>IFERROR(IF($I3=0,"",$J3/$I3),"")</f>
         <v/>
@@ -5989,6 +14364,7 @@
       <c r="M3" s="16" t="n"/>
       <c r="N3" s="16" t="n"/>
       <c r="O3" s="16" t="n"/>
+      <c r="P3" s="16" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="18" t="n"/>
@@ -6025,7 +14401,10 @@
         </is>
       </c>
       <c r="I4" s="16" t="n"/>
-      <c r="J4" s="16" t="n"/>
+      <c r="J4" s="4">
+        <f>IF($P4&lt;&gt;"",$P4,COUNTIFS('14_案件管理台帳'!$H$2:$H$61,"&gt;="&amp;INDEX('03_設定'!$C$18:$C$22,MATCH($E4,'03_設定'!$B$18:$B$22,0)),'14_案件管理台帳'!$H$2:$H$61,"&lt;="&amp;INDEX('03_設定'!$D$18:$D$22,MATCH($E4,'03_設定'!$B$18:$B$22,0)))+COUNTIFS('14_案件管理台帳'!$I$2:$I$61,"&gt;="&amp;INDEX('03_設定'!$C$18:$C$22,MATCH($E4,'03_設定'!$B$18:$B$22,0)),'14_案件管理台帳'!$I$2:$I$61,"&lt;="&amp;INDEX('03_設定'!$D$18:$D$22,MATCH($E4,'03_設定'!$B$18:$B$22,0))))</f>
+        <v/>
+      </c>
       <c r="K4" s="17">
         <f>IFERROR(IF($I4=0,"",$J4/$I4),"")</f>
         <v/>
@@ -6037,6 +14416,7 @@
       <c r="M4" s="16" t="n"/>
       <c r="N4" s="16" t="n"/>
       <c r="O4" s="16" t="n"/>
+      <c r="P4" s="16" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="18" t="n"/>
@@ -6073,7 +14453,10 @@
         </is>
       </c>
       <c r="I5" s="16" t="n"/>
-      <c r="J5" s="16" t="n"/>
+      <c r="J5" s="4">
+        <f>IF($P5&lt;&gt;"",$P5,COUNTIFS('14_案件管理台帳'!$L$2:$L$61,"&gt;="&amp;INDEX('03_設定'!$C$18:$C$22,MATCH($E5,'03_設定'!$B$18:$B$22,0)),'14_案件管理台帳'!$L$2:$L$61,"&lt;="&amp;INDEX('03_設定'!$D$18:$D$22,MATCH($E5,'03_設定'!$B$18:$B$22,0))))</f>
+        <v/>
+      </c>
       <c r="K5" s="17">
         <f>IFERROR(IF($I5=0,"",$J5/$I5),"")</f>
         <v/>
@@ -6085,6 +14468,7 @@
       <c r="M5" s="16" t="n"/>
       <c r="N5" s="16" t="n"/>
       <c r="O5" s="16" t="n"/>
+      <c r="P5" s="16" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="18" t="n"/>
@@ -6121,7 +14505,10 @@
         </is>
       </c>
       <c r="I6" s="19" t="n"/>
-      <c r="J6" s="19" t="n"/>
+      <c r="J6" s="17">
+        <f>IF($P6&lt;&gt;"",$P6,IFERROR(INDEX('11_月次_SS稼働'!$AQ$4:$AQ$8,MATCH($E6,'11_月次_SS稼働'!$AN$4:$AN$8,0)),""))</f>
+        <v/>
+      </c>
       <c r="K6" s="17">
         <f>IFERROR(IF($I6=0,"",$J6/$I6),"")</f>
         <v/>
@@ -6133,6 +14520,7 @@
       <c r="M6" s="16" t="n"/>
       <c r="N6" s="16" t="n"/>
       <c r="O6" s="16" t="n"/>
+      <c r="P6" s="16" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="18" t="n"/>
@@ -6169,7 +14557,10 @@
         </is>
       </c>
       <c r="I7" s="16" t="n"/>
-      <c r="J7" s="16" t="n"/>
+      <c r="J7" s="4">
+        <f>IF($P7&lt;&gt;"",$P7,COUNTIFS('14_案件管理台帳'!$G$2:$G$61,"&gt;="&amp;INDEX('03_設定'!$C$18:$C$22,MATCH($E7,'03_設定'!$B$18:$B$22,0)),'14_案件管理台帳'!$G$2:$G$61,"&lt;="&amp;INDEX('03_設定'!$D$18:$D$22,MATCH($E7,'03_設定'!$B$18:$B$22,0)),'14_案件管理台帳'!$D$2:$D$61,"SS"))</f>
+        <v/>
+      </c>
       <c r="K7" s="17">
         <f>IFERROR(IF($I7=0,"",$J7/$I7),"")</f>
         <v/>
@@ -6181,6 +14572,7 @@
       <c r="M7" s="16" t="n"/>
       <c r="N7" s="16" t="n"/>
       <c r="O7" s="16" t="n"/>
+      <c r="P7" s="16" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="18" t="n"/>
@@ -6217,7 +14609,10 @@
         </is>
       </c>
       <c r="I8" s="19" t="n"/>
-      <c r="J8" s="19" t="n"/>
+      <c r="J8" s="17">
+        <f>IF($P8&lt;&gt;"",$P8,IFERROR(INDEX('13_月次_加算要件'!$AQ$5:$AQ$9,MATCH($E8,'13_月次_加算要件'!$AN$5:$AN$9,0)),""))</f>
+        <v/>
+      </c>
       <c r="K8" s="17">
         <f>IFERROR(IF($I8=0,"",$J8/$I8),"")</f>
         <v/>
@@ -6229,6 +14624,7 @@
       <c r="M8" s="16" t="n"/>
       <c r="N8" s="16" t="n"/>
       <c r="O8" s="16" t="n"/>
+      <c r="P8" s="16" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="18" t="n"/>
@@ -6265,7 +14661,10 @@
         </is>
       </c>
       <c r="I9" s="16" t="n"/>
-      <c r="J9" s="16" t="n"/>
+      <c r="J9" s="4">
+        <f>IF($P9&lt;&gt;"",$P9,"")</f>
+        <v/>
+      </c>
       <c r="K9" s="17">
         <f>IFERROR(IF($I9=0,"",$J9/$I9),"")</f>
         <v/>
@@ -6277,6 +14676,7 @@
       <c r="M9" s="16" t="n"/>
       <c r="N9" s="16" t="n"/>
       <c r="O9" s="16" t="n"/>
+      <c r="P9" s="16" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="18" t="n"/>
@@ -6313,7 +14713,10 @@
         </is>
       </c>
       <c r="I10" s="16" t="n"/>
-      <c r="J10" s="16" t="n"/>
+      <c r="J10" s="4">
+        <f>IF($P10&lt;&gt;"",$P10,"")</f>
+        <v/>
+      </c>
       <c r="K10" s="17">
         <f>IFERROR(IF($I10=0,"",$J10/$I10),"")</f>
         <v/>
@@ -6325,6 +14728,7 @@
       <c r="M10" s="16" t="n"/>
       <c r="N10" s="16" t="n"/>
       <c r="O10" s="16" t="n"/>
+      <c r="P10" s="16" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="18" t="n"/>
@@ -6361,7 +14765,10 @@
         </is>
       </c>
       <c r="I11" s="19" t="n"/>
-      <c r="J11" s="19" t="n"/>
+      <c r="J11" s="17">
+        <f>IF($P11&lt;&gt;"",$P11,IFERROR(INDEX('10_月次_GH稼働'!$AQ$4:$AQ$8,MATCH($E11,'10_月次_GH稼働'!$AN$4:$AN$8,0)),""))</f>
+        <v/>
+      </c>
       <c r="K11" s="17">
         <f>IFERROR(IF($I11=0,"",$J11/$I11),"")</f>
         <v/>
@@ -6373,6 +14780,7 @@
       <c r="M11" s="16" t="n"/>
       <c r="N11" s="16" t="n"/>
       <c r="O11" s="16" t="n"/>
+      <c r="P11" s="16" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="18" t="n"/>
@@ -6409,7 +14817,10 @@
         </is>
       </c>
       <c r="I12" s="16" t="n"/>
-      <c r="J12" s="16" t="n"/>
+      <c r="J12" s="4">
+        <f>IF($P12&lt;&gt;"",$P12,IFERROR(INDEX('12_月次_営業行動'!$AO$4:$AO$8,MATCH($E12,'12_月次_営業行動'!$AN$4:$AN$8,0)),""))</f>
+        <v/>
+      </c>
       <c r="K12" s="17">
         <f>IFERROR(IF($I12=0,"",$J12/$I12),"")</f>
         <v/>
@@ -6421,6 +14832,7 @@
       <c r="M12" s="16" t="n"/>
       <c r="N12" s="16" t="n"/>
       <c r="O12" s="16" t="n"/>
+      <c r="P12" s="16" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="18" t="n"/>
@@ -6457,7 +14869,10 @@
         </is>
       </c>
       <c r="I13" s="16" t="n"/>
-      <c r="J13" s="16" t="n"/>
+      <c r="J13" s="4">
+        <f>IF($P13&lt;&gt;"",$P13,COUNTIFS('14_案件管理台帳'!$H$2:$H$61,"&gt;="&amp;INDEX('03_設定'!$C$18:$C$22,MATCH($E13,'03_設定'!$B$18:$B$22,0)),'14_案件管理台帳'!$H$2:$H$61,"&lt;="&amp;INDEX('03_設定'!$D$18:$D$22,MATCH($E13,'03_設定'!$B$18:$B$22,0)))+COUNTIFS('14_案件管理台帳'!$I$2:$I$61,"&gt;="&amp;INDEX('03_設定'!$C$18:$C$22,MATCH($E13,'03_設定'!$B$18:$B$22,0)),'14_案件管理台帳'!$I$2:$I$61,"&lt;="&amp;INDEX('03_設定'!$D$18:$D$22,MATCH($E13,'03_設定'!$B$18:$B$22,0))))</f>
+        <v/>
+      </c>
       <c r="K13" s="17">
         <f>IFERROR(IF($I13=0,"",$J13/$I13),"")</f>
         <v/>
@@ -6469,6 +14884,7 @@
       <c r="M13" s="16" t="n"/>
       <c r="N13" s="16" t="n"/>
       <c r="O13" s="16" t="n"/>
+      <c r="P13" s="16" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="18" t="n"/>
@@ -6505,7 +14921,10 @@
         </is>
       </c>
       <c r="I14" s="16" t="n"/>
-      <c r="J14" s="16" t="n"/>
+      <c r="J14" s="4">
+        <f>IF($P14&lt;&gt;"",$P14,COUNTIFS('14_案件管理台帳'!$L$2:$L$61,"&gt;="&amp;INDEX('03_設定'!$C$18:$C$22,MATCH($E14,'03_設定'!$B$18:$B$22,0)),'14_案件管理台帳'!$L$2:$L$61,"&lt;="&amp;INDEX('03_設定'!$D$18:$D$22,MATCH($E14,'03_設定'!$B$18:$B$22,0))))</f>
+        <v/>
+      </c>
       <c r="K14" s="17">
         <f>IFERROR(IF($I14=0,"",$J14/$I14),"")</f>
         <v/>
@@ -6517,6 +14936,7 @@
       <c r="M14" s="16" t="n"/>
       <c r="N14" s="16" t="n"/>
       <c r="O14" s="16" t="n"/>
+      <c r="P14" s="16" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="18" t="n"/>
@@ -6553,7 +14973,10 @@
         </is>
       </c>
       <c r="I15" s="19" t="n"/>
-      <c r="J15" s="19" t="n"/>
+      <c r="J15" s="17">
+        <f>IF($P15&lt;&gt;"",$P15,IFERROR(INDEX('11_月次_SS稼働'!$AQ$4:$AQ$8,MATCH($E15,'11_月次_SS稼働'!$AN$4:$AN$8,0)),""))</f>
+        <v/>
+      </c>
       <c r="K15" s="17">
         <f>IFERROR(IF($I15=0,"",$J15/$I15),"")</f>
         <v/>
@@ -6565,6 +14988,7 @@
       <c r="M15" s="16" t="n"/>
       <c r="N15" s="16" t="n"/>
       <c r="O15" s="16" t="n"/>
+      <c r="P15" s="16" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="18" t="n"/>
@@ -6601,7 +15025,10 @@
         </is>
       </c>
       <c r="I16" s="16" t="n"/>
-      <c r="J16" s="16" t="n"/>
+      <c r="J16" s="4">
+        <f>IF($P16&lt;&gt;"",$P16,COUNTIFS('14_案件管理台帳'!$G$2:$G$61,"&gt;="&amp;INDEX('03_設定'!$C$18:$C$22,MATCH($E16,'03_設定'!$B$18:$B$22,0)),'14_案件管理台帳'!$G$2:$G$61,"&lt;="&amp;INDEX('03_設定'!$D$18:$D$22,MATCH($E16,'03_設定'!$B$18:$B$22,0)),'14_案件管理台帳'!$D$2:$D$61,"SS"))</f>
+        <v/>
+      </c>
       <c r="K16" s="17">
         <f>IFERROR(IF($I16=0,"",$J16/$I16),"")</f>
         <v/>
@@ -6613,6 +15040,7 @@
       <c r="M16" s="16" t="n"/>
       <c r="N16" s="16" t="n"/>
       <c r="O16" s="16" t="n"/>
+      <c r="P16" s="16" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="18" t="n"/>
@@ -6649,7 +15077,10 @@
         </is>
       </c>
       <c r="I17" s="19" t="n"/>
-      <c r="J17" s="19" t="n"/>
+      <c r="J17" s="17">
+        <f>IF($P17&lt;&gt;"",$P17,IFERROR(INDEX('13_月次_加算要件'!$AQ$5:$AQ$9,MATCH($E17,'13_月次_加算要件'!$AN$5:$AN$9,0)),""))</f>
+        <v/>
+      </c>
       <c r="K17" s="17">
         <f>IFERROR(IF($I17=0,"",$J17/$I17),"")</f>
         <v/>
@@ -6661,6 +15092,7 @@
       <c r="M17" s="16" t="n"/>
       <c r="N17" s="16" t="n"/>
       <c r="O17" s="16" t="n"/>
+      <c r="P17" s="16" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="18" t="n"/>
@@ -6697,7 +15129,10 @@
         </is>
       </c>
       <c r="I18" s="16" t="n"/>
-      <c r="J18" s="16" t="n"/>
+      <c r="J18" s="4">
+        <f>IF($P18&lt;&gt;"",$P18,"")</f>
+        <v/>
+      </c>
       <c r="K18" s="17">
         <f>IFERROR(IF($I18=0,"",$J18/$I18),"")</f>
         <v/>
@@ -6709,6 +15144,7 @@
       <c r="M18" s="16" t="n"/>
       <c r="N18" s="16" t="n"/>
       <c r="O18" s="16" t="n"/>
+      <c r="P18" s="16" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="18" t="n"/>
@@ -6745,7 +15181,10 @@
         </is>
       </c>
       <c r="I19" s="16" t="n"/>
-      <c r="J19" s="16" t="n"/>
+      <c r="J19" s="4">
+        <f>IF($P19&lt;&gt;"",$P19,"")</f>
+        <v/>
+      </c>
       <c r="K19" s="17">
         <f>IFERROR(IF($I19=0,"",$J19/$I19),"")</f>
         <v/>
@@ -6757,6 +15196,7 @@
       <c r="M19" s="16" t="n"/>
       <c r="N19" s="16" t="n"/>
       <c r="O19" s="16" t="n"/>
+      <c r="P19" s="16" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="18" t="n"/>
@@ -6793,7 +15233,10 @@
         </is>
       </c>
       <c r="I20" s="19" t="n"/>
-      <c r="J20" s="19" t="n"/>
+      <c r="J20" s="17">
+        <f>IF($P20&lt;&gt;"",$P20,IFERROR(INDEX('10_月次_GH稼働'!$AQ$4:$AQ$8,MATCH($E20,'10_月次_GH稼働'!$AN$4:$AN$8,0)),""))</f>
+        <v/>
+      </c>
       <c r="K20" s="17">
         <f>IFERROR(IF($I20=0,"",$J20/$I20),"")</f>
         <v/>
@@ -6805,6 +15248,7 @@
       <c r="M20" s="16" t="n"/>
       <c r="N20" s="16" t="n"/>
       <c r="O20" s="16" t="n"/>
+      <c r="P20" s="16" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="18" t="n"/>
@@ -6841,7 +15285,10 @@
         </is>
       </c>
       <c r="I21" s="16" t="n"/>
-      <c r="J21" s="16" t="n"/>
+      <c r="J21" s="4">
+        <f>IF($P21&lt;&gt;"",$P21,IFERROR(INDEX('12_月次_営業行動'!$AO$4:$AO$8,MATCH($E21,'12_月次_営業行動'!$AN$4:$AN$8,0)),""))</f>
+        <v/>
+      </c>
       <c r="K21" s="17">
         <f>IFERROR(IF($I21=0,"",$J21/$I21),"")</f>
         <v/>
@@ -6853,6 +15300,7 @@
       <c r="M21" s="16" t="n"/>
       <c r="N21" s="16" t="n"/>
       <c r="O21" s="16" t="n"/>
+      <c r="P21" s="16" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="18" t="n"/>
@@ -6889,7 +15337,10 @@
         </is>
       </c>
       <c r="I22" s="16" t="n"/>
-      <c r="J22" s="16" t="n"/>
+      <c r="J22" s="4">
+        <f>IF($P22&lt;&gt;"",$P22,COUNTIFS('14_案件管理台帳'!$H$2:$H$61,"&gt;="&amp;INDEX('03_設定'!$C$18:$C$22,MATCH($E22,'03_設定'!$B$18:$B$22,0)),'14_案件管理台帳'!$H$2:$H$61,"&lt;="&amp;INDEX('03_設定'!$D$18:$D$22,MATCH($E22,'03_設定'!$B$18:$B$22,0)))+COUNTIFS('14_案件管理台帳'!$I$2:$I$61,"&gt;="&amp;INDEX('03_設定'!$C$18:$C$22,MATCH($E22,'03_設定'!$B$18:$B$22,0)),'14_案件管理台帳'!$I$2:$I$61,"&lt;="&amp;INDEX('03_設定'!$D$18:$D$22,MATCH($E22,'03_設定'!$B$18:$B$22,0))))</f>
+        <v/>
+      </c>
       <c r="K22" s="17">
         <f>IFERROR(IF($I22=0,"",$J22/$I22),"")</f>
         <v/>
@@ -6901,6 +15352,7 @@
       <c r="M22" s="16" t="n"/>
       <c r="N22" s="16" t="n"/>
       <c r="O22" s="16" t="n"/>
+      <c r="P22" s="16" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="18" t="n"/>
@@ -6937,7 +15389,10 @@
         </is>
       </c>
       <c r="I23" s="16" t="n"/>
-      <c r="J23" s="16" t="n"/>
+      <c r="J23" s="4">
+        <f>IF($P23&lt;&gt;"",$P23,COUNTIFS('14_案件管理台帳'!$L$2:$L$61,"&gt;="&amp;INDEX('03_設定'!$C$18:$C$22,MATCH($E23,'03_設定'!$B$18:$B$22,0)),'14_案件管理台帳'!$L$2:$L$61,"&lt;="&amp;INDEX('03_設定'!$D$18:$D$22,MATCH($E23,'03_設定'!$B$18:$B$22,0))))</f>
+        <v/>
+      </c>
       <c r="K23" s="17">
         <f>IFERROR(IF($I23=0,"",$J23/$I23),"")</f>
         <v/>
@@ -6949,6 +15404,7 @@
       <c r="M23" s="16" t="n"/>
       <c r="N23" s="16" t="n"/>
       <c r="O23" s="16" t="n"/>
+      <c r="P23" s="16" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="18" t="n"/>
@@ -6985,7 +15441,10 @@
         </is>
       </c>
       <c r="I24" s="19" t="n"/>
-      <c r="J24" s="19" t="n"/>
+      <c r="J24" s="17">
+        <f>IF($P24&lt;&gt;"",$P24,IFERROR(INDEX('11_月次_SS稼働'!$AQ$4:$AQ$8,MATCH($E24,'11_月次_SS稼働'!$AN$4:$AN$8,0)),""))</f>
+        <v/>
+      </c>
       <c r="K24" s="17">
         <f>IFERROR(IF($I24=0,"",$J24/$I24),"")</f>
         <v/>
@@ -6997,6 +15456,7 @@
       <c r="M24" s="16" t="n"/>
       <c r="N24" s="16" t="n"/>
       <c r="O24" s="16" t="n"/>
+      <c r="P24" s="16" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="18" t="n"/>
@@ -7033,7 +15493,10 @@
         </is>
       </c>
       <c r="I25" s="16" t="n"/>
-      <c r="J25" s="16" t="n"/>
+      <c r="J25" s="4">
+        <f>IF($P25&lt;&gt;"",$P25,COUNTIFS('14_案件管理台帳'!$G$2:$G$61,"&gt;="&amp;INDEX('03_設定'!$C$18:$C$22,MATCH($E25,'03_設定'!$B$18:$B$22,0)),'14_案件管理台帳'!$G$2:$G$61,"&lt;="&amp;INDEX('03_設定'!$D$18:$D$22,MATCH($E25,'03_設定'!$B$18:$B$22,0)),'14_案件管理台帳'!$D$2:$D$61,"SS"))</f>
+        <v/>
+      </c>
       <c r="K25" s="17">
         <f>IFERROR(IF($I25=0,"",$J25/$I25),"")</f>
         <v/>
@@ -7045,6 +15508,7 @@
       <c r="M25" s="16" t="n"/>
       <c r="N25" s="16" t="n"/>
       <c r="O25" s="16" t="n"/>
+      <c r="P25" s="16" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="18" t="n"/>
@@ -7081,7 +15545,10 @@
         </is>
       </c>
       <c r="I26" s="19" t="n"/>
-      <c r="J26" s="19" t="n"/>
+      <c r="J26" s="17">
+        <f>IF($P26&lt;&gt;"",$P26,IFERROR(INDEX('13_月次_加算要件'!$AQ$5:$AQ$9,MATCH($E26,'13_月次_加算要件'!$AN$5:$AN$9,0)),""))</f>
+        <v/>
+      </c>
       <c r="K26" s="17">
         <f>IFERROR(IF($I26=0,"",$J26/$I26),"")</f>
         <v/>
@@ -7093,6 +15560,7 @@
       <c r="M26" s="16" t="n"/>
       <c r="N26" s="16" t="n"/>
       <c r="O26" s="16" t="n"/>
+      <c r="P26" s="16" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="18" t="n"/>
@@ -7129,7 +15597,10 @@
         </is>
       </c>
       <c r="I27" s="16" t="n"/>
-      <c r="J27" s="16" t="n"/>
+      <c r="J27" s="4">
+        <f>IF($P27&lt;&gt;"",$P27,"")</f>
+        <v/>
+      </c>
       <c r="K27" s="17">
         <f>IFERROR(IF($I27=0,"",$J27/$I27),"")</f>
         <v/>
@@ -7141,6 +15612,7 @@
       <c r="M27" s="16" t="n"/>
       <c r="N27" s="16" t="n"/>
       <c r="O27" s="16" t="n"/>
+      <c r="P27" s="16" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="18" t="n"/>
@@ -7177,7 +15649,10 @@
         </is>
       </c>
       <c r="I28" s="16" t="n"/>
-      <c r="J28" s="16" t="n"/>
+      <c r="J28" s="4">
+        <f>IF($P28&lt;&gt;"",$P28,"")</f>
+        <v/>
+      </c>
       <c r="K28" s="17">
         <f>IFERROR(IF($I28=0,"",$J28/$I28),"")</f>
         <v/>
@@ -7189,6 +15664,7 @@
       <c r="M28" s="16" t="n"/>
       <c r="N28" s="16" t="n"/>
       <c r="O28" s="16" t="n"/>
+      <c r="P28" s="16" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="18" t="n"/>
@@ -7225,7 +15701,10 @@
         </is>
       </c>
       <c r="I29" s="19" t="n"/>
-      <c r="J29" s="19" t="n"/>
+      <c r="J29" s="17">
+        <f>IF($P29&lt;&gt;"",$P29,IFERROR(INDEX('10_月次_GH稼働'!$AQ$4:$AQ$8,MATCH($E29,'10_月次_GH稼働'!$AN$4:$AN$8,0)),""))</f>
+        <v/>
+      </c>
       <c r="K29" s="17">
         <f>IFERROR(IF($I29=0,"",$J29/$I29),"")</f>
         <v/>
@@ -7237,6 +15716,7 @@
       <c r="M29" s="16" t="n"/>
       <c r="N29" s="16" t="n"/>
       <c r="O29" s="16" t="n"/>
+      <c r="P29" s="16" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="18" t="n"/>
@@ -7273,7 +15753,10 @@
         </is>
       </c>
       <c r="I30" s="16" t="n"/>
-      <c r="J30" s="16" t="n"/>
+      <c r="J30" s="4">
+        <f>IF($P30&lt;&gt;"",$P30,IFERROR(INDEX('12_月次_営業行動'!$AO$4:$AO$8,MATCH($E30,'12_月次_営業行動'!$AN$4:$AN$8,0)),""))</f>
+        <v/>
+      </c>
       <c r="K30" s="17">
         <f>IFERROR(IF($I30=0,"",$J30/$I30),"")</f>
         <v/>
@@ -7285,6 +15768,7 @@
       <c r="M30" s="16" t="n"/>
       <c r="N30" s="16" t="n"/>
       <c r="O30" s="16" t="n"/>
+      <c r="P30" s="16" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="18" t="n"/>
@@ -7321,7 +15805,10 @@
         </is>
       </c>
       <c r="I31" s="16" t="n"/>
-      <c r="J31" s="16" t="n"/>
+      <c r="J31" s="4">
+        <f>IF($P31&lt;&gt;"",$P31,COUNTIFS('14_案件管理台帳'!$H$2:$H$61,"&gt;="&amp;INDEX('03_設定'!$C$18:$C$22,MATCH($E31,'03_設定'!$B$18:$B$22,0)),'14_案件管理台帳'!$H$2:$H$61,"&lt;="&amp;INDEX('03_設定'!$D$18:$D$22,MATCH($E31,'03_設定'!$B$18:$B$22,0)))+COUNTIFS('14_案件管理台帳'!$I$2:$I$61,"&gt;="&amp;INDEX('03_設定'!$C$18:$C$22,MATCH($E31,'03_設定'!$B$18:$B$22,0)),'14_案件管理台帳'!$I$2:$I$61,"&lt;="&amp;INDEX('03_設定'!$D$18:$D$22,MATCH($E31,'03_設定'!$B$18:$B$22,0))))</f>
+        <v/>
+      </c>
       <c r="K31" s="17">
         <f>IFERROR(IF($I31=0,"",$J31/$I31),"")</f>
         <v/>
@@ -7333,6 +15820,7 @@
       <c r="M31" s="16" t="n"/>
       <c r="N31" s="16" t="n"/>
       <c r="O31" s="16" t="n"/>
+      <c r="P31" s="16" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="18" t="n"/>
@@ -7369,7 +15857,10 @@
         </is>
       </c>
       <c r="I32" s="16" t="n"/>
-      <c r="J32" s="16" t="n"/>
+      <c r="J32" s="4">
+        <f>IF($P32&lt;&gt;"",$P32,COUNTIFS('14_案件管理台帳'!$L$2:$L$61,"&gt;="&amp;INDEX('03_設定'!$C$18:$C$22,MATCH($E32,'03_設定'!$B$18:$B$22,0)),'14_案件管理台帳'!$L$2:$L$61,"&lt;="&amp;INDEX('03_設定'!$D$18:$D$22,MATCH($E32,'03_設定'!$B$18:$B$22,0))))</f>
+        <v/>
+      </c>
       <c r="K32" s="17">
         <f>IFERROR(IF($I32=0,"",$J32/$I32),"")</f>
         <v/>
@@ -7381,6 +15872,7 @@
       <c r="M32" s="16" t="n"/>
       <c r="N32" s="16" t="n"/>
       <c r="O32" s="16" t="n"/>
+      <c r="P32" s="16" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="18" t="n"/>
@@ -7417,7 +15909,10 @@
         </is>
       </c>
       <c r="I33" s="19" t="n"/>
-      <c r="J33" s="19" t="n"/>
+      <c r="J33" s="17">
+        <f>IF($P33&lt;&gt;"",$P33,IFERROR(INDEX('11_月次_SS稼働'!$AQ$4:$AQ$8,MATCH($E33,'11_月次_SS稼働'!$AN$4:$AN$8,0)),""))</f>
+        <v/>
+      </c>
       <c r="K33" s="17">
         <f>IFERROR(IF($I33=0,"",$J33/$I33),"")</f>
         <v/>
@@ -7429,6 +15924,7 @@
       <c r="M33" s="16" t="n"/>
       <c r="N33" s="16" t="n"/>
       <c r="O33" s="16" t="n"/>
+      <c r="P33" s="16" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="18" t="n"/>
@@ -7465,7 +15961,10 @@
         </is>
       </c>
       <c r="I34" s="16" t="n"/>
-      <c r="J34" s="16" t="n"/>
+      <c r="J34" s="4">
+        <f>IF($P34&lt;&gt;"",$P34,COUNTIFS('14_案件管理台帳'!$G$2:$G$61,"&gt;="&amp;INDEX('03_設定'!$C$18:$C$22,MATCH($E34,'03_設定'!$B$18:$B$22,0)),'14_案件管理台帳'!$G$2:$G$61,"&lt;="&amp;INDEX('03_設定'!$D$18:$D$22,MATCH($E34,'03_設定'!$B$18:$B$22,0)),'14_案件管理台帳'!$D$2:$D$61,"SS"))</f>
+        <v/>
+      </c>
       <c r="K34" s="17">
         <f>IFERROR(IF($I34=0,"",$J34/$I34),"")</f>
         <v/>
@@ -7477,6 +15976,7 @@
       <c r="M34" s="16" t="n"/>
       <c r="N34" s="16" t="n"/>
       <c r="O34" s="16" t="n"/>
+      <c r="P34" s="16" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="18" t="n"/>
@@ -7513,7 +16013,10 @@
         </is>
       </c>
       <c r="I35" s="19" t="n"/>
-      <c r="J35" s="19" t="n"/>
+      <c r="J35" s="17">
+        <f>IF($P35&lt;&gt;"",$P35,IFERROR(INDEX('13_月次_加算要件'!$AQ$5:$AQ$9,MATCH($E35,'13_月次_加算要件'!$AN$5:$AN$9,0)),""))</f>
+        <v/>
+      </c>
       <c r="K35" s="17">
         <f>IFERROR(IF($I35=0,"",$J35/$I35),"")</f>
         <v/>
@@ -7525,6 +16028,7 @@
       <c r="M35" s="16" t="n"/>
       <c r="N35" s="16" t="n"/>
       <c r="O35" s="16" t="n"/>
+      <c r="P35" s="16" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="18" t="n"/>
@@ -7561,7 +16065,10 @@
         </is>
       </c>
       <c r="I36" s="16" t="n"/>
-      <c r="J36" s="16" t="n"/>
+      <c r="J36" s="4">
+        <f>IF($P36&lt;&gt;"",$P36,"")</f>
+        <v/>
+      </c>
       <c r="K36" s="17">
         <f>IFERROR(IF($I36=0,"",$J36/$I36),"")</f>
         <v/>
@@ -7573,6 +16080,7 @@
       <c r="M36" s="16" t="n"/>
       <c r="N36" s="16" t="n"/>
       <c r="O36" s="16" t="n"/>
+      <c r="P36" s="16" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="18" t="n"/>
@@ -7609,7 +16117,10 @@
         </is>
       </c>
       <c r="I37" s="16" t="n"/>
-      <c r="J37" s="16" t="n"/>
+      <c r="J37" s="4">
+        <f>IF($P37&lt;&gt;"",$P37,"")</f>
+        <v/>
+      </c>
       <c r="K37" s="17">
         <f>IFERROR(IF($I37=0,"",$J37/$I37),"")</f>
         <v/>
@@ -7621,6 +16132,7 @@
       <c r="M37" s="16" t="n"/>
       <c r="N37" s="16" t="n"/>
       <c r="O37" s="16" t="n"/>
+      <c r="P37" s="16" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="18" t="n"/>
@@ -7657,7 +16169,10 @@
         </is>
       </c>
       <c r="I38" s="19" t="n"/>
-      <c r="J38" s="19" t="n"/>
+      <c r="J38" s="17">
+        <f>IF($P38&lt;&gt;"",$P38,IFERROR(INDEX('10_月次_GH稼働'!$AQ$4:$AQ$8,MATCH($E38,'10_月次_GH稼働'!$AN$4:$AN$8,0)),""))</f>
+        <v/>
+      </c>
       <c r="K38" s="17">
         <f>IFERROR(IF($I38=0,"",$J38/$I38),"")</f>
         <v/>
@@ -7669,6 +16184,7 @@
       <c r="M38" s="16" t="n"/>
       <c r="N38" s="16" t="n"/>
       <c r="O38" s="16" t="n"/>
+      <c r="P38" s="16" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="18" t="n"/>
@@ -7705,7 +16221,10 @@
         </is>
       </c>
       <c r="I39" s="16" t="n"/>
-      <c r="J39" s="16" t="n"/>
+      <c r="J39" s="4">
+        <f>IF($P39&lt;&gt;"",$P39,IFERROR(INDEX('12_月次_営業行動'!$AO$4:$AO$8,MATCH($E39,'12_月次_営業行動'!$AN$4:$AN$8,0)),""))</f>
+        <v/>
+      </c>
       <c r="K39" s="17">
         <f>IFERROR(IF($I39=0,"",$J39/$I39),"")</f>
         <v/>
@@ -7717,6 +16236,7 @@
       <c r="M39" s="16" t="n"/>
       <c r="N39" s="16" t="n"/>
       <c r="O39" s="16" t="n"/>
+      <c r="P39" s="16" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="18" t="n"/>
@@ -7753,7 +16273,10 @@
         </is>
       </c>
       <c r="I40" s="16" t="n"/>
-      <c r="J40" s="16" t="n"/>
+      <c r="J40" s="4">
+        <f>IF($P40&lt;&gt;"",$P40,COUNTIFS('14_案件管理台帳'!$H$2:$H$61,"&gt;="&amp;INDEX('03_設定'!$C$18:$C$22,MATCH($E40,'03_設定'!$B$18:$B$22,0)),'14_案件管理台帳'!$H$2:$H$61,"&lt;="&amp;INDEX('03_設定'!$D$18:$D$22,MATCH($E40,'03_設定'!$B$18:$B$22,0)))+COUNTIFS('14_案件管理台帳'!$I$2:$I$61,"&gt;="&amp;INDEX('03_設定'!$C$18:$C$22,MATCH($E40,'03_設定'!$B$18:$B$22,0)),'14_案件管理台帳'!$I$2:$I$61,"&lt;="&amp;INDEX('03_設定'!$D$18:$D$22,MATCH($E40,'03_設定'!$B$18:$B$22,0))))</f>
+        <v/>
+      </c>
       <c r="K40" s="17">
         <f>IFERROR(IF($I40=0,"",$J40/$I40),"")</f>
         <v/>
@@ -7765,6 +16288,7 @@
       <c r="M40" s="16" t="n"/>
       <c r="N40" s="16" t="n"/>
       <c r="O40" s="16" t="n"/>
+      <c r="P40" s="16" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="18" t="n"/>
@@ -7801,7 +16325,10 @@
         </is>
       </c>
       <c r="I41" s="16" t="n"/>
-      <c r="J41" s="16" t="n"/>
+      <c r="J41" s="4">
+        <f>IF($P41&lt;&gt;"",$P41,COUNTIFS('14_案件管理台帳'!$L$2:$L$61,"&gt;="&amp;INDEX('03_設定'!$C$18:$C$22,MATCH($E41,'03_設定'!$B$18:$B$22,0)),'14_案件管理台帳'!$L$2:$L$61,"&lt;="&amp;INDEX('03_設定'!$D$18:$D$22,MATCH($E41,'03_設定'!$B$18:$B$22,0))))</f>
+        <v/>
+      </c>
       <c r="K41" s="17">
         <f>IFERROR(IF($I41=0,"",$J41/$I41),"")</f>
         <v/>
@@ -7813,6 +16340,7 @@
       <c r="M41" s="16" t="n"/>
       <c r="N41" s="16" t="n"/>
       <c r="O41" s="16" t="n"/>
+      <c r="P41" s="16" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="18" t="n"/>
@@ -7849,7 +16377,10 @@
         </is>
       </c>
       <c r="I42" s="19" t="n"/>
-      <c r="J42" s="19" t="n"/>
+      <c r="J42" s="17">
+        <f>IF($P42&lt;&gt;"",$P42,IFERROR(INDEX('11_月次_SS稼働'!$AQ$4:$AQ$8,MATCH($E42,'11_月次_SS稼働'!$AN$4:$AN$8,0)),""))</f>
+        <v/>
+      </c>
       <c r="K42" s="17">
         <f>IFERROR(IF($I42=0,"",$J42/$I42),"")</f>
         <v/>
@@ -7861,6 +16392,7 @@
       <c r="M42" s="16" t="n"/>
       <c r="N42" s="16" t="n"/>
       <c r="O42" s="16" t="n"/>
+      <c r="P42" s="16" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="18" t="n"/>
@@ -7897,7 +16429,10 @@
         </is>
       </c>
       <c r="I43" s="16" t="n"/>
-      <c r="J43" s="16" t="n"/>
+      <c r="J43" s="4">
+        <f>IF($P43&lt;&gt;"",$P43,COUNTIFS('14_案件管理台帳'!$G$2:$G$61,"&gt;="&amp;INDEX('03_設定'!$C$18:$C$22,MATCH($E43,'03_設定'!$B$18:$B$22,0)),'14_案件管理台帳'!$G$2:$G$61,"&lt;="&amp;INDEX('03_設定'!$D$18:$D$22,MATCH($E43,'03_設定'!$B$18:$B$22,0)),'14_案件管理台帳'!$D$2:$D$61,"SS"))</f>
+        <v/>
+      </c>
       <c r="K43" s="17">
         <f>IFERROR(IF($I43=0,"",$J43/$I43),"")</f>
         <v/>
@@ -7909,6 +16444,7 @@
       <c r="M43" s="16" t="n"/>
       <c r="N43" s="16" t="n"/>
       <c r="O43" s="16" t="n"/>
+      <c r="P43" s="16" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="18" t="n"/>
@@ -7945,7 +16481,10 @@
         </is>
       </c>
       <c r="I44" s="19" t="n"/>
-      <c r="J44" s="19" t="n"/>
+      <c r="J44" s="17">
+        <f>IF($P44&lt;&gt;"",$P44,IFERROR(INDEX('13_月次_加算要件'!$AQ$5:$AQ$9,MATCH($E44,'13_月次_加算要件'!$AN$5:$AN$9,0)),""))</f>
+        <v/>
+      </c>
       <c r="K44" s="17">
         <f>IFERROR(IF($I44=0,"",$J44/$I44),"")</f>
         <v/>
@@ -7957,6 +16496,7 @@
       <c r="M44" s="16" t="n"/>
       <c r="N44" s="16" t="n"/>
       <c r="O44" s="16" t="n"/>
+      <c r="P44" s="16" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="18" t="n"/>
@@ -7993,7 +16533,10 @@
         </is>
       </c>
       <c r="I45" s="16" t="n"/>
-      <c r="J45" s="16" t="n"/>
+      <c r="J45" s="4">
+        <f>IF($P45&lt;&gt;"",$P45,"")</f>
+        <v/>
+      </c>
       <c r="K45" s="17">
         <f>IFERROR(IF($I45=0,"",$J45/$I45),"")</f>
         <v/>
@@ -8005,6 +16548,7 @@
       <c r="M45" s="16" t="n"/>
       <c r="N45" s="16" t="n"/>
       <c r="O45" s="16" t="n"/>
+      <c r="P45" s="16" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="18" t="n"/>
@@ -8041,7 +16585,10 @@
         </is>
       </c>
       <c r="I46" s="16" t="n"/>
-      <c r="J46" s="16" t="n"/>
+      <c r="J46" s="4">
+        <f>IF($P46&lt;&gt;"",$P46,"")</f>
+        <v/>
+      </c>
       <c r="K46" s="17">
         <f>IFERROR(IF($I46=0,"",$J46/$I46),"")</f>
         <v/>
@@ -8053,9 +16600,17 @@
       <c r="M46" s="16" t="n"/>
       <c r="N46" s="16" t="n"/>
       <c r="O46" s="16" t="n"/>
+      <c r="P46" s="16" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="13" t="inlineStr">
+        <is>
+          <t>※ J列『実績』は 10〜14 の入力シートから自動集計されます。自動値を使わない場合のみ P列に数値を入れると、そちらが優先されます。</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O46"/>
+  <autoFilter ref="A1:P46"/>
   <conditionalFormatting sqref="K2:K46">
     <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="0">
       <formula>1</formula>
@@ -9095,7 +17650,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -9640,38 +18195,143 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
+          <t>構造</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>月シート（4月〜26年9月の22枚）が、利用者ごとの日別稼働カレンダー・SS予約・営業行動・案件管理・加算要件の入力面を兼ねている。週間PDCAの文章は BF16 等の長大な文字列連結式で自動生成されている。</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>入力面（原簿）と管理面（PDCA）が同じシートに同居し、月が変わるたびシートを増やす必要がある。連結式で作った文章は、あとから数値として再利用できない。</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>原簿は月次入力シートとして分離し、集計値だけをPDCA側へ渡す。</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>10〜13の月次入力シートに分離。週別集計値は05_週次KPIログが自動で参照する。</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>構造</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>案件管理が『kintone名×日別セルに進捗記号』のマトリクス（55〜78行）。相談元・区分・希望種別が別セルに散る。</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>同じ案件の履歴が月シートをまたいで分断され、発掘→見学→体験→契約のリードタイムが測れない。</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>案件は1件1行の台帳にし、各フェーズの日付を列で持つ。</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>14_案件管理台帳。日付列から見学・体験・入居件数を週次で自動集計し、停滞14日超は赤表示。</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>運用</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>重度障害者支援体制・福祉専門職員配置等加算の要件確認が、月シートの隅にチェック欄として置かれている（BR88 常勤比率0.368→✕ 等）。</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>算定可否の根拠が月シートを開かないと見えず、要件を割った時に誰がいつ気づくかが運用任せ。</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>要件判定を独立させ、割り込み時に『要対応』として表示する。</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>13_月次_加算要件に集約。夜勤加配は日別実績から取得率を自動計算、体制加算は✕が1つでもあれば『要対応』。</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
           <t>拡張</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>40施設分のファイルが個別に存在し、AMは自分の担当分だけを見る運用。</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>エリア長・本部が全体傾向（未達KPI・遅延課題の偏り）を把握するのに手作業の集約が必要。</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="E19" s="4" t="inlineStr">
         <is>
           <t>縦持ちログを束ねてピボット集計できる形にする。</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr">
+      <c r="F19" s="4" t="inlineStr">
         <is>
           <t>05_週次KPIログは施設名・担当者を各行に持つため、40施設分を連結してそのまま集計可能。06に担当AM別の遅延件数を実装。</t>
         </is>
       </c>
-      <c r="G16" s="4" t="inlineStr">
+      <c r="G19" s="4" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G16"/>
-  <conditionalFormatting sqref="G2:G16">
+  <autoFilter ref="A1:G19"/>
+  <conditionalFormatting sqref="G2:G19">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$G2="高"</formula>
     </cfRule>

--- a/dist/週間PDCA_改善版テンプレート.xlsx
+++ b/dist/週間PDCA_改善版テンプレート.xlsx
@@ -22,6 +22,8 @@
     <sheet name="12_月次_営業行動" sheetId="13" state="visible" r:id="rId13"/>
     <sheet name="13_月次_加算要件" sheetId="14" state="visible" r:id="rId14"/>
     <sheet name="14_案件管理台帳" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="15_KPI累積ログ" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="16_年間推移" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames>
     <definedName name="施設名リスト">'01_施設マスタ'!$B$2:$B$41</definedName>
@@ -35,8 +37,9 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'01_施設マスタ'!$A$1:$I$41</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'04_課題管理表'!$A$1:$U$61</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'05_週次KPIログ'!$A$1:$P$46</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'07_改善提案一覧'!$A$1:$G$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'07_改善提案一覧'!$A$1:$G$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'14_案件管理台帳'!$A$1:$Q$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'15_KPI累積ログ'!$A$1:$P$2000</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -610,7 +613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:C11"/>
+  <dimension ref="B2:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -707,10 +710,34 @@
     <row r="11" ht="34" customHeight="1">
       <c r="B11" s="3" t="inlineStr">
         <is>
+          <t>継続運用</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>月ごとにシートを増やしません。月末に締め処理を行うと、当月ブックが実績として保管され、週次KPIは 15_KPI累積ログ に値で積み上がり、日別入力欄が空の翌月ブックが作られます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="34" customHeight="1">
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>過去の参照</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>月をまたいだ推移は 16_年間推移 で見ます。個別の日別実績は、締めのときに保管された『〇〇_実績.xlsx』を開いてください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="34" customHeight="1">
+      <c r="B13" s="3" t="inlineStr">
+        <is>
           <t>改善の根拠</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>07_改善提案一覧 に、旧シートで検出した具体的な不具合と改善内容を記載しています。</t>
         </is>
@@ -9127,6 +9154,854 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:R6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="9" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="30" customWidth="1" min="14" max="14"/>
+    <col width="30" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>記録日</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>対象施設</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>年</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>週</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>カテゴリ</t>
+        </is>
+      </c>
+      <c r="G1" s="5" t="inlineStr">
+        <is>
+          <t>指標名</t>
+        </is>
+      </c>
+      <c r="H1" s="5" t="inlineStr">
+        <is>
+          <t>単位</t>
+        </is>
+      </c>
+      <c r="I1" s="5" t="inlineStr">
+        <is>
+          <t>週次目標</t>
+        </is>
+      </c>
+      <c r="J1" s="5" t="inlineStr">
+        <is>
+          <t>実績</t>
+        </is>
+      </c>
+      <c r="K1" s="5" t="inlineStr">
+        <is>
+          <t>達成率</t>
+        </is>
+      </c>
+      <c r="L1" s="5" t="inlineStr">
+        <is>
+          <t>差異</t>
+        </is>
+      </c>
+      <c r="M1" s="5" t="inlineStr">
+        <is>
+          <t>担当者</t>
+        </is>
+      </c>
+      <c r="N1" s="5" t="inlineStr">
+        <is>
+          <t>未達要因（Check）</t>
+        </is>
+      </c>
+      <c r="O1" s="5" t="inlineStr">
+        <is>
+          <t>次週アクション（Act）</t>
+        </is>
+      </c>
+      <c r="P1" s="5" t="inlineStr">
+        <is>
+          <t>締め処理日</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="R3" s="28" t="inlineStr">
+        <is>
+          <t>このシートは月締め処理（tools/pdca/close_month.py）で自動追記される保管庫です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="R4" s="13" t="inlineStr">
+        <is>
+          <t>・数式ではなく『値』が入ります。対象月を切り替えても過去の実績が消えません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="R5" s="13" t="inlineStr">
+        <is>
+          <t>・手で編集しないでください。修正が必要な場合は該当行を直し、締め日を入れ直します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="R6" s="13" t="inlineStr">
+        <is>
+          <t>・40施設分をこのシートに縦に積めば、そのままピボットで全社集計できます。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:P2000"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:P15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
+    <col width="9" customWidth="1" min="12" max="12"/>
+    <col width="9" customWidth="1" min="13" max="13"/>
+    <col width="9" customWidth="1" min="14" max="14"/>
+    <col width="9" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>年間推移（15_KPI累積ログの集計）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="20">
+        <f>設定対象年&amp;"年度／"&amp;設定対象施設</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>※ 月締めが済んだ月だけ数値が入ります。率は週平均、件数は月合計です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>指標名</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>単位</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>4月</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>5月</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>6月</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>7月</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>8月</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>9月</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>10月</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="inlineStr">
+        <is>
+          <t>11月</t>
+        </is>
+      </c>
+      <c r="L6" s="5" t="inlineStr">
+        <is>
+          <t>12月</t>
+        </is>
+      </c>
+      <c r="M6" s="5" t="inlineStr">
+        <is>
+          <t>1月</t>
+        </is>
+      </c>
+      <c r="N6" s="5" t="inlineStr">
+        <is>
+          <t>2月</t>
+        </is>
+      </c>
+      <c r="O6" s="5" t="inlineStr">
+        <is>
+          <t>3月</t>
+        </is>
+      </c>
+      <c r="P6" s="5" t="inlineStr">
+        <is>
+          <t>年度計/平均</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>GH稼働率</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D7" s="17">
+        <f>IFERROR(AVERAGEIFS('15_KPI累積ログ'!$J$2:$J$2000,'15_KPI累積ログ'!$G$2:$G$2000,$B7,'15_KPI累積ログ'!$C$2:$C$2000,設定対象年,'15_KPI累積ログ'!$D$2:$D$2000,4),"")</f>
+        <v/>
+      </c>
+      <c r="E7" s="17">
+        <f>IFERROR(AVERAGEIFS('15_KPI累積ログ'!$J$2:$J$2000,'15_KPI累積ログ'!$G$2:$G$2000,$B7,'15_KPI累積ログ'!$C$2:$C$2000,設定対象年,'15_KPI累積ログ'!$D$2:$D$2000,5),"")</f>
+        <v/>
+      </c>
+      <c r="F7" s="17">
+        <f>IFERROR(AVERAGEIFS('15_KPI累積ログ'!$J$2:$J$2000,'15_KPI累積ログ'!$G$2:$G$2000,$B7,'15_KPI累積ログ'!$C$2:$C$2000,設定対象年,'15_KPI累積ログ'!$D$2:$D$2000,6),"")</f>
+        <v/>
+      </c>
+      <c r="G7" s="17">
+        <f>IFERROR(AVERAGEIFS('15_KPI累積ログ'!$J$2:$J$2000,'15_KPI累積ログ'!$G$2:$G$2000,$B7,'15_KPI累積ログ'!$C$2:$C$2000,設定対象年,'15_KPI累積ログ'!$D$2:$D$2000,7),"")</f>
+        <v/>
+      </c>
+      <c r="H7" s="17">
+        <f>IFERROR(AVERAGEIFS('15_KPI累積ログ'!$J$2:$J$2000,'15_KPI累積ログ'!$G$2:$G$2000,$B7,'15_KPI累積ログ'!$C$2:$C$2000,設定対象年,'15_KPI累積ログ'!$D$2:$D$2000,8),"")</f>
+        <v/>
+      </c>
+      <c r="I7" s="17">
+        <f>IFERROR(AVERAGEIFS('15_KPI累積ログ'!$J$2:$J$2000,'15_KPI累積ログ'!$G$2:$G$2000,$B7,'15_KPI累積ログ'!$C$2:$C$2000,設定対象年,'15_KPI累積ログ'!$D$2:$D$2000,9),"")</f>
+        <v/>
+      </c>
+      <c r="J7" s="17">
+        <f>IFERROR(AVERAGEIFS('15_KPI累積ログ'!$J$2:$J$2000,'15_KPI累積ログ'!$G$2:$G$2000,$B7,'15_KPI累積ログ'!$C$2:$C$2000,設定対象年,'15_KPI累積ログ'!$D$2:$D$2000,10),"")</f>
+        <v/>
+      </c>
+      <c r="K7" s="17">
+        <f>IFERROR(AVERAGEIFS('15_KPI累積ログ'!$J$2:$J$2000,'15_KPI累積ログ'!$G$2:$G$2000,$B7,'15_KPI累積ログ'!$C$2:$C$2000,設定対象年,'15_KPI累積ログ'!$D$2:$D$2000,11),"")</f>
+        <v/>
+      </c>
+      <c r="L7" s="17">
+        <f>IFERROR(AVERAGEIFS('15_KPI累積ログ'!$J$2:$J$2000,'15_KPI累積ログ'!$G$2:$G$2000,$B7,'15_KPI累積ログ'!$C$2:$C$2000,設定対象年,'15_KPI累積ログ'!$D$2:$D$2000,12),"")</f>
+        <v/>
+      </c>
+      <c r="M7" s="17">
+        <f>IFERROR(AVERAGEIFS('15_KPI累積ログ'!$J$2:$J$2000,'15_KPI累積ログ'!$G$2:$G$2000,$B7,'15_KPI累積ログ'!$C$2:$C$2000,設定対象年+1,'15_KPI累積ログ'!$D$2:$D$2000,1),"")</f>
+        <v/>
+      </c>
+      <c r="N7" s="17">
+        <f>IFERROR(AVERAGEIFS('15_KPI累積ログ'!$J$2:$J$2000,'15_KPI累積ログ'!$G$2:$G$2000,$B7,'15_KPI累積ログ'!$C$2:$C$2000,設定対象年+1,'15_KPI累積ログ'!$D$2:$D$2000,2),"")</f>
+        <v/>
+      </c>
+      <c r="O7" s="17">
+        <f>IFERROR(AVERAGEIFS('15_KPI累積ログ'!$J$2:$J$2000,'15_KPI累積ログ'!$G$2:$G$2000,$B7,'15_KPI累積ログ'!$C$2:$C$2000,設定対象年+1,'15_KPI累積ログ'!$D$2:$D$2000,3),"")</f>
+        <v/>
+      </c>
+      <c r="P7" s="17">
+        <f>IFERROR(AVERAGE($D7:$O7),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>営業接点件数</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>件</t>
+        </is>
+      </c>
+      <c r="D8" s="4">
+        <f>IFERROR(SUMIFS('15_KPI累積ログ'!$J$2:$J$2000,'15_KPI累積ログ'!$G$2:$G$2000,$B8,'15_KPI累積ログ'!$C$2:$C$2000,設定対象年,'15_KPI累積ログ'!$D$2:$D$2000,4),"")</f>
+        <v/>
+      </c>
+      <c r="E8" s="4">
+        <f>IFERROR(SUMIFS('15_KPI累積ログ'!$J$2:$J$2000,'15_KPI累積ログ'!$G$2:$G$2000,$B8,'15_KPI累積ログ'!$C$2:$C$2000,設定対象年,'15_KPI累積ログ'!$D$2:$D$2000,5),"")</f>
+        <v/>
+      </c>
+      <c r="F8" s="4">
+        <f>IFERROR(SUMIFS('15_KPI累積ログ'!$J$2:$J$2000,'15_KPI累積ログ'!$G$2:$G$2000,$B8,'15_KPI累積ログ'!$C$2:$C$2000,設定対象年,'15_KPI累積ログ'!$D$2:$D$2000,6),"")</f>
+        <v/>
+      </c>
+      <c r="G8" s="4">
+        <f>IFERROR(SUMIFS('15_KPI累積ログ'!$J$2:$J$2000,'15_KPI累積ログ'!$G$2:$G$2000,$B8,'15_KPI累積ログ'!$C$2:$C$2000,設定対象年,'15_KPI累積ログ'!$D$2:$D$2000,7),"")</f>
+        <v/>
+      </c>
+      <c r="H8" s="4">
+        <f>IFERROR(SUMIFS('15_KPI累積ログ'!$J$2:$J$2000,'15_KPI累積ログ'!$G$2:$G$2000,$B8,'15_KPI累積ログ'!$C$2:$C$2000,設定対象年,'15_KPI累積ログ'!$D$2:$D$2000,8),"")</f>
+        <v/>
+      </c>
+      <c r="I8" s="4">
+        <f>IFERROR(SUMIFS('15_KPI累積ログ'!$J$2:$J$2000,'15_KPI累積ログ'!$G$2:$G$2000,$B8,'15_KPI累積ログ'!$C$2:$C$2000,設定対象年,'15_KPI累積ログ'!$D$2:$D$2000,9),"")</f>
+        <v/>
+      </c>
+      <c r="J8" s="4">
+        <f>IFERROR(SUMIFS('15_KPI累積ログ'!$J$2:$J$2000,'15_KPI累積ログ'!$G$2:$G$2000,$B8,'15_KPI累積ログ'!$C$2:$C$2000,設定対象年,'15_KPI累積ログ'!$D$2:$D$2000,10),"")</f>
+        <v/>
+      </c>
+      <c r="K8" s="4">
+        <f>IFERROR(SUMIFS('15_KPI累積ログ'!$J$2:$J$2000,'15_KPI累積ログ'!$G$2:$G$2000,$B8,'15_KPI累積ログ'!$C$2:$C$2000,設定対象年,'15_KPI累積ログ'!$D$2:$D$2000,11),"")</f>
+        <v/>
+      </c>
+      <c r="L8" s="4">
+        <f>IFERROR(SUMIFS('15_KPI累積ログ'!$J$2:$J$2000,'15_KPI累積ログ'!$G$2:$G$2000,$B8,'15_KPI累積ログ'!$C$2:$C$2000,設定対象年,'15_KPI累積ログ'!$D$2:$D$2000,12),"")</f>
+        <v/>
+      </c>
+      <c r="M8" s="4">
+        <f>IFERROR(SUMIFS('15_KPI累積ログ'!$J$2:$J$2000,'15_KPI累積ログ'!$G$2:$G$2000,$B8,'15_KPI累積ログ'!$C$2:$C$2000,設定対象年+1,'15_KPI累積ログ'!$D$2:$D$2000,1),"")</f>
+        <v/>
+      </c>
+      <c r="N8" s="4">
+        <f>IFERROR(SUMIFS('15_KPI累積ログ'!$J$2:$J$2000,'15_KPI累積ログ'!$G$2:$G$2000,$B8,'15_KPI累積ログ'!$C$2:$C$2000,設定対象年+1,'15_KPI累積ログ'!$D$2:$D$2000,2),"")</f>
+        <v/>
+      </c>
+      <c r="O8" s="4">
+        <f>IFERROR(SUMIFS('15_KPI累積ログ'!$J$2:$J$2000,'15_KPI累積ログ'!$G$2:$G$2000,$B8,'15_KPI累積ログ'!$C$2:$C$2000,設定対象年+1,'15_KPI累積ログ'!$D$2:$D$2000,3),"")</f>
+        <v/>
+      </c>
+      <c r="P8" s="4">
+        <f>IFERROR(SUM($D8:$O8),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>見学・体験件数</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>件</t>
+        </is>
+      </c>
+      <c r="D9" s="4">
+        <f>IFERROR(SUMIFS('15_KPI累積ログ'!$J$2:$J$2000,'15_KPI累積ログ'!$G$2:$G$2000,$B9,'15_KPI累積ログ'!$C$2:$C$2000,設定対象年,'15_KPI累積ログ'!$D$2:$D$2000,4),"")</f>
+        <v/>
+      </c>
+      <c r="E9" s="4">
+        <f>IFERROR(SUMIFS('15_KPI累積ログ'!$J$2:$J$2000,'15_KPI累積ログ'!$G$2:$G$2000,$B9,'15_KPI累積ログ'!$C$2:$C$2000,設定対象年,'15_KPI累積ログ'!$D$2:$D$2000,5),"")</f>
+        <v/>
+      </c>
+      <c r="F9" s="4">
+        <f>IFERROR(SUMIFS('15_KPI累積ログ'!$J$2:$J$2000,'15_KPI累積ログ'!$G$2:$G$2000,$B9,'15_KPI累積ログ'!$C$2:$C$2000,設定対象年,'15_KPI累積ログ'!$D$2:$D$2000,6),"")</f>
+        <v/>
+      </c>
+      <c r="G9" s="4">
+        <f>IFERROR(SUMIFS('15_KPI累積ログ'!$J$2:$J$2000,'15_KPI累積ログ'!$G$2:$G$2000,$B9,'15_KPI累積ログ'!$C$2:$C$2000,設定対象年,'15_KPI累積ログ'!$D$2:$D$2000,7),"")</f>
+        <v/>
+      </c>
+      <c r="H9" s="4">
+        <f>IFERROR(SUMIFS('15_KPI累積ログ'!$J$2:$J$2000,'15_KPI累積ログ'!$G$2:$G$2000,$B9,'15_KPI累積ログ'!$C$2:$C$2000,設定対象年,'15_KPI累積ログ'!$D$2:$D$2000,8),"")</f>
+        <v/>
+      </c>
+      <c r="I9" s="4">
+        <f>IFERROR(SUMIFS('15_KPI累積ログ'!$J$2:$J$2000,'15_KPI累積ログ'!$G$2:$G$2000,$B9,'15_KPI累積ログ'!$C$2:$C$2000,設定対象年,'15_KPI累積ログ'!$D$2:$D$2000,9),"")</f>
+        <v/>
+      </c>
+      <c r="J9" s="4">
+        <f>IFERROR(SUMIFS('15_KPI累積ログ'!$J$2:$J$2000,'15_KPI累積ログ'!$G$2:$G$2000,$B9,'15_KPI累積ログ'!$C$2:$C$2000,設定対象年,'15_KPI累積ログ'!$D$2:$D$2000,10),"")</f>
+        <v/>
+      </c>
+      <c r="K9" s="4">
+        <f>IFERROR(SUMIFS('15_KPI累積ログ'!$J$2:$J$2000,'15_KPI累積ログ'!$G$2:$G$2000,$B9,'15_KPI累積ログ'!$C$2:$C$2000,設定対象年,'15_KPI累積ログ'!$D$2:$D$2000,11),"")</f>
+        <v/>
+      </c>
+      <c r="L9" s="4">
+        <f>IFERROR(SUMIFS('15_KPI累積ログ'!$J$2:$J$2000,'15_KPI累積ログ'!$G$2:$G$2000,$B9,'15_KPI累積ログ'!$C$2:$C$2000,設定対象年,'15_KPI累積ログ'!$D$2:$D$2000,12),"")</f>
+        <v/>
+      </c>
+      <c r="M9" s="4">
+        <f>IFERROR(SUMIFS('15_KPI累積ログ'!$J$2:$J$2000,'15_KPI累積ログ'!$G$2:$G$2000,$B9,'15_KPI累積ログ'!$C$2:$C$2000,設定対象年+1,'15_KPI累積ログ'!$D$2:$D$2000,1),"")</f>
+        <v/>
+      </c>
+      <c r="N9" s="4">
+        <f>IFERROR(SUMIFS('15_KPI累積ログ'!$J$2:$J$2000,'15_KPI累積ログ'!$G$2:$G$2000,$B9,'15_KPI累積ログ'!$C$2:$C$2000,設定対象年+1,'15_KPI累積ログ'!$D$2:$D$2000,2),"")</f>
+        <v/>
+      </c>
+      <c r="O9" s="4">
+        <f>IFERROR(SUMIFS('15_KPI累積ログ'!$J$2:$J$2000,'15_KPI累積ログ'!$G$2:$G$2000,$B9,'15_KPI累積ログ'!$C$2:$C$2000,設定対象年+1,'15_KPI累積ログ'!$D$2:$D$2000,3),"")</f>
+        <v/>
+      </c>
+      <c r="P9" s="4">
+        <f>IFERROR(SUM($D9:$O9),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>入居契約件数</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>件</t>
+        </is>
+      </c>
+      <c r="D10" s="4">
+        <f>IFERROR(SUMIFS('15_KPI累積ログ'!$J$2:$J$2000,'15_KPI累積ログ'!$G$2:$G$2000,$B10,'15_KPI累積ログ'!$C$2:$C$2000,設定対象年,'15_KPI累積ログ'!$D$2:$D$2000,4),"")</f>
+        <v/>
+      </c>
+      <c r="E10" s="4">
+        <f>IFERROR(SUMIFS('15_KPI累積ログ'!$J$2:$J$2000,'15_KPI累積ログ'!$G$2:$G$2000,$B10,'15_KPI累積ログ'!$C$2:$C$2000,設定対象年,'15_KPI累積ログ'!$D$2:$D$2000,5),"")</f>
+        <v/>
+      </c>
+      <c r="F10" s="4">
+        <f>IFERROR(SUMIFS('15_KPI累積ログ'!$J$2:$J$2000,'15_KPI累積ログ'!$G$2:$G$2000,$B10,'15_KPI累積ログ'!$C$2:$C$2000,設定対象年,'15_KPI累積ログ'!$D$2:$D$2000,6),"")</f>
+        <v/>
+      </c>
+      <c r="G10" s="4">
+        <f>IFERROR(SUMIFS('15_KPI累積ログ'!$J$2:$J$2000,'15_KPI累積ログ'!$G$2:$G$2000,$B10,'15_KPI累積ログ'!$C$2:$C$2000,設定対象年,'15_KPI累積ログ'!$D$2:$D$2000,7),"")</f>
+        <v/>
+      </c>
+      <c r="H10" s="4">
+        <f>IFERROR(SUMIFS('15_KPI累積ログ'!$J$2:$J$2000,'15_KPI累積ログ'!$G$2:$G$2000,$B10,'15_KPI累積ログ'!$C$2:$C$2000,設定対象年,'15_KPI累積ログ'!$D$2:$D$2000,8),"")</f>
+        <v/>
+      </c>
+      <c r="I10" s="4">
+        <f>IFERROR(SUMIFS('15_KPI累積ログ'!$J$2:$J$2000,'15_KPI累積ログ'!$G$2:$G$2000,$B10,'15_KPI累積ログ'!$C$2:$C$2000,設定対象年,'15_KPI累積ログ'!$D$2:$D$2000,9),"")</f>
+        <v/>
+      </c>
+      <c r="J10" s="4">
+        <f>IFERROR(SUMIFS('15_KPI累積ログ'!$J$2:$J$2000,'15_KPI累積ログ'!$G$2:$G$2000,$B10,'15_KPI累積ログ'!$C$2:$C$2000,設定対象年,'15_KPI累積ログ'!$D$2:$D$2000,10),"")</f>
+        <v/>
+      </c>
+      <c r="K10" s="4">
+        <f>IFERROR(SUMIFS('15_KPI累積ログ'!$J$2:$J$2000,'15_KPI累積ログ'!$G$2:$G$2000,$B10,'15_KPI累積ログ'!$C$2:$C$2000,設定対象年,'15_KPI累積ログ'!$D$2:$D$2000,11),"")</f>
+        <v/>
+      </c>
+      <c r="L10" s="4">
+        <f>IFERROR(SUMIFS('15_KPI累積ログ'!$J$2:$J$2000,'15_KPI累積ログ'!$G$2:$G$2000,$B10,'15_KPI累積ログ'!$C$2:$C$2000,設定対象年,'15_KPI累積ログ'!$D$2:$D$2000,12),"")</f>
+        <v/>
+      </c>
+      <c r="M10" s="4">
+        <f>IFERROR(SUMIFS('15_KPI累積ログ'!$J$2:$J$2000,'15_KPI累積ログ'!$G$2:$G$2000,$B10,'15_KPI累積ログ'!$C$2:$C$2000,設定対象年+1,'15_KPI累積ログ'!$D$2:$D$2000,1),"")</f>
+        <v/>
+      </c>
+      <c r="N10" s="4">
+        <f>IFERROR(SUMIFS('15_KPI累積ログ'!$J$2:$J$2000,'15_KPI累積ログ'!$G$2:$G$2000,$B10,'15_KPI累積ログ'!$C$2:$C$2000,設定対象年+1,'15_KPI累積ログ'!$D$2:$D$2000,2),"")</f>
+        <v/>
+      </c>
+      <c r="O10" s="4">
+        <f>IFERROR(SUMIFS('15_KPI累積ログ'!$J$2:$J$2000,'15_KPI累積ログ'!$G$2:$G$2000,$B10,'15_KPI累積ログ'!$C$2:$C$2000,設定対象年+1,'15_KPI累積ログ'!$D$2:$D$2000,3),"")</f>
+        <v/>
+      </c>
+      <c r="P10" s="4">
+        <f>IFERROR(SUM($D10:$O10),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>SS稼働率</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D11" s="17">
+        <f>IFERROR(AVERAGEIFS('15_KPI累積ログ'!$J$2:$J$2000,'15_KPI累積ログ'!$G$2:$G$2000,$B11,'15_KPI累積ログ'!$C$2:$C$2000,設定対象年,'15_KPI累積ログ'!$D$2:$D$2000,4),"")</f>
+        <v/>
+      </c>
+      <c r="E11" s="17">
+        <f>IFERROR(AVERAGEIFS('15_KPI累積ログ'!$J$2:$J$2000,'15_KPI累積ログ'!$G$2:$G$2000,$B11,'15_KPI累積ログ'!$C$2:$C$2000,設定対象年,'15_KPI累積ログ'!$D$2:$D$2000,5),"")</f>
+        <v/>
+      </c>
+      <c r="F11" s="17">
+        <f>IFERROR(AVERAGEIFS('15_KPI累積ログ'!$J$2:$J$2000,'15_KPI累積ログ'!$G$2:$G$2000,$B11,'15_KPI累積ログ'!$C$2:$C$2000,設定対象年,'15_KPI累積ログ'!$D$2:$D$2000,6),"")</f>
+        <v/>
+      </c>
+      <c r="G11" s="17">
+        <f>IFERROR(AVERAGEIFS('15_KPI累積ログ'!$J$2:$J$2000,'15_KPI累積ログ'!$G$2:$G$2000,$B11,'15_KPI累積ログ'!$C$2:$C$2000,設定対象年,'15_KPI累積ログ'!$D$2:$D$2000,7),"")</f>
+        <v/>
+      </c>
+      <c r="H11" s="17">
+        <f>IFERROR(AVERAGEIFS('15_KPI累積ログ'!$J$2:$J$2000,'15_KPI累積ログ'!$G$2:$G$2000,$B11,'15_KPI累積ログ'!$C$2:$C$2000,設定対象年,'15_KPI累積ログ'!$D$2:$D$2000,8),"")</f>
+        <v/>
+      </c>
+      <c r="I11" s="17">
+        <f>IFERROR(AVERAGEIFS('15_KPI累積ログ'!$J$2:$J$2000,'15_KPI累積ログ'!$G$2:$G$2000,$B11,'15_KPI累積ログ'!$C$2:$C$2000,設定対象年,'15_KPI累積ログ'!$D$2:$D$2000,9),"")</f>
+        <v/>
+      </c>
+      <c r="J11" s="17">
+        <f>IFERROR(AVERAGEIFS('15_KPI累積ログ'!$J$2:$J$2000,'15_KPI累積ログ'!$G$2:$G$2000,$B11,'15_KPI累積ログ'!$C$2:$C$2000,設定対象年,'15_KPI累積ログ'!$D$2:$D$2000,10),"")</f>
+        <v/>
+      </c>
+      <c r="K11" s="17">
+        <f>IFERROR(AVERAGEIFS('15_KPI累積ログ'!$J$2:$J$2000,'15_KPI累積ログ'!$G$2:$G$2000,$B11,'15_KPI累積ログ'!$C$2:$C$2000,設定対象年,'15_KPI累積ログ'!$D$2:$D$2000,11),"")</f>
+        <v/>
+      </c>
+      <c r="L11" s="17">
+        <f>IFERROR(AVERAGEIFS('15_KPI累積ログ'!$J$2:$J$2000,'15_KPI累積ログ'!$G$2:$G$2000,$B11,'15_KPI累積ログ'!$C$2:$C$2000,設定対象年,'15_KPI累積ログ'!$D$2:$D$2000,12),"")</f>
+        <v/>
+      </c>
+      <c r="M11" s="17">
+        <f>IFERROR(AVERAGEIFS('15_KPI累積ログ'!$J$2:$J$2000,'15_KPI累積ログ'!$G$2:$G$2000,$B11,'15_KPI累積ログ'!$C$2:$C$2000,設定対象年+1,'15_KPI累積ログ'!$D$2:$D$2000,1),"")</f>
+        <v/>
+      </c>
+      <c r="N11" s="17">
+        <f>IFERROR(AVERAGEIFS('15_KPI累積ログ'!$J$2:$J$2000,'15_KPI累積ログ'!$G$2:$G$2000,$B11,'15_KPI累積ログ'!$C$2:$C$2000,設定対象年+1,'15_KPI累積ログ'!$D$2:$D$2000,2),"")</f>
+        <v/>
+      </c>
+      <c r="O11" s="17">
+        <f>IFERROR(AVERAGEIFS('15_KPI累積ログ'!$J$2:$J$2000,'15_KPI累積ログ'!$G$2:$G$2000,$B11,'15_KPI累積ログ'!$C$2:$C$2000,設定対象年+1,'15_KPI累積ログ'!$D$2:$D$2000,3),"")</f>
+        <v/>
+      </c>
+      <c r="P11" s="17">
+        <f>IFERROR(AVERAGE($D11:$O11),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>SS案件発掘件数</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>件</t>
+        </is>
+      </c>
+      <c r="D12" s="4">
+        <f>IFERROR(SUMIFS('15_KPI累積ログ'!$J$2:$J$2000,'15_KPI累積ログ'!$G$2:$G$2000,$B12,'15_KPI累積ログ'!$C$2:$C$2000,設定対象年,'15_KPI累積ログ'!$D$2:$D$2000,4),"")</f>
+        <v/>
+      </c>
+      <c r="E12" s="4">
+        <f>IFERROR(SUMIFS('15_KPI累積ログ'!$J$2:$J$2000,'15_KPI累積ログ'!$G$2:$G$2000,$B12,'15_KPI累積ログ'!$C$2:$C$2000,設定対象年,'15_KPI累積ログ'!$D$2:$D$2000,5),"")</f>
+        <v/>
+      </c>
+      <c r="F12" s="4">
+        <f>IFERROR(SUMIFS('15_KPI累積ログ'!$J$2:$J$2000,'15_KPI累積ログ'!$G$2:$G$2000,$B12,'15_KPI累積ログ'!$C$2:$C$2000,設定対象年,'15_KPI累積ログ'!$D$2:$D$2000,6),"")</f>
+        <v/>
+      </c>
+      <c r="G12" s="4">
+        <f>IFERROR(SUMIFS('15_KPI累積ログ'!$J$2:$J$2000,'15_KPI累積ログ'!$G$2:$G$2000,$B12,'15_KPI累積ログ'!$C$2:$C$2000,設定対象年,'15_KPI累積ログ'!$D$2:$D$2000,7),"")</f>
+        <v/>
+      </c>
+      <c r="H12" s="4">
+        <f>IFERROR(SUMIFS('15_KPI累積ログ'!$J$2:$J$2000,'15_KPI累積ログ'!$G$2:$G$2000,$B12,'15_KPI累積ログ'!$C$2:$C$2000,設定対象年,'15_KPI累積ログ'!$D$2:$D$2000,8),"")</f>
+        <v/>
+      </c>
+      <c r="I12" s="4">
+        <f>IFERROR(SUMIFS('15_KPI累積ログ'!$J$2:$J$2000,'15_KPI累積ログ'!$G$2:$G$2000,$B12,'15_KPI累積ログ'!$C$2:$C$2000,設定対象年,'15_KPI累積ログ'!$D$2:$D$2000,9),"")</f>
+        <v/>
+      </c>
+      <c r="J12" s="4">
+        <f>IFERROR(SUMIFS('15_KPI累積ログ'!$J$2:$J$2000,'15_KPI累積ログ'!$G$2:$G$2000,$B12,'15_KPI累積ログ'!$C$2:$C$2000,設定対象年,'15_KPI累積ログ'!$D$2:$D$2000,10),"")</f>
+        <v/>
+      </c>
+      <c r="K12" s="4">
+        <f>IFERROR(SUMIFS('15_KPI累積ログ'!$J$2:$J$2000,'15_KPI累積ログ'!$G$2:$G$2000,$B12,'15_KPI累積ログ'!$C$2:$C$2000,設定対象年,'15_KPI累積ログ'!$D$2:$D$2000,11),"")</f>
+        <v/>
+      </c>
+      <c r="L12" s="4">
+        <f>IFERROR(SUMIFS('15_KPI累積ログ'!$J$2:$J$2000,'15_KPI累積ログ'!$G$2:$G$2000,$B12,'15_KPI累積ログ'!$C$2:$C$2000,設定対象年,'15_KPI累積ログ'!$D$2:$D$2000,12),"")</f>
+        <v/>
+      </c>
+      <c r="M12" s="4">
+        <f>IFERROR(SUMIFS('15_KPI累積ログ'!$J$2:$J$2000,'15_KPI累積ログ'!$G$2:$G$2000,$B12,'15_KPI累積ログ'!$C$2:$C$2000,設定対象年+1,'15_KPI累積ログ'!$D$2:$D$2000,1),"")</f>
+        <v/>
+      </c>
+      <c r="N12" s="4">
+        <f>IFERROR(SUMIFS('15_KPI累積ログ'!$J$2:$J$2000,'15_KPI累積ログ'!$G$2:$G$2000,$B12,'15_KPI累積ログ'!$C$2:$C$2000,設定対象年+1,'15_KPI累積ログ'!$D$2:$D$2000,2),"")</f>
+        <v/>
+      </c>
+      <c r="O12" s="4">
+        <f>IFERROR(SUMIFS('15_KPI累積ログ'!$J$2:$J$2000,'15_KPI累積ログ'!$G$2:$G$2000,$B12,'15_KPI累積ログ'!$C$2:$C$2000,設定対象年+1,'15_KPI累積ログ'!$D$2:$D$2000,3),"")</f>
+        <v/>
+      </c>
+      <c r="P12" s="4">
+        <f>IFERROR(SUM($D12:$O12),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>夜勤加配 取得率</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D13" s="17">
+        <f>IFERROR(AVERAGEIFS('15_KPI累積ログ'!$J$2:$J$2000,'15_KPI累積ログ'!$G$2:$G$2000,$B13,'15_KPI累積ログ'!$C$2:$C$2000,設定対象年,'15_KPI累積ログ'!$D$2:$D$2000,4),"")</f>
+        <v/>
+      </c>
+      <c r="E13" s="17">
+        <f>IFERROR(AVERAGEIFS('15_KPI累積ログ'!$J$2:$J$2000,'15_KPI累積ログ'!$G$2:$G$2000,$B13,'15_KPI累積ログ'!$C$2:$C$2000,設定対象年,'15_KPI累積ログ'!$D$2:$D$2000,5),"")</f>
+        <v/>
+      </c>
+      <c r="F13" s="17">
+        <f>IFERROR(AVERAGEIFS('15_KPI累積ログ'!$J$2:$J$2000,'15_KPI累積ログ'!$G$2:$G$2000,$B13,'15_KPI累積ログ'!$C$2:$C$2000,設定対象年,'15_KPI累積ログ'!$D$2:$D$2000,6),"")</f>
+        <v/>
+      </c>
+      <c r="G13" s="17">
+        <f>IFERROR(AVERAGEIFS('15_KPI累積ログ'!$J$2:$J$2000,'15_KPI累積ログ'!$G$2:$G$2000,$B13,'15_KPI累積ログ'!$C$2:$C$2000,設定対象年,'15_KPI累積ログ'!$D$2:$D$2000,7),"")</f>
+        <v/>
+      </c>
+      <c r="H13" s="17">
+        <f>IFERROR(AVERAGEIFS('15_KPI累積ログ'!$J$2:$J$2000,'15_KPI累積ログ'!$G$2:$G$2000,$B13,'15_KPI累積ログ'!$C$2:$C$2000,設定対象年,'15_KPI累積ログ'!$D$2:$D$2000,8),"")</f>
+        <v/>
+      </c>
+      <c r="I13" s="17">
+        <f>IFERROR(AVERAGEIFS('15_KPI累積ログ'!$J$2:$J$2000,'15_KPI累積ログ'!$G$2:$G$2000,$B13,'15_KPI累積ログ'!$C$2:$C$2000,設定対象年,'15_KPI累積ログ'!$D$2:$D$2000,9),"")</f>
+        <v/>
+      </c>
+      <c r="J13" s="17">
+        <f>IFERROR(AVERAGEIFS('15_KPI累積ログ'!$J$2:$J$2000,'15_KPI累積ログ'!$G$2:$G$2000,$B13,'15_KPI累積ログ'!$C$2:$C$2000,設定対象年,'15_KPI累積ログ'!$D$2:$D$2000,10),"")</f>
+        <v/>
+      </c>
+      <c r="K13" s="17">
+        <f>IFERROR(AVERAGEIFS('15_KPI累積ログ'!$J$2:$J$2000,'15_KPI累積ログ'!$G$2:$G$2000,$B13,'15_KPI累積ログ'!$C$2:$C$2000,設定対象年,'15_KPI累積ログ'!$D$2:$D$2000,11),"")</f>
+        <v/>
+      </c>
+      <c r="L13" s="17">
+        <f>IFERROR(AVERAGEIFS('15_KPI累積ログ'!$J$2:$J$2000,'15_KPI累積ログ'!$G$2:$G$2000,$B13,'15_KPI累積ログ'!$C$2:$C$2000,設定対象年,'15_KPI累積ログ'!$D$2:$D$2000,12),"")</f>
+        <v/>
+      </c>
+      <c r="M13" s="17">
+        <f>IFERROR(AVERAGEIFS('15_KPI累積ログ'!$J$2:$J$2000,'15_KPI累積ログ'!$G$2:$G$2000,$B13,'15_KPI累積ログ'!$C$2:$C$2000,設定対象年+1,'15_KPI累積ログ'!$D$2:$D$2000,1),"")</f>
+        <v/>
+      </c>
+      <c r="N13" s="17">
+        <f>IFERROR(AVERAGEIFS('15_KPI累積ログ'!$J$2:$J$2000,'15_KPI累積ログ'!$G$2:$G$2000,$B13,'15_KPI累積ログ'!$C$2:$C$2000,設定対象年+1,'15_KPI累積ログ'!$D$2:$D$2000,2),"")</f>
+        <v/>
+      </c>
+      <c r="O13" s="17">
+        <f>IFERROR(AVERAGEIFS('15_KPI累積ログ'!$J$2:$J$2000,'15_KPI累積ログ'!$G$2:$G$2000,$B13,'15_KPI累積ログ'!$C$2:$C$2000,設定対象年+1,'15_KPI累積ログ'!$D$2:$D$2000,3),"")</f>
+        <v/>
+      </c>
+      <c r="P13" s="17">
+        <f>IFERROR(AVERAGE($D13:$O13),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>訪看契約件数</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>件</t>
+        </is>
+      </c>
+      <c r="D14" s="4">
+        <f>IFERROR(SUMIFS('15_KPI累積ログ'!$J$2:$J$2000,'15_KPI累積ログ'!$G$2:$G$2000,$B14,'15_KPI累積ログ'!$C$2:$C$2000,設定対象年,'15_KPI累積ログ'!$D$2:$D$2000,4),"")</f>
+        <v/>
+      </c>
+      <c r="E14" s="4">
+        <f>IFERROR(SUMIFS('15_KPI累積ログ'!$J$2:$J$2000,'15_KPI累積ログ'!$G$2:$G$2000,$B14,'15_KPI累積ログ'!$C$2:$C$2000,設定対象年,'15_KPI累積ログ'!$D$2:$D$2000,5),"")</f>
+        <v/>
+      </c>
+      <c r="F14" s="4">
+        <f>IFERROR(SUMIFS('15_KPI累積ログ'!$J$2:$J$2000,'15_KPI累積ログ'!$G$2:$G$2000,$B14,'15_KPI累積ログ'!$C$2:$C$2000,設定対象年,'15_KPI累積ログ'!$D$2:$D$2000,6),"")</f>
+        <v/>
+      </c>
+      <c r="G14" s="4">
+        <f>IFERROR(SUMIFS('15_KPI累積ログ'!$J$2:$J$2000,'15_KPI累積ログ'!$G$2:$G$2000,$B14,'15_KPI累積ログ'!$C$2:$C$2000,設定対象年,'15_KPI累積ログ'!$D$2:$D$2000,7),"")</f>
+        <v/>
+      </c>
+      <c r="H14" s="4">
+        <f>IFERROR(SUMIFS('15_KPI累積ログ'!$J$2:$J$2000,'15_KPI累積ログ'!$G$2:$G$2000,$B14,'15_KPI累積ログ'!$C$2:$C$2000,設定対象年,'15_KPI累積ログ'!$D$2:$D$2000,8),"")</f>
+        <v/>
+      </c>
+      <c r="I14" s="4">
+        <f>IFERROR(SUMIFS('15_KPI累積ログ'!$J$2:$J$2000,'15_KPI累積ログ'!$G$2:$G$2000,$B14,'15_KPI累積ログ'!$C$2:$C$2000,設定対象年,'15_KPI累積ログ'!$D$2:$D$2000,9),"")</f>
+        <v/>
+      </c>
+      <c r="J14" s="4">
+        <f>IFERROR(SUMIFS('15_KPI累積ログ'!$J$2:$J$2000,'15_KPI累積ログ'!$G$2:$G$2000,$B14,'15_KPI累積ログ'!$C$2:$C$2000,設定対象年,'15_KPI累積ログ'!$D$2:$D$2000,10),"")</f>
+        <v/>
+      </c>
+      <c r="K14" s="4">
+        <f>IFERROR(SUMIFS('15_KPI累積ログ'!$J$2:$J$2000,'15_KPI累積ログ'!$G$2:$G$2000,$B14,'15_KPI累積ログ'!$C$2:$C$2000,設定対象年,'15_KPI累積ログ'!$D$2:$D$2000,11),"")</f>
+        <v/>
+      </c>
+      <c r="L14" s="4">
+        <f>IFERROR(SUMIFS('15_KPI累積ログ'!$J$2:$J$2000,'15_KPI累積ログ'!$G$2:$G$2000,$B14,'15_KPI累積ログ'!$C$2:$C$2000,設定対象年,'15_KPI累積ログ'!$D$2:$D$2000,12),"")</f>
+        <v/>
+      </c>
+      <c r="M14" s="4">
+        <f>IFERROR(SUMIFS('15_KPI累積ログ'!$J$2:$J$2000,'15_KPI累積ログ'!$G$2:$G$2000,$B14,'15_KPI累積ログ'!$C$2:$C$2000,設定対象年+1,'15_KPI累積ログ'!$D$2:$D$2000,1),"")</f>
+        <v/>
+      </c>
+      <c r="N14" s="4">
+        <f>IFERROR(SUMIFS('15_KPI累積ログ'!$J$2:$J$2000,'15_KPI累積ログ'!$G$2:$G$2000,$B14,'15_KPI累積ログ'!$C$2:$C$2000,設定対象年+1,'15_KPI累積ログ'!$D$2:$D$2000,2),"")</f>
+        <v/>
+      </c>
+      <c r="O14" s="4">
+        <f>IFERROR(SUMIFS('15_KPI累積ログ'!$J$2:$J$2000,'15_KPI累積ログ'!$G$2:$G$2000,$B14,'15_KPI累積ログ'!$C$2:$C$2000,設定対象年+1,'15_KPI累積ログ'!$D$2:$D$2000,3),"")</f>
+        <v/>
+      </c>
+      <c r="P14" s="4">
+        <f>IFERROR(SUM($D14:$O14),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>SQ契約件数</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>件</t>
+        </is>
+      </c>
+      <c r="D15" s="4">
+        <f>IFERROR(SUMIFS('15_KPI累積ログ'!$J$2:$J$2000,'15_KPI累積ログ'!$G$2:$G$2000,$B15,'15_KPI累積ログ'!$C$2:$C$2000,設定対象年,'15_KPI累積ログ'!$D$2:$D$2000,4),"")</f>
+        <v/>
+      </c>
+      <c r="E15" s="4">
+        <f>IFERROR(SUMIFS('15_KPI累積ログ'!$J$2:$J$2000,'15_KPI累積ログ'!$G$2:$G$2000,$B15,'15_KPI累積ログ'!$C$2:$C$2000,設定対象年,'15_KPI累積ログ'!$D$2:$D$2000,5),"")</f>
+        <v/>
+      </c>
+      <c r="F15" s="4">
+        <f>IFERROR(SUMIFS('15_KPI累積ログ'!$J$2:$J$2000,'15_KPI累積ログ'!$G$2:$G$2000,$B15,'15_KPI累積ログ'!$C$2:$C$2000,設定対象年,'15_KPI累積ログ'!$D$2:$D$2000,6),"")</f>
+        <v/>
+      </c>
+      <c r="G15" s="4">
+        <f>IFERROR(SUMIFS('15_KPI累積ログ'!$J$2:$J$2000,'15_KPI累積ログ'!$G$2:$G$2000,$B15,'15_KPI累積ログ'!$C$2:$C$2000,設定対象年,'15_KPI累積ログ'!$D$2:$D$2000,7),"")</f>
+        <v/>
+      </c>
+      <c r="H15" s="4">
+        <f>IFERROR(SUMIFS('15_KPI累積ログ'!$J$2:$J$2000,'15_KPI累積ログ'!$G$2:$G$2000,$B15,'15_KPI累積ログ'!$C$2:$C$2000,設定対象年,'15_KPI累積ログ'!$D$2:$D$2000,8),"")</f>
+        <v/>
+      </c>
+      <c r="I15" s="4">
+        <f>IFERROR(SUMIFS('15_KPI累積ログ'!$J$2:$J$2000,'15_KPI累積ログ'!$G$2:$G$2000,$B15,'15_KPI累積ログ'!$C$2:$C$2000,設定対象年,'15_KPI累積ログ'!$D$2:$D$2000,9),"")</f>
+        <v/>
+      </c>
+      <c r="J15" s="4">
+        <f>IFERROR(SUMIFS('15_KPI累積ログ'!$J$2:$J$2000,'15_KPI累積ログ'!$G$2:$G$2000,$B15,'15_KPI累積ログ'!$C$2:$C$2000,設定対象年,'15_KPI累積ログ'!$D$2:$D$2000,10),"")</f>
+        <v/>
+      </c>
+      <c r="K15" s="4">
+        <f>IFERROR(SUMIFS('15_KPI累積ログ'!$J$2:$J$2000,'15_KPI累積ログ'!$G$2:$G$2000,$B15,'15_KPI累積ログ'!$C$2:$C$2000,設定対象年,'15_KPI累積ログ'!$D$2:$D$2000,11),"")</f>
+        <v/>
+      </c>
+      <c r="L15" s="4">
+        <f>IFERROR(SUMIFS('15_KPI累積ログ'!$J$2:$J$2000,'15_KPI累積ログ'!$G$2:$G$2000,$B15,'15_KPI累積ログ'!$C$2:$C$2000,設定対象年,'15_KPI累積ログ'!$D$2:$D$2000,12),"")</f>
+        <v/>
+      </c>
+      <c r="M15" s="4">
+        <f>IFERROR(SUMIFS('15_KPI累積ログ'!$J$2:$J$2000,'15_KPI累積ログ'!$G$2:$G$2000,$B15,'15_KPI累積ログ'!$C$2:$C$2000,設定対象年+1,'15_KPI累積ログ'!$D$2:$D$2000,1),"")</f>
+        <v/>
+      </c>
+      <c r="N15" s="4">
+        <f>IFERROR(SUMIFS('15_KPI累積ログ'!$J$2:$J$2000,'15_KPI累積ログ'!$G$2:$G$2000,$B15,'15_KPI累積ログ'!$C$2:$C$2000,設定対象年+1,'15_KPI累積ログ'!$D$2:$D$2000,2),"")</f>
+        <v/>
+      </c>
+      <c r="O15" s="4">
+        <f>IFERROR(SUMIFS('15_KPI累積ログ'!$J$2:$J$2000,'15_KPI累積ログ'!$G$2:$G$2000,$B15,'15_KPI累積ログ'!$C$2:$C$2000,設定対象年+1,'15_KPI累積ログ'!$D$2:$D$2000,3),"")</f>
+        <v/>
+      </c>
+      <c r="P15" s="4">
+        <f>IFERROR(SUM($D15:$O15),"")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -17650,7 +18525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -17950,27 +18825,27 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>運用</t>
+          <t>構造</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>対応方針・所感が1セルに改行で詰め込まれた長文（【営業行動】…▶2/25 追客 等）。</t>
+          <t>継続運用の方法が『月シートを1枚ずつ増やす』こと。実ファイルでは22枚まで増え、命名も不統一になっている。</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>目標値と実績が数式で取り出せず、達成／未達の自動判定ができない。読む人によって解釈が変わる。</t>
+          <t>シートが増えるほどブックが重くなり、集計式（12か月固定のHLOOKUP表）が追従できない。年度をまたぐと参照が壊れ、過去の修正が現在の集計に波及する。</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>『数値で置く欄』と『文章で残す欄』を分離する。</t>
+          <t>月ごとにシートを増やさず、月末に締めて『実績ブックの保管＋累積ログへの追記＋翌月ブックの生成』に分ける。</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>週次目標・実績・達成率・差異を数値列に分離し、所感は別列に残す。</t>
+          <t>15_KPI累積ログ（値で保管）＋16_年間推移＋tools/pdca/close_month.py（締め処理）。ブックの枚数は月に関係なく一定。</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
@@ -17990,22 +18865,22 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>ステータス列・期限列（G/H, P/Q…）は結合セルで、入力規則も条件付き書式もなく空欄のまま。</t>
+          <t>対応方針・所感が1セルに改行で詰め込まれた長文（【営業行動】…▶2/25 追客 等）。</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>期限超過が誰にも見えない。ステータスの表記ゆれ（完了／済／OK）で集計不能。</t>
+          <t>目標値と実績が数式で取り出せず、達成／未達の自動判定ができない。読む人によって解釈が変わる。</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>ステータスはプルダウン、期限は日付、遅延は自動判定＋色付け。</t>
+          <t>『数値で置く欄』と『文章で残す欄』を分離する。</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>04_課題管理表にステータスDV・残日数・遅延判定・行の自動着色を実装。</t>
+          <t>週次目標・実績・達成率・差異を数値列に分離し、所感は別列に残す。</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
@@ -18025,27 +18900,27 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>『※未対象施設』とだけ書かれた行（④訪看契約・⑤SQ利用）が毎週コピーされ続けている。</t>
+          <t>ステータス列・期限列（G/H, P/Q…）は結合セルで、入力規則も条件付き書式もなく空欄のまま。</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>対象外の項目が常時表示され、シートのノイズになる。対象化した時に誰が判断するか決まっていない。</t>
+          <t>期限超過が誰にも見えない。ステータスの表記ゆれ（完了／済／OK）で集計不能。</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>対象／対象外を施設マスタ側の属性で持ち、非対象は非表示にする。</t>
+          <t>ステータスはプルダウン、期限は日付、遅延は自動判定＋色付け。</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>01_施設マスタ I列『PDCA対象』で管理。カテゴリは04で必要な行だけ起票する運用。</t>
+          <t>04_課題管理表にステータスDV・残日数・遅延判定・行の自動着色を実装。</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
     </row>
@@ -18060,22 +18935,22 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>『週間PDCA (見本)』が本体と別に存在し、内容が本体とずれている。</t>
+          <t>『※未対象施設』とだけ書かれた行（④訪看契約・⑤SQ利用）が毎週コピーされ続けている。</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>見本の更新漏れで、書き方の基準が人によって変わる。</t>
+          <t>対象外の項目が常時表示され、シートのノイズになる。対象化した時に誰が判断するか決まっていない。</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>見本を別シートで持たず、テンプレート自体に入力例と注記を持たせる。</t>
+          <t>対象／対象外を施設マスタ側の属性で持ち、非対象は非表示にする。</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>00_はじめに に運用手順、各シートの黄色セルで入力箇所を明示。</t>
+          <t>01_施設マスタ I列『PDCA対象』で管理。カテゴリは04で必要な行だけ起票する運用。</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
@@ -18095,22 +18970,22 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>予算達成状況の判定が =IF(予算比&gt;=0,"〇","✕") の2値のみ。前月比の一部は文字列 '-'。</t>
+          <t>『週間PDCA (見本)』が本体と別に存在し、内容が本体とずれている。</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>あと一歩の未達と大幅未達が同じ『✕』。文字列混在で平均・グラフが崩れる。</t>
+          <t>見本の更新漏れで、書き方の基準が人によって変わる。</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>達成／要注意／未達の3段階にし、空欄は空欄のまま扱う。</t>
+          <t>見本を別シートで持たず、テンプレート自体に入力例と注記を持たせる。</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>06_ダッシュボードで 100%以上=〇、90%以上=△、それ未満=✕、未入力は『未入力』と判定。</t>
+          <t>00_はじめに に運用手順、各シートの黄色セルで入力箇所を明示。</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
@@ -18125,27 +19000,27 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>運用</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Sheet2 に居室番号・区分・年齢の生データが残置。個人に紐づく情報がシート内に混在。</t>
+          <t>予算達成状況の判定が =IF(予算比&gt;=0,"〇","✕") の2値のみ。前月比の一部は文字列 '-'。</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>配布時に意図しない情報が同梱される。マスタとしての位置づけも不明。</t>
+          <t>あと一歩の未達と大幅未達が同じ『✕』。文字列混在で平均・グラフが崩れる。</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>個人データは配布用テンプレートから分離する。</t>
+          <t>達成／要注意／未達の3段階にし、空欄は空欄のまま扱う。</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>本テンプレートには個人データを含めない。必要なら別ファイルで管理。</t>
+          <t>06_ダッシュボードで 100%以上=〇、90%以上=△、それ未満=✕、未入力は『未入力』と判定。</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
@@ -18160,27 +19035,27 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>拡張</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>施設一覧側に『グループホームイノベル信中島／公式名 小信中島』など名称差3件、住所照合注記あり。</t>
+          <t>Sheet2 に居室番号・区分・年齢の生データが残置。個人に紐づく情報がシート内に混在。</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>施設名がキーなのに正式名称と社内呼称が混在すると、集計時に名寄せできない。</t>
+          <t>配布時に意図しない情報が同梱される。マスタとしての位置づけも不明。</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>施設IDを主キーにし、名称は表示用の属性として持つ。</t>
+          <t>個人データは配布用テンプレートから分離する。</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>01_施設マスタに施設ID（F001〜F040）を付与。名称変更はマスタ1か所で吸収。</t>
+          <t>本テンプレートには個人データを含めない。必要なら別ファイルで管理。</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
@@ -18195,32 +19070,32 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>構造</t>
+          <t>拡張</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>月シート（4月〜26年9月の22枚）が、利用者ごとの日別稼働カレンダー・SS予約・営業行動・案件管理・加算要件の入力面を兼ねている。週間PDCAの文章は BF16 等の長大な文字列連結式で自動生成されている。</t>
+          <t>施設一覧側に『グループホームイノベル信中島／公式名 小信中島』など名称差3件、住所照合注記あり。</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>入力面（原簿）と管理面（PDCA）が同じシートに同居し、月が変わるたびシートを増やす必要がある。連結式で作った文章は、あとから数値として再利用できない。</t>
+          <t>施設名がキーなのに正式名称と社内呼称が混在すると、集計時に名寄せできない。</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>原簿は月次入力シートとして分離し、集計値だけをPDCA側へ渡す。</t>
+          <t>施設IDを主キーにし、名称は表示用の属性として持つ。</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>10〜13の月次入力シートに分離。週別集計値は05_週次KPIログが自動で参照する。</t>
+          <t>01_施設マスタに施設ID（F001〜F040）を付与。名称変更はマスタ1か所で吸収。</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>中</t>
         </is>
       </c>
     </row>
@@ -18235,22 +19110,22 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>案件管理が『kintone名×日別セルに進捗記号』のマトリクス（55〜78行）。相談元・区分・希望種別が別セルに散る。</t>
+          <t>月シート（4月〜26年9月の22枚）が、利用者ごとの日別稼働カレンダー・SS予約・営業行動・案件管理・加算要件の入力面を兼ねている。週間PDCAの文章は BF16 等の長大な文字列連結式で自動生成されている。</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>同じ案件の履歴が月シートをまたいで分断され、発掘→見学→体験→契約のリードタイムが測れない。</t>
+          <t>入力面（原簿）と管理面（PDCA）が同じシートに同居し、月が変わるたびシートを増やす必要がある。連結式で作った文章は、あとから数値として再利用できない。</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>案件は1件1行の台帳にし、各フェーズの日付を列で持つ。</t>
+          <t>原簿は月次入力シートとして分離し、集計値だけをPDCA側へ渡す。</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>14_案件管理台帳。日付列から見学・体験・入居件数を週次で自動集計し、停滞14日超は赤表示。</t>
+          <t>10〜13の月次入力シートに分離。週別集計値は05_週次KPIログが自動で参照する。</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
@@ -18265,32 +19140,32 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>運用</t>
+          <t>構造</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>重度障害者支援体制・福祉専門職員配置等加算の要件確認が、月シートの隅にチェック欄として置かれている（BR88 常勤比率0.368→✕ 等）。</t>
+          <t>案件管理が『kintone名×日別セルに進捗記号』のマトリクス（55〜78行）。相談元・区分・希望種別が別セルに散る。</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>算定可否の根拠が月シートを開かないと見えず、要件を割った時に誰がいつ気づくかが運用任せ。</t>
+          <t>同じ案件の履歴が月シートをまたいで分断され、発掘→見学→体験→契約のリードタイムが測れない。</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>要件判定を独立させ、割り込み時に『要対応』として表示する。</t>
+          <t>案件は1件1行の台帳にし、各フェーズの日付を列で持つ。</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>13_月次_加算要件に集約。夜勤加配は日別実績から取得率を自動計算、体制加算は✕が1つでもあれば『要対応』。</t>
+          <t>14_案件管理台帳。日付列から見学・体験・入居件数を週次で自動集計し、停滞14日超は赤表示。</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
     </row>
@@ -18300,38 +19175,73 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
+          <t>運用</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>重度障害者支援体制・福祉専門職員配置等加算の要件確認が、月シートの隅にチェック欄として置かれている（BR88 常勤比率0.368→✕ 等）。</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>算定可否の根拠が月シートを開かないと見えず、要件を割った時に誰がいつ気づくかが運用任せ。</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>要件判定を独立させ、割り込み時に『要対応』として表示する。</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>13_月次_加算要件に集約。夜勤加配は日別実績から取得率を自動計算、体制加算は✕が1つでもあれば『要対応』。</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
           <t>拡張</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>40施設分のファイルが個別に存在し、AMは自分の担当分だけを見る運用。</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>エリア長・本部が全体傾向（未達KPI・遅延課題の偏り）を把握するのに手作業の集約が必要。</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="E20" s="4" t="inlineStr">
         <is>
           <t>縦持ちログを束ねてピボット集計できる形にする。</t>
         </is>
       </c>
-      <c r="F19" s="4" t="inlineStr">
+      <c r="F20" s="4" t="inlineStr">
         <is>
           <t>05_週次KPIログは施設名・担当者を各行に持つため、40施設分を連結してそのまま集計可能。06に担当AM別の遅延件数を実装。</t>
         </is>
       </c>
-      <c r="G19" s="4" t="inlineStr">
+      <c r="G20" s="4" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G19"/>
-  <conditionalFormatting sqref="G2:G19">
+  <autoFilter ref="A1:G20"/>
+  <conditionalFormatting sqref="G2:G20">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$G2="高"</formula>
     </cfRule>
@@ -18346,7 +19256,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:E10"/>
+  <dimension ref="B2:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -18498,20 +19408,64 @@
     <row r="10" ht="30" customHeight="1">
       <c r="B10" s="4" t="inlineStr">
         <is>
+          <t>月次（月末）</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>担当AM</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>Excelで保存後、月締め処理を実行して翌月ブックを作成</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>締める前に必ずExcelで保存する（数式の値が確定するため）</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>月次（翌月初）</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>担当AM</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>16_年間推移で前月までの推移を確認</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>2か月連続で未達のKPIは対応方針を作り直す</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="B12" s="4" t="inlineStr">
+        <is>
           <t>随時</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>本部</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>01_施設マスタの担当変更・新規開設を反映</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>マスタ更新は本部のみ。現場は編集しない</t>
         </is>
